--- a/Score_Class_2026_Summary.xlsx
+++ b/Score_Class_2026_Summary.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="38300" yWindow="-7000" windowWidth="18380" windowHeight="20970" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="39620" yWindow="-7000" windowWidth="18090" windowHeight="20970" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exercise" sheetId="1" state="visible" r:id="rId1"/>
@@ -22,7 +22,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="B1d\-mmm\-yy"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <color rgb="FF000000"/>
@@ -84,6 +84,12 @@
       <sz val="12"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color rgb="FFFF0000"/>
+      <sz val="12"/>
+    </font>
+    <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="9"/>
@@ -114,12 +120,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.0499893185216834"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -133,6 +133,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.5999938962981048"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.7999816888943144"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -196,7 +202,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -249,52 +255,54 @@
     <xf numFmtId="164" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -306,28 +314,28 @@
     <xf numFmtId="164" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="11" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="12" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="ปกติ" xfId="0" builtinId="0"/>
@@ -417,7 +425,7 @@
       <col>3</col>
       <colOff>1313180</colOff>
       <row>5</row>
-      <rowOff>1423330</rowOff>
+      <rowOff>1420790</rowOff>
     </to>
     <pic>
       <nvPicPr>
@@ -643,19 +651,20 @@
     <col hidden="1" width="18" customWidth="1" min="5" max="6"/>
     <col hidden="1" width="10" customWidth="1" min="7" max="8"/>
     <col hidden="1" width="10.796875" customWidth="1" min="9" max="11"/>
-    <col width="4.6484375" customWidth="1" style="39" min="12" max="20"/>
-    <col width="4.796875" customWidth="1" min="21" max="26"/>
+    <col width="4.6484375" customWidth="1" style="41" min="12" max="20"/>
+    <col width="4.796875" customWidth="1" style="41" min="21" max="21"/>
+    <col width="4.796875" customWidth="1" min="22" max="26"/>
   </cols>
   <sheetData>
     <row r="2" ht="16" customHeight="1">
-      <c r="B2" s="38" t="inlineStr">
+      <c r="B2" s="40" t="inlineStr">
         <is>
           <t>รายงานแสดงจำนวนนิสิต จำแนกตามหมู่เรียน ภาคต้น ปีการศึกษา 2569</t>
         </is>
       </c>
     </row>
     <row r="3" ht="18.3" customHeight="1">
-      <c r="B3" s="38" t="inlineStr">
+      <c r="B3" s="40" t="inlineStr">
         <is>
           <t>มหาวิทยาลัยเกษตรศาสตร์ บางเขน ระดับการศึกษา ปริญญาตรี</t>
         </is>
@@ -672,7 +681,7 @@
           <t>01218332-65 การฉายแผนที่ Map Projection</t>
         </is>
       </c>
-      <c r="M4" s="39" t="inlineStr">
+      <c r="M4" s="41" t="inlineStr">
         <is>
           <t xml:space="preserve">รศ.ดร.ไพศาล สันติธรรมนนท์ </t>
         </is>
@@ -716,7 +725,7 @@
           <t>EX.3 Draw Sphere/Spheroid</t>
         </is>
       </c>
-      <c r="N6" s="28" t="inlineStr">
+      <c r="N6" s="25" t="inlineStr">
         <is>
           <t>Ex.4 EFG for Sphere</t>
         </is>
@@ -731,7 +740,7 @@
           <t>Ex.6 Tissot Indicator</t>
         </is>
       </c>
-      <c r="Q6" s="29" t="inlineStr">
+      <c r="Q6" s="26" t="inlineStr">
         <is>
           <t>MidTerm</t>
         </is>
@@ -746,8 +755,16 @@
           <t>Ex.8 Planar Map Projection</t>
         </is>
       </c>
-      <c r="T6" s="10" t="n"/>
-      <c r="U6" s="9" t="n"/>
+      <c r="T6" s="11" t="inlineStr">
+        <is>
+          <t>Ex.9 Mercator vs EqualEarth</t>
+        </is>
+      </c>
+      <c r="U6" s="11" t="inlineStr">
+        <is>
+          <t>Ex. UTM zone 47/48</t>
+        </is>
+      </c>
       <c r="V6" s="9" t="n"/>
       <c r="W6" s="9" t="n"/>
       <c r="X6" s="9" t="n"/>
@@ -805,32 +822,36 @@
           <t>Email Office365</t>
         </is>
       </c>
-      <c r="L7" s="22" t="n">
+      <c r="L7" s="20" t="n">
         <v>12</v>
       </c>
-      <c r="M7" s="22" t="n">
-        <v>10</v>
-      </c>
-      <c r="N7" s="22" t="n">
-        <v>10</v>
-      </c>
-      <c r="O7" s="22" t="n">
-        <v>10</v>
-      </c>
-      <c r="P7" s="22" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q7" s="30" t="n">
+      <c r="M7" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="N7" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="O7" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="P7" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q7" s="27" t="n">
         <v>26</v>
       </c>
-      <c r="R7" s="22" t="n">
-        <v>10</v>
-      </c>
-      <c r="S7" s="22" t="n">
-        <v>10</v>
-      </c>
-      <c r="T7" s="22" t="n"/>
-      <c r="U7" s="9" t="n"/>
+      <c r="R7" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="S7" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="U7" s="20" t="n">
+        <v>10</v>
+      </c>
       <c r="V7" s="9" t="n"/>
       <c r="W7" s="9" t="n"/>
       <c r="X7" s="9" t="n"/>
@@ -897,17 +918,19 @@
       <c r="P8" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="Q8" s="31" t="n">
+      <c r="Q8" s="28" t="n">
         <v>10</v>
       </c>
       <c r="R8" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="S8" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" s="10" t="n"/>
-      <c r="U8" s="9" t="n"/>
+      <c r="S8" s="10" t="n"/>
+      <c r="T8" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="U8" s="10" t="n">
+        <v>9</v>
+      </c>
       <c r="V8" s="9" t="n"/>
       <c r="W8" s="9" t="n"/>
       <c r="X8" s="9" t="n"/>
@@ -974,7 +997,7 @@
         <v>10</v>
       </c>
       <c r="P9" s="10" t="n"/>
-      <c r="Q9" s="31" t="n">
+      <c r="Q9" s="28" t="n">
         <v>4</v>
       </c>
       <c r="R9" s="10" t="n">
@@ -983,8 +1006,12 @@
       <c r="S9" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="T9" s="10" t="n"/>
-      <c r="U9" s="9" t="n"/>
+      <c r="T9" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="U9" s="10" t="n">
+        <v>9</v>
+      </c>
       <c r="V9" s="9" t="n"/>
       <c r="W9" s="9" t="n"/>
       <c r="X9" s="9" t="n"/>
@@ -1053,15 +1080,19 @@
       <c r="P10" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="Q10" s="31" t="n">
+      <c r="Q10" s="28" t="n">
         <v>4</v>
       </c>
       <c r="R10" s="10" t="n"/>
       <c r="S10" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="T10" s="10" t="n"/>
-      <c r="U10" s="9" t="n"/>
+      <c r="T10" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="U10" s="10" t="n">
+        <v>10</v>
+      </c>
       <c r="V10" s="9" t="n"/>
       <c r="W10" s="9" t="n"/>
       <c r="X10" s="9" t="n"/>
@@ -1134,7 +1165,7 @@
       <c r="P11" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="Q11" s="31" t="n">
+      <c r="Q11" s="28" t="n">
         <v>9</v>
       </c>
       <c r="R11" s="10" t="n">
@@ -1143,8 +1174,12 @@
       <c r="S11" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="T11" s="10" t="n"/>
-      <c r="U11" s="9" t="n"/>
+      <c r="T11" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="U11" s="10" t="n">
+        <v>7</v>
+      </c>
       <c r="V11" s="9" t="n"/>
       <c r="W11" s="9" t="n"/>
       <c r="X11" s="9" t="n"/>
@@ -1211,7 +1246,7 @@
       <c r="P12" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q12" s="31" t="n">
+      <c r="Q12" s="28" t="n">
         <v>9</v>
       </c>
       <c r="R12" s="10" t="n">
@@ -1220,8 +1255,12 @@
       <c r="S12" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="T12" s="10" t="n"/>
-      <c r="U12" s="9" t="n"/>
+      <c r="T12" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="U12" s="10" t="n">
+        <v>8</v>
+      </c>
       <c r="V12" s="9" t="n"/>
       <c r="W12" s="9" t="n"/>
       <c r="X12" s="9" t="n"/>
@@ -1284,7 +1323,7 @@
       <c r="N13" s="10" t="n"/>
       <c r="O13" s="10" t="n"/>
       <c r="P13" s="10" t="n"/>
-      <c r="Q13" s="31" t="n">
+      <c r="Q13" s="28" t="n">
         <v>0</v>
       </c>
       <c r="R13" s="10" t="n">
@@ -1293,8 +1332,12 @@
       <c r="S13" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="T13" s="10" t="n"/>
-      <c r="U13" s="9" t="n"/>
+      <c r="T13" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="U13" s="10" t="n">
+        <v>9</v>
+      </c>
       <c r="V13" s="9" t="n"/>
       <c r="W13" s="9" t="n"/>
       <c r="X13" s="9" t="n"/>
@@ -1363,7 +1406,7 @@
       <c r="P14" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="Q14" s="31" t="n">
+      <c r="Q14" s="28" t="n">
         <v>2</v>
       </c>
       <c r="R14" s="10" t="n">
@@ -1372,8 +1415,12 @@
       <c r="S14" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="T14" s="10" t="n"/>
-      <c r="U14" s="9" t="n"/>
+      <c r="T14" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="U14" s="10" t="n">
+        <v>7</v>
+      </c>
       <c r="V14" s="9" t="n"/>
       <c r="W14" s="9" t="n"/>
       <c r="X14" s="9" t="n"/>
@@ -1446,7 +1493,7 @@
       <c r="P15" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="Q15" s="31" t="n">
+      <c r="Q15" s="28" t="n">
         <v>11</v>
       </c>
       <c r="R15" s="10" t="n">
@@ -1455,8 +1502,12 @@
       <c r="S15" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="T15" s="10" t="n"/>
-      <c r="U15" s="9" t="n"/>
+      <c r="T15" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="U15" s="10" t="n">
+        <v>7</v>
+      </c>
       <c r="V15" s="9" t="n"/>
       <c r="W15" s="9" t="n"/>
       <c r="X15" s="9" t="n"/>
@@ -1525,7 +1576,7 @@
         <v>5</v>
       </c>
       <c r="P16" s="10" t="n"/>
-      <c r="Q16" s="31" t="n">
+      <c r="Q16" s="28" t="n">
         <v>14</v>
       </c>
       <c r="R16" s="10" t="n">
@@ -1534,8 +1585,12 @@
       <c r="S16" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="T16" s="10" t="n"/>
-      <c r="U16" s="9" t="n"/>
+      <c r="T16" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="U16" s="10" t="n">
+        <v>6</v>
+      </c>
       <c r="V16" s="9" t="n"/>
       <c r="W16" s="9" t="n"/>
       <c r="X16" s="9" t="n"/>
@@ -1608,7 +1663,7 @@
       <c r="P17" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q17" s="31" t="n">
+      <c r="Q17" s="28" t="n">
         <v>9</v>
       </c>
       <c r="R17" s="10" t="n">
@@ -1617,8 +1672,12 @@
       <c r="S17" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="T17" s="10" t="n"/>
-      <c r="U17" s="9" t="n"/>
+      <c r="T17" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="U17" s="10" t="n">
+        <v>6</v>
+      </c>
       <c r="V17" s="9" t="n"/>
       <c r="W17" s="9" t="n"/>
       <c r="X17" s="9" t="n"/>
@@ -1687,7 +1746,7 @@
       <c r="P18" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="Q18" s="31" t="n">
+      <c r="Q18" s="28" t="n">
         <v>2</v>
       </c>
       <c r="R18" s="10" t="n">
@@ -1696,8 +1755,12 @@
       <c r="S18" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="T18" s="10" t="n"/>
-      <c r="U18" s="9" t="n"/>
+      <c r="T18" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="U18" s="10" t="n">
+        <v>10</v>
+      </c>
       <c r="V18" s="9" t="n"/>
       <c r="W18" s="9" t="n"/>
       <c r="X18" s="9" t="n"/>
@@ -1760,7 +1823,7 @@
       <c r="N19" s="10" t="n"/>
       <c r="O19" s="10" t="n"/>
       <c r="P19" s="10" t="n"/>
-      <c r="Q19" s="31" t="n">
+      <c r="Q19" s="28" t="n">
         <v>0</v>
       </c>
       <c r="R19" s="10" t="n">
@@ -1769,8 +1832,12 @@
       <c r="S19" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="T19" s="10" t="n"/>
-      <c r="U19" s="9" t="n"/>
+      <c r="T19" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="U19" s="10" t="n">
+        <v>7</v>
+      </c>
       <c r="V19" s="9" t="n"/>
       <c r="W19" s="9" t="n"/>
       <c r="X19" s="9" t="n"/>
@@ -1843,15 +1910,19 @@
       <c r="P20" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q20" s="31" t="n">
+      <c r="Q20" s="28" t="n">
         <v>5</v>
       </c>
       <c r="R20" s="10" t="n">
         <v>5</v>
       </c>
       <c r="S20" s="10" t="n"/>
-      <c r="T20" s="10" t="n"/>
-      <c r="U20" s="9" t="n"/>
+      <c r="T20" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="U20" s="10" t="n">
+        <v>7</v>
+      </c>
       <c r="V20" s="9" t="n"/>
       <c r="W20" s="9" t="n"/>
       <c r="X20" s="9" t="n"/>
@@ -1920,15 +1991,19 @@
         <v>5</v>
       </c>
       <c r="P21" s="10" t="n"/>
-      <c r="Q21" s="31" t="n">
+      <c r="Q21" s="28" t="n">
         <v>6</v>
       </c>
       <c r="R21" s="10" t="n"/>
       <c r="S21" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="T21" s="10" t="n"/>
-      <c r="U21" s="9" t="n"/>
+      <c r="T21" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="U21" s="10" t="n">
+        <v>8</v>
+      </c>
       <c r="V21" s="9" t="n"/>
       <c r="W21" s="9" t="n"/>
       <c r="X21" s="9" t="n"/>
@@ -2001,7 +2076,7 @@
       <c r="P22" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q22" s="31" t="n">
+      <c r="Q22" s="28" t="n">
         <v>2</v>
       </c>
       <c r="R22" s="10" t="n">
@@ -2011,7 +2086,7 @@
         <v>9</v>
       </c>
       <c r="T22" s="10" t="n"/>
-      <c r="U22" s="9" t="n"/>
+      <c r="U22" s="10" t="n"/>
       <c r="V22" s="9" t="n"/>
       <c r="W22" s="9" t="n"/>
       <c r="X22" s="9" t="n"/>
@@ -2084,7 +2159,7 @@
       <c r="P23" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q23" s="31" t="n">
+      <c r="Q23" s="28" t="n">
         <v>16</v>
       </c>
       <c r="R23" s="10" t="n">
@@ -2093,8 +2168,12 @@
       <c r="S23" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="T23" s="10" t="n"/>
-      <c r="U23" s="9" t="n"/>
+      <c r="T23" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="U23" s="10" t="n">
+        <v>10</v>
+      </c>
       <c r="V23" s="9" t="n"/>
       <c r="W23" s="9" t="n"/>
       <c r="X23" s="9" t="n"/>
@@ -2167,7 +2246,7 @@
       <c r="P24" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q24" s="31" t="n">
+      <c r="Q24" s="28" t="n">
         <v>12</v>
       </c>
       <c r="R24" s="10" t="n">
@@ -2176,8 +2255,12 @@
       <c r="S24" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="T24" s="10" t="n"/>
-      <c r="U24" s="9" t="n"/>
+      <c r="T24" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="U24" s="10" t="n">
+        <v>10</v>
+      </c>
       <c r="V24" s="9" t="n"/>
       <c r="W24" s="9" t="n"/>
       <c r="X24" s="9" t="n"/>
@@ -2250,7 +2333,7 @@
       <c r="P25" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q25" s="31" t="n">
+      <c r="Q25" s="28" t="n">
         <v>9</v>
       </c>
       <c r="R25" s="10" t="n">
@@ -2259,8 +2342,12 @@
       <c r="S25" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="T25" s="10" t="n"/>
-      <c r="U25" s="9" t="n"/>
+      <c r="T25" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="U25" s="10" t="n">
+        <v>8</v>
+      </c>
       <c r="V25" s="9" t="n"/>
       <c r="W25" s="9" t="n"/>
       <c r="X25" s="9" t="n"/>
@@ -2333,7 +2420,7 @@
       <c r="P26" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q26" s="31" t="n">
+      <c r="Q26" s="28" t="n">
         <v>1</v>
       </c>
       <c r="R26" s="10" t="n">
@@ -2342,8 +2429,12 @@
       <c r="S26" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="T26" s="10" t="n"/>
-      <c r="U26" s="9" t="n"/>
+      <c r="T26" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="U26" s="10" t="n">
+        <v>8</v>
+      </c>
       <c r="V26" s="9" t="n"/>
       <c r="W26" s="9" t="n"/>
       <c r="X26" s="9" t="n"/>
@@ -2414,7 +2505,7 @@
       <c r="P27" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q27" s="31" t="n">
+      <c r="Q27" s="28" t="n">
         <v>1</v>
       </c>
       <c r="R27" s="10" t="n">
@@ -2423,8 +2514,12 @@
       <c r="S27" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="T27" s="10" t="n"/>
-      <c r="U27" s="9" t="n"/>
+      <c r="T27" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="U27" s="10" t="n">
+        <v>10</v>
+      </c>
       <c r="V27" s="9" t="n"/>
       <c r="W27" s="9" t="n"/>
       <c r="X27" s="9" t="n"/>
@@ -2493,7 +2588,7 @@
         <v>4</v>
       </c>
       <c r="P28" s="10" t="n"/>
-      <c r="Q28" s="31" t="n">
+      <c r="Q28" s="28" t="n">
         <v>8</v>
       </c>
       <c r="R28" s="10" t="n">
@@ -2503,7 +2598,7 @@
         <v>10</v>
       </c>
       <c r="T28" s="10" t="n"/>
-      <c r="U28" s="9" t="n"/>
+      <c r="U28" s="10" t="n"/>
       <c r="V28" s="9" t="n"/>
       <c r="W28" s="9" t="n"/>
       <c r="X28" s="9" t="n"/>
@@ -2576,7 +2671,7 @@
       <c r="P29" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q29" s="31" t="n">
+      <c r="Q29" s="28" t="n">
         <v>9</v>
       </c>
       <c r="R29" s="10" t="n">
@@ -2585,8 +2680,12 @@
       <c r="S29" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="T29" s="10" t="n"/>
-      <c r="U29" s="9" t="n"/>
+      <c r="T29" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="U29" s="10" t="n">
+        <v>10</v>
+      </c>
       <c r="V29" s="9" t="n"/>
       <c r="W29" s="9" t="n"/>
       <c r="X29" s="9" t="n"/>
@@ -2659,7 +2758,7 @@
       <c r="P30" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q30" s="31" t="n">
+      <c r="Q30" s="28" t="n">
         <v>11</v>
       </c>
       <c r="R30" s="10" t="n">
@@ -2668,8 +2767,12 @@
       <c r="S30" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="T30" s="10" t="n"/>
-      <c r="U30" s="9" t="n"/>
+      <c r="T30" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="U30" s="10" t="n">
+        <v>10</v>
+      </c>
       <c r="V30" s="9" t="n"/>
       <c r="W30" s="9" t="n"/>
       <c r="X30" s="9" t="n"/>
@@ -2677,71 +2780,71 @@
       <c r="Z30" s="9" t="n"/>
     </row>
     <row r="31" ht="18" customHeight="1">
-      <c r="B31" s="32" t="inlineStr">
+      <c r="B31" s="29" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="C31" s="33" t="inlineStr">
+      <c r="C31" s="30" t="inlineStr">
         <is>
           <t>6710553051</t>
         </is>
       </c>
-      <c r="D31" s="33" t="inlineStr">
+      <c r="D31" s="30" t="inlineStr">
         <is>
           <t>นายธนทัต มุทธากาญจน์</t>
         </is>
       </c>
-      <c r="E31" s="33" t="inlineStr">
+      <c r="E31" s="30" t="inlineStr">
         <is>
           <t>Mr. Tanatud MUTTAKARN</t>
         </is>
       </c>
-      <c r="F31" s="33" t="inlineStr">
+      <c r="F31" s="30" t="inlineStr">
         <is>
           <t>วิศวกรรมศาสตร์</t>
         </is>
       </c>
-      <c r="G31" s="33" t="inlineStr">
+      <c r="G31" s="30" t="inlineStr">
         <is>
           <t>วิศวกรรมสำรวจและสารสนเทศภูมิศาสตร์</t>
         </is>
       </c>
-      <c r="H31" s="33" t="inlineStr">
+      <c r="H31" s="30" t="inlineStr">
         <is>
           <t>E18</t>
         </is>
       </c>
-      <c r="I31" s="33" t="inlineStr">
+      <c r="I31" s="30" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="J31" s="33" t="inlineStr">
+      <c r="J31" s="30" t="inlineStr">
         <is>
           <t>tanatud.m@ku.th</t>
         </is>
       </c>
-      <c r="K31" s="34" t="inlineStr">
+      <c r="K31" s="31" t="inlineStr">
         <is>
           <t>tanatud.m@live.ku.th</t>
         </is>
       </c>
-      <c r="L31" s="35" t="n"/>
-      <c r="M31" s="35" t="n"/>
-      <c r="N31" s="35" t="n"/>
-      <c r="O31" s="35" t="n"/>
-      <c r="P31" s="35" t="n"/>
-      <c r="Q31" s="35" t="n"/>
-      <c r="R31" s="35" t="n"/>
-      <c r="S31" s="35" t="n"/>
-      <c r="T31" s="35" t="n"/>
-      <c r="U31" s="36" t="n"/>
-      <c r="V31" s="36" t="n"/>
-      <c r="W31" s="36" t="n"/>
-      <c r="X31" s="36" t="n"/>
-      <c r="Y31" s="36" t="n"/>
-      <c r="Z31" s="36" t="n"/>
+      <c r="L31" s="32" t="n"/>
+      <c r="M31" s="32" t="n"/>
+      <c r="N31" s="32" t="n"/>
+      <c r="O31" s="32" t="n"/>
+      <c r="P31" s="32" t="n"/>
+      <c r="Q31" s="32" t="n"/>
+      <c r="R31" s="32" t="n"/>
+      <c r="S31" s="32" t="n"/>
+      <c r="T31" s="32" t="n"/>
+      <c r="U31" s="32" t="n"/>
+      <c r="V31" s="33" t="n"/>
+      <c r="W31" s="33" t="n"/>
+      <c r="X31" s="33" t="n"/>
+      <c r="Y31" s="33" t="n"/>
+      <c r="Z31" s="33" t="n"/>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="B32" s="5" t="inlineStr">
@@ -2809,7 +2912,7 @@
       <c r="P32" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q32" s="31" t="n">
+      <c r="Q32" s="28" t="n">
         <v>14</v>
       </c>
       <c r="R32" s="10" t="n">
@@ -2818,8 +2921,12 @@
       <c r="S32" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="T32" s="10" t="n"/>
-      <c r="U32" s="9" t="n"/>
+      <c r="T32" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="U32" s="10" t="n">
+        <v>7</v>
+      </c>
       <c r="V32" s="9" t="n"/>
       <c r="W32" s="9" t="n"/>
       <c r="X32" s="9" t="n"/>
@@ -2890,7 +2997,7 @@
       <c r="P33" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q33" s="31" t="n">
+      <c r="Q33" s="28" t="n">
         <v>3</v>
       </c>
       <c r="R33" s="10" t="n">
@@ -2900,7 +3007,9 @@
         <v>10</v>
       </c>
       <c r="T33" s="10" t="n"/>
-      <c r="U33" s="9" t="n"/>
+      <c r="U33" s="10" t="n">
+        <v>10</v>
+      </c>
       <c r="V33" s="9" t="n"/>
       <c r="W33" s="9" t="n"/>
       <c r="X33" s="9" t="n"/>
@@ -2982,8 +3091,12 @@
       <c r="S34" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="T34" s="10" t="n"/>
-      <c r="U34" s="9" t="n"/>
+      <c r="T34" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="U34" s="10" t="n">
+        <v>10</v>
+      </c>
       <c r="V34" s="9" t="n"/>
       <c r="W34" s="9" t="n"/>
       <c r="X34" s="9" t="n"/>
@@ -3056,7 +3169,7 @@
       <c r="P35" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q35" s="31" t="n">
+      <c r="Q35" s="28" t="n">
         <v>17</v>
       </c>
       <c r="R35" s="10" t="n">
@@ -3065,8 +3178,12 @@
       <c r="S35" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="T35" s="10" t="n"/>
-      <c r="U35" s="9" t="n"/>
+      <c r="T35" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="U35" s="10" t="n">
+        <v>9</v>
+      </c>
       <c r="V35" s="9" t="n"/>
       <c r="W35" s="9" t="n"/>
       <c r="X35" s="9" t="n"/>
@@ -3139,7 +3256,7 @@
       <c r="P36" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q36" s="31" t="n">
+      <c r="Q36" s="28" t="n">
         <v>7</v>
       </c>
       <c r="R36" s="10" t="n">
@@ -3148,8 +3265,12 @@
       <c r="S36" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="T36" s="10" t="n"/>
-      <c r="U36" s="9" t="n"/>
+      <c r="T36" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="U36" s="10" t="n">
+        <v>7</v>
+      </c>
       <c r="V36" s="9" t="n"/>
       <c r="W36" s="9" t="n"/>
       <c r="X36" s="9" t="n"/>
@@ -3222,7 +3343,7 @@
       <c r="P37" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="Q37" s="31" t="n">
+      <c r="Q37" s="28" t="n">
         <v>17</v>
       </c>
       <c r="R37" s="10" t="n">
@@ -3231,8 +3352,12 @@
       <c r="S37" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="T37" s="10" t="n"/>
-      <c r="U37" s="9" t="n"/>
+      <c r="T37" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="U37" s="10" t="n">
+        <v>6</v>
+      </c>
       <c r="V37" s="9" t="n"/>
       <c r="W37" s="9" t="n"/>
       <c r="X37" s="9" t="n"/>
@@ -3303,7 +3428,7 @@
       <c r="P38" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q38" s="31" t="n">
+      <c r="Q38" s="28" t="n">
         <v>16</v>
       </c>
       <c r="R38" s="10" t="n">
@@ -3312,8 +3437,12 @@
       <c r="S38" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="T38" s="10" t="n"/>
-      <c r="U38" s="9" t="n"/>
+      <c r="T38" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="U38" s="10" t="n">
+        <v>8</v>
+      </c>
       <c r="V38" s="9" t="n"/>
       <c r="W38" s="9" t="n"/>
       <c r="X38" s="9" t="n"/>
@@ -3386,7 +3515,7 @@
       <c r="P39" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q39" s="31" t="n">
+      <c r="Q39" s="28" t="n">
         <v>22</v>
       </c>
       <c r="R39" s="10" t="n">
@@ -3395,8 +3524,12 @@
       <c r="S39" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="T39" s="10" t="n"/>
-      <c r="U39" s="9" t="n"/>
+      <c r="T39" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="U39" s="10" t="n">
+        <v>10</v>
+      </c>
       <c r="V39" s="9" t="n"/>
       <c r="W39" s="9" t="n"/>
       <c r="X39" s="9" t="n"/>
@@ -3469,7 +3602,7 @@
       <c r="P40" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q40" s="31" t="n">
+      <c r="Q40" s="28" t="n">
         <v>15</v>
       </c>
       <c r="R40" s="10" t="n">
@@ -3478,8 +3611,12 @@
       <c r="S40" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="T40" s="10" t="n"/>
-      <c r="U40" s="9" t="n"/>
+      <c r="T40" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="U40" s="10" t="n">
+        <v>10</v>
+      </c>
       <c r="V40" s="9" t="n"/>
       <c r="W40" s="9" t="n"/>
       <c r="X40" s="9" t="n"/>
@@ -3552,7 +3689,7 @@
       <c r="P41" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q41" s="31" t="n">
+      <c r="Q41" s="28" t="n">
         <v>6</v>
       </c>
       <c r="R41" s="10" t="n">
@@ -3561,8 +3698,12 @@
       <c r="S41" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="T41" s="10" t="n"/>
-      <c r="U41" s="9" t="n"/>
+      <c r="T41" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="U41" s="10" t="n">
+        <v>10</v>
+      </c>
       <c r="V41" s="9" t="n"/>
       <c r="W41" s="9" t="n"/>
       <c r="X41" s="9" t="n"/>
@@ -3633,15 +3774,19 @@
         <v>10</v>
       </c>
       <c r="P42" s="10" t="n"/>
-      <c r="Q42" s="31" t="n">
+      <c r="Q42" s="28" t="n">
         <v>4</v>
       </c>
       <c r="R42" s="10" t="n">
         <v>10</v>
       </c>
       <c r="S42" s="10" t="n"/>
-      <c r="T42" s="10" t="n"/>
-      <c r="U42" s="9" t="n"/>
+      <c r="T42" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="U42" s="10" t="n">
+        <v>7</v>
+      </c>
       <c r="V42" s="9" t="n"/>
       <c r="W42" s="9" t="n"/>
       <c r="X42" s="9" t="n"/>
@@ -3714,7 +3859,7 @@
       <c r="P43" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="Q43" s="31" t="n">
+      <c r="Q43" s="28" t="n">
         <v>4</v>
       </c>
       <c r="R43" s="10" t="n">
@@ -3723,8 +3868,12 @@
       <c r="S43" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="T43" s="10" t="n"/>
-      <c r="U43" s="9" t="n"/>
+      <c r="T43" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="U43" s="10" t="n">
+        <v>4</v>
+      </c>
       <c r="V43" s="9" t="n"/>
       <c r="W43" s="9" t="n"/>
       <c r="X43" s="9" t="n"/>
@@ -3797,7 +3946,7 @@
       <c r="P44" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="Q44" s="31" t="n">
+      <c r="Q44" s="28" t="n">
         <v>4</v>
       </c>
       <c r="R44" s="10" t="n">
@@ -3806,8 +3955,12 @@
       <c r="S44" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="T44" s="10" t="n"/>
-      <c r="U44" s="9" t="n"/>
+      <c r="T44" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="U44" s="10" t="n">
+        <v>10</v>
+      </c>
       <c r="V44" s="9" t="n"/>
       <c r="W44" s="9" t="n"/>
       <c r="X44" s="9" t="n"/>
@@ -3880,7 +4033,7 @@
       <c r="P45" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="Q45" s="31" t="n">
+      <c r="Q45" s="28" t="n">
         <v>18</v>
       </c>
       <c r="R45" s="10" t="n">
@@ -3889,8 +4042,12 @@
       <c r="S45" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="T45" s="10" t="n"/>
-      <c r="U45" s="9" t="n"/>
+      <c r="T45" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="U45" s="10" t="n">
+        <v>9</v>
+      </c>
       <c r="V45" s="9" t="n"/>
       <c r="W45" s="9" t="n"/>
       <c r="X45" s="9" t="n"/>
@@ -3963,7 +4120,7 @@
       <c r="P46" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q46" s="31" t="n">
+      <c r="Q46" s="28" t="n">
         <v>3</v>
       </c>
       <c r="R46" s="10" t="n">
@@ -3972,8 +4129,12 @@
       <c r="S46" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="T46" s="10" t="n"/>
-      <c r="U46" s="9" t="n"/>
+      <c r="T46" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="U46" s="10" t="n">
+        <v>10</v>
+      </c>
       <c r="V46" s="9" t="n"/>
       <c r="W46" s="9" t="n"/>
       <c r="X46" s="9" t="n"/>
@@ -4046,7 +4207,7 @@
       <c r="P47" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q47" s="31" t="n">
+      <c r="Q47" s="28" t="n">
         <v>13</v>
       </c>
       <c r="R47" s="10" t="n">
@@ -4055,8 +4216,12 @@
       <c r="S47" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="T47" s="10" t="n"/>
-      <c r="U47" s="9" t="n"/>
+      <c r="T47" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="U47" s="10" t="n">
+        <v>10</v>
+      </c>
       <c r="V47" s="9" t="n"/>
       <c r="W47" s="9" t="n"/>
       <c r="X47" s="9" t="n"/>
@@ -4129,7 +4294,7 @@
       <c r="P48" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q48" s="31" t="n">
+      <c r="Q48" s="28" t="n">
         <v>6</v>
       </c>
       <c r="R48" s="10" t="n">
@@ -4138,8 +4303,12 @@
       <c r="S48" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="T48" s="10" t="n"/>
-      <c r="U48" s="9" t="n"/>
+      <c r="T48" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="U48" s="10" t="n">
+        <v>10</v>
+      </c>
       <c r="V48" s="9" t="n"/>
       <c r="W48" s="9" t="n"/>
       <c r="X48" s="9" t="n"/>
@@ -4212,7 +4381,7 @@
       <c r="P49" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q49" s="31" t="n">
+      <c r="Q49" s="28" t="n">
         <v>21</v>
       </c>
       <c r="R49" s="10" t="n">
@@ -4221,8 +4390,12 @@
       <c r="S49" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="T49" s="10" t="n"/>
-      <c r="U49" s="9" t="n"/>
+      <c r="T49" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="U49" s="10" t="n">
+        <v>7</v>
+      </c>
       <c r="V49" s="9" t="n"/>
       <c r="W49" s="9" t="n"/>
       <c r="X49" s="9" t="n"/>
@@ -4295,7 +4468,7 @@
       <c r="P50" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q50" s="31" t="n">
+      <c r="Q50" s="28" t="n">
         <v>20</v>
       </c>
       <c r="R50" s="10" t="n">
@@ -4304,8 +4477,12 @@
       <c r="S50" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="T50" s="10" t="n"/>
-      <c r="U50" s="9" t="n"/>
+      <c r="T50" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="U50" s="10" t="n">
+        <v>10</v>
+      </c>
       <c r="V50" s="9" t="n"/>
       <c r="W50" s="9" t="n"/>
       <c r="X50" s="9" t="n"/>
@@ -4376,15 +4553,19 @@
         <v>10</v>
       </c>
       <c r="P51" s="10" t="n"/>
-      <c r="Q51" s="31" t="n">
+      <c r="Q51" s="28" t="n">
         <v>4</v>
       </c>
       <c r="R51" s="10" t="n">
         <v>4</v>
       </c>
       <c r="S51" s="10" t="n"/>
-      <c r="T51" s="10" t="n"/>
-      <c r="U51" s="9" t="n"/>
+      <c r="T51" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="U51" s="10" t="n">
+        <v>3</v>
+      </c>
       <c r="V51" s="9" t="n"/>
       <c r="W51" s="9" t="n"/>
       <c r="X51" s="9" t="n"/>
@@ -4457,7 +4638,7 @@
       <c r="P52" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="Q52" s="31" t="n">
+      <c r="Q52" s="28" t="n">
         <v>22</v>
       </c>
       <c r="R52" s="10" t="n">
@@ -4466,8 +4647,12 @@
       <c r="S52" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="T52" s="10" t="n"/>
-      <c r="U52" s="9" t="n"/>
+      <c r="T52" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="U52" s="10" t="n">
+        <v>10</v>
+      </c>
       <c r="V52" s="9" t="n"/>
       <c r="W52" s="9" t="n"/>
       <c r="X52" s="9" t="n"/>
@@ -4540,7 +4725,7 @@
       <c r="P53" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q53" s="31" t="n">
+      <c r="Q53" s="28" t="n">
         <v>19</v>
       </c>
       <c r="R53" s="10" t="n">
@@ -4549,8 +4734,10 @@
       <c r="S53" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="T53" s="10" t="n"/>
-      <c r="U53" s="9" t="n"/>
+      <c r="T53" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="U53" s="10" t="n"/>
       <c r="V53" s="9" t="n"/>
       <c r="W53" s="9" t="n"/>
       <c r="X53" s="9" t="n"/>
@@ -4558,7 +4745,12 @@
       <c r="Z53" s="9" t="n"/>
     </row>
     <row r="54">
-      <c r="Q54" s="23" t="inlineStr">
+      <c r="Q54" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="T54" s="41" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
@@ -4600,8 +4792,11 @@
     <col width="3.796875" customWidth="1" style="12" min="4" max="4"/>
     <col width="3.796875" customWidth="1" min="5" max="5"/>
     <col width="3.796875" customWidth="1" style="18" min="6" max="6"/>
-    <col width="3.796875" customWidth="1" style="20" min="7" max="7"/>
-    <col width="3.796875" customWidth="1" min="8" max="14"/>
+    <col width="3.796875" customWidth="1" style="41" min="7" max="7"/>
+    <col width="3.796875" customWidth="1" min="8" max="8"/>
+    <col width="3.796875" customWidth="1" style="36" min="9" max="9"/>
+    <col width="3.796875" customWidth="1" style="41" min="10" max="10"/>
+    <col width="3.796875" customWidth="1" min="11" max="14"/>
     <col width="8.796875" customWidth="1" min="15" max="15"/>
     <col width="4.6484375" customWidth="1" min="16" max="26"/>
   </cols>
@@ -4625,48 +4820,54 @@
           <t>05-20JUL69</t>
         </is>
       </c>
-      <c r="F6" s="40" t="inlineStr">
+      <c r="F6" s="42" t="inlineStr">
         <is>
           <t>06-10/8/1969</t>
         </is>
       </c>
-      <c r="G6" s="41" t="n">
+      <c r="G6" s="43" t="n">
         <v>46258</v>
       </c>
-      <c r="H6" s="42" t="n">
+      <c r="H6" s="43" t="n">
         <v>46265</v>
       </c>
-      <c r="I6" s="17" t="n"/>
-      <c r="J6" s="17" t="n"/>
+      <c r="I6" s="44" t="n">
+        <v>25460</v>
+      </c>
+      <c r="J6" s="39" t="inlineStr">
+        <is>
+          <t>21/Sept/2569</t>
+        </is>
+      </c>
       <c r="K6" s="17" t="n"/>
       <c r="L6" s="17" t="n"/>
       <c r="M6" s="17" t="n"/>
       <c r="N6" s="17" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="25">
+      <c r="A7" s="22">
         <f>Exercise!B7</f>
         <v/>
       </c>
-      <c r="B7" s="25">
+      <c r="B7" s="22">
         <f>Exercise!C7</f>
         <v/>
       </c>
-      <c r="C7" s="25">
+      <c r="C7" s="22">
         <f>Exercise!D7</f>
         <v/>
       </c>
-      <c r="D7" s="26" t="n"/>
-      <c r="E7" s="26" t="n"/>
-      <c r="F7" s="27" t="n"/>
-      <c r="G7" s="27" t="n"/>
-      <c r="H7" s="26" t="n"/>
-      <c r="I7" s="26" t="n"/>
-      <c r="J7" s="26" t="n"/>
-      <c r="K7" s="26" t="n"/>
-      <c r="L7" s="26" t="n"/>
-      <c r="M7" s="26" t="n"/>
-      <c r="N7" s="26" t="n"/>
+      <c r="D7" s="23" t="n"/>
+      <c r="E7" s="23" t="n"/>
+      <c r="F7" s="24" t="n"/>
+      <c r="G7" s="35" t="n"/>
+      <c r="H7" s="23" t="n"/>
+      <c r="I7" s="38" t="n"/>
+      <c r="J7" s="24" t="n"/>
+      <c r="K7" s="23" t="n"/>
+      <c r="L7" s="23" t="n"/>
+      <c r="M7" s="23" t="n"/>
+      <c r="N7" s="23" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="9">
@@ -4688,12 +4889,14 @@
       <c r="F8" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="G8" s="21" t="n"/>
+      <c r="G8" s="10" t="n"/>
       <c r="H8" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I8" s="9" t="n"/>
-      <c r="J8" s="9" t="n"/>
+      <c r="I8" s="38" t="n"/>
+      <c r="J8" s="10" t="n">
+        <v>1</v>
+      </c>
       <c r="K8" s="9" t="n"/>
       <c r="L8" s="9" t="n"/>
       <c r="M8" s="9" t="n"/>
@@ -4717,14 +4920,18 @@
         <v>1</v>
       </c>
       <c r="F9" s="14" t="n"/>
-      <c r="G9" s="21" t="n">
+      <c r="G9" s="10" t="n">
         <v>1</v>
       </c>
       <c r="H9" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I9" s="9" t="n"/>
-      <c r="J9" s="9" t="n"/>
+      <c r="I9" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" s="10" t="n">
+        <v>1</v>
+      </c>
       <c r="K9" s="9" t="n"/>
       <c r="L9" s="9" t="n"/>
       <c r="M9" s="9" t="n"/>
@@ -4748,12 +4955,14 @@
         <v>1</v>
       </c>
       <c r="F10" s="14" t="n"/>
-      <c r="G10" s="21" t="n"/>
+      <c r="G10" s="10" t="n"/>
       <c r="H10" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I10" s="9" t="n"/>
-      <c r="J10" s="9" t="n"/>
+      <c r="I10" s="38" t="n"/>
+      <c r="J10" s="10" t="n">
+        <v>1</v>
+      </c>
       <c r="K10" s="9" t="n"/>
       <c r="L10" s="9" t="n"/>
       <c r="M10" s="9" t="n"/>
@@ -4781,14 +4990,18 @@
       <c r="F11" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="G11" s="21" t="n">
+      <c r="G11" s="10" t="n">
         <v>1</v>
       </c>
       <c r="H11" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I11" s="9" t="n"/>
-      <c r="J11" s="9" t="n"/>
+      <c r="I11" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" s="10" t="n">
+        <v>1</v>
+      </c>
       <c r="K11" s="9" t="n"/>
       <c r="L11" s="9" t="n"/>
       <c r="M11" s="9" t="n"/>
@@ -4816,14 +5029,18 @@
       <c r="F12" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="G12" s="21" t="n">
+      <c r="G12" s="10" t="n">
         <v>1</v>
       </c>
       <c r="H12" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I12" s="9" t="n"/>
-      <c r="J12" s="9" t="n"/>
+      <c r="I12" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" s="10" t="n">
+        <v>1</v>
+      </c>
       <c r="K12" s="9" t="n"/>
       <c r="L12" s="9" t="n"/>
       <c r="M12" s="9" t="n"/>
@@ -4847,14 +5064,18 @@
         <v>1</v>
       </c>
       <c r="F13" s="14" t="n"/>
-      <c r="G13" s="21" t="n">
+      <c r="G13" s="10" t="n">
         <v>1</v>
       </c>
       <c r="H13" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I13" s="9" t="n"/>
-      <c r="J13" s="9" t="n"/>
+      <c r="I13" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" s="10" t="n">
+        <v>1</v>
+      </c>
       <c r="K13" s="9" t="n"/>
       <c r="L13" s="9" t="n"/>
       <c r="M13" s="9" t="n"/>
@@ -4880,12 +5101,16 @@
       <c r="F14" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="G14" s="21" t="n">
+      <c r="G14" s="10" t="n">
         <v>1</v>
       </c>
       <c r="H14" s="9" t="n"/>
-      <c r="I14" s="9" t="n"/>
-      <c r="J14" s="9" t="n"/>
+      <c r="I14" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" s="10" t="n">
+        <v>1</v>
+      </c>
       <c r="K14" s="9" t="n"/>
       <c r="L14" s="9" t="n"/>
       <c r="M14" s="9" t="n"/>
@@ -4913,14 +5138,18 @@
       <c r="F15" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="G15" s="21" t="n">
+      <c r="G15" s="10" t="n">
         <v>1</v>
       </c>
       <c r="H15" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I15" s="9" t="n"/>
-      <c r="J15" s="9" t="n"/>
+      <c r="I15" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" s="10" t="n">
+        <v>1</v>
+      </c>
       <c r="K15" s="9" t="n"/>
       <c r="L15" s="9" t="n"/>
       <c r="M15" s="9" t="n"/>
@@ -4948,14 +5177,18 @@
       <c r="F16" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="G16" s="21" t="n">
+      <c r="G16" s="10" t="n">
         <v>1</v>
       </c>
       <c r="H16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I16" s="9" t="n"/>
-      <c r="J16" s="9" t="n"/>
+      <c r="I16" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="J16" s="10" t="n">
+        <v>1</v>
+      </c>
       <c r="K16" s="9" t="n"/>
       <c r="L16" s="9" t="n"/>
       <c r="M16" s="9" t="n"/>
@@ -4983,14 +5216,18 @@
       <c r="F17" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="G17" s="21" t="n">
+      <c r="G17" s="10" t="n">
         <v>1</v>
       </c>
       <c r="H17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I17" s="9" t="n"/>
-      <c r="J17" s="9" t="n"/>
+      <c r="I17" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" s="10" t="n">
+        <v>1</v>
+      </c>
       <c r="K17" s="9" t="n"/>
       <c r="L17" s="9" t="n"/>
       <c r="M17" s="9" t="n"/>
@@ -5016,14 +5253,18 @@
       <c r="F18" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="G18" s="21" t="n">
+      <c r="G18" s="10" t="n">
         <v>1</v>
       </c>
       <c r="H18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I18" s="9" t="n"/>
-      <c r="J18" s="9" t="n"/>
+      <c r="I18" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" s="10" t="n">
+        <v>1</v>
+      </c>
       <c r="K18" s="9" t="n"/>
       <c r="L18" s="9" t="n"/>
       <c r="M18" s="9" t="n"/>
@@ -5047,14 +5288,18 @@
         <v>1</v>
       </c>
       <c r="F19" s="14" t="n"/>
-      <c r="G19" s="21" t="n">
+      <c r="G19" s="10" t="n">
         <v>1</v>
       </c>
       <c r="H19" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I19" s="9" t="n"/>
-      <c r="J19" s="9" t="n"/>
+      <c r="I19" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" s="10" t="n">
+        <v>1</v>
+      </c>
       <c r="K19" s="9" t="n"/>
       <c r="L19" s="9" t="n"/>
       <c r="M19" s="9" t="n"/>
@@ -5078,14 +5323,18 @@
       <c r="F20" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="G20" s="21" t="n">
+      <c r="G20" s="10" t="n">
         <v>1</v>
       </c>
       <c r="H20" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I20" s="9" t="n"/>
-      <c r="J20" s="9" t="n"/>
+      <c r="I20" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" s="10" t="n">
+        <v>1</v>
+      </c>
       <c r="K20" s="9" t="n"/>
       <c r="L20" s="9" t="n"/>
       <c r="M20" s="9" t="n"/>
@@ -5111,10 +5360,12 @@
         <v>1</v>
       </c>
       <c r="F21" s="14" t="n"/>
-      <c r="G21" s="21" t="n"/>
+      <c r="G21" s="10" t="n"/>
       <c r="H21" s="9" t="n"/>
-      <c r="I21" s="9" t="n"/>
-      <c r="J21" s="9" t="n"/>
+      <c r="I21" s="38" t="n"/>
+      <c r="J21" s="10" t="n">
+        <v>1</v>
+      </c>
       <c r="K21" s="9" t="n"/>
       <c r="L21" s="9" t="n"/>
       <c r="M21" s="9" t="n"/>
@@ -5142,14 +5393,16 @@
       <c r="F22" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="G22" s="21" t="n">
+      <c r="G22" s="10" t="n">
         <v>1</v>
       </c>
       <c r="H22" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I22" s="9" t="n"/>
-      <c r="J22" s="9" t="n"/>
+      <c r="I22" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" s="10" t="n"/>
       <c r="K22" s="9" t="n"/>
       <c r="L22" s="9" t="n"/>
       <c r="M22" s="9" t="n"/>
@@ -5177,14 +5430,18 @@
       <c r="F23" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="G23" s="21" t="n">
+      <c r="G23" s="10" t="n">
         <v>1</v>
       </c>
       <c r="H23" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I23" s="9" t="n"/>
-      <c r="J23" s="9" t="n"/>
+      <c r="I23" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" s="10" t="n">
+        <v>1</v>
+      </c>
       <c r="K23" s="9" t="n"/>
       <c r="L23" s="9" t="n"/>
       <c r="M23" s="9" t="n"/>
@@ -5212,14 +5469,18 @@
       <c r="F24" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="G24" s="21" t="n">
+      <c r="G24" s="10" t="n">
         <v>1</v>
       </c>
       <c r="H24" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I24" s="9" t="n"/>
-      <c r="J24" s="9" t="n"/>
+      <c r="I24" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" s="10" t="n">
+        <v>1</v>
+      </c>
       <c r="K24" s="9" t="n"/>
       <c r="L24" s="9" t="n"/>
       <c r="M24" s="9" t="n"/>
@@ -5247,14 +5508,18 @@
       <c r="F25" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="G25" s="21" t="n">
+      <c r="G25" s="10" t="n">
         <v>1</v>
       </c>
       <c r="H25" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I25" s="9" t="n"/>
-      <c r="J25" s="9" t="n"/>
+      <c r="I25" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" s="10" t="n">
+        <v>1</v>
+      </c>
       <c r="K25" s="9" t="n"/>
       <c r="L25" s="9" t="n"/>
       <c r="M25" s="9" t="n"/>
@@ -5282,14 +5547,18 @@
       <c r="F26" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="G26" s="21" t="n">
+      <c r="G26" s="10" t="n">
         <v>1</v>
       </c>
       <c r="H26" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I26" s="9" t="n"/>
-      <c r="J26" s="9" t="n"/>
+      <c r="I26" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="J26" s="10" t="n">
+        <v>1</v>
+      </c>
       <c r="K26" s="9" t="n"/>
       <c r="L26" s="9" t="n"/>
       <c r="M26" s="9" t="n"/>
@@ -5315,14 +5584,18 @@
       <c r="F27" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="G27" s="21" t="n">
+      <c r="G27" s="10" t="n">
         <v>1</v>
       </c>
       <c r="H27" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I27" s="9" t="n"/>
-      <c r="J27" s="9" t="n"/>
+      <c r="I27" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="J27" s="10" t="n">
+        <v>1</v>
+      </c>
       <c r="K27" s="9" t="n"/>
       <c r="L27" s="9" t="n"/>
       <c r="M27" s="9" t="n"/>
@@ -5348,12 +5621,14 @@
       <c r="F28" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="G28" s="21" t="n">
+      <c r="G28" s="10" t="n">
         <v>1</v>
       </c>
       <c r="H28" s="9" t="n"/>
-      <c r="I28" s="9" t="n"/>
-      <c r="J28" s="9" t="n"/>
+      <c r="I28" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="J28" s="10" t="n"/>
       <c r="K28" s="9" t="n"/>
       <c r="L28" s="9" t="n"/>
       <c r="M28" s="9" t="n"/>
@@ -5381,14 +5656,18 @@
       <c r="F29" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="G29" s="21" t="n">
+      <c r="G29" s="10" t="n">
         <v>1</v>
       </c>
       <c r="H29" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I29" s="9" t="n"/>
-      <c r="J29" s="9" t="n"/>
+      <c r="I29" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="J29" s="10" t="n">
+        <v>1</v>
+      </c>
       <c r="K29" s="9" t="n"/>
       <c r="L29" s="9" t="n"/>
       <c r="M29" s="9" t="n"/>
@@ -5416,14 +5695,18 @@
       <c r="F30" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="G30" s="21" t="n">
+      <c r="G30" s="10" t="n">
         <v>1</v>
       </c>
       <c r="H30" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I30" s="9" t="n"/>
-      <c r="J30" s="9" t="n"/>
+      <c r="I30" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="J30" s="10" t="n">
+        <v>1</v>
+      </c>
       <c r="K30" s="9" t="n"/>
       <c r="L30" s="9" t="n"/>
       <c r="M30" s="9" t="n"/>
@@ -5445,10 +5728,10 @@
       <c r="D31" s="13" t="n"/>
       <c r="E31" s="15" t="n"/>
       <c r="F31" s="14" t="n"/>
-      <c r="G31" s="21" t="n"/>
+      <c r="G31" s="10" t="n"/>
       <c r="H31" s="9" t="n"/>
-      <c r="I31" s="9" t="n"/>
-      <c r="J31" s="9" t="n"/>
+      <c r="I31" s="38" t="n"/>
+      <c r="J31" s="10" t="n"/>
       <c r="K31" s="9" t="n"/>
       <c r="L31" s="9" t="n"/>
       <c r="M31" s="9" t="n"/>
@@ -5476,14 +5759,18 @@
       <c r="F32" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="G32" s="21" t="n">
+      <c r="G32" s="10" t="n">
         <v>1</v>
       </c>
       <c r="H32" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I32" s="9" t="n"/>
-      <c r="J32" s="9" t="n"/>
+      <c r="I32" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="J32" s="10" t="n">
+        <v>1</v>
+      </c>
       <c r="K32" s="9" t="n"/>
       <c r="L32" s="9" t="n"/>
       <c r="M32" s="9" t="n"/>
@@ -5509,14 +5796,18 @@
       <c r="F33" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="G33" s="21" t="n">
+      <c r="G33" s="10" t="n">
         <v>1</v>
       </c>
       <c r="H33" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I33" s="9" t="n"/>
-      <c r="J33" s="9" t="n"/>
+      <c r="I33" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="J33" s="10" t="n">
+        <v>1</v>
+      </c>
       <c r="K33" s="9" t="n"/>
       <c r="L33" s="9" t="n"/>
       <c r="M33" s="9" t="n"/>
@@ -5544,14 +5835,18 @@
       <c r="F34" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="G34" s="21" t="n">
+      <c r="G34" s="10" t="n">
         <v>1</v>
       </c>
       <c r="H34" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I34" s="9" t="n"/>
-      <c r="J34" s="9" t="n"/>
+      <c r="I34" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="J34" s="10" t="n">
+        <v>1</v>
+      </c>
       <c r="K34" s="9" t="n"/>
       <c r="L34" s="9" t="n"/>
       <c r="M34" s="9" t="n"/>
@@ -5579,14 +5874,18 @@
       <c r="F35" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="G35" s="21" t="n">
+      <c r="G35" s="10" t="n">
         <v>1</v>
       </c>
       <c r="H35" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I35" s="9" t="n"/>
-      <c r="J35" s="9" t="n"/>
+      <c r="I35" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="J35" s="10" t="n">
+        <v>1</v>
+      </c>
       <c r="K35" s="9" t="n"/>
       <c r="L35" s="9" t="n"/>
       <c r="M35" s="9" t="n"/>
@@ -5614,12 +5913,16 @@
       <c r="F36" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="G36" s="21" t="n">
+      <c r="G36" s="10" t="n">
         <v>1</v>
       </c>
       <c r="H36" s="9" t="n"/>
-      <c r="I36" s="9" t="n"/>
-      <c r="J36" s="9" t="n"/>
+      <c r="I36" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="J36" s="10" t="n">
+        <v>1</v>
+      </c>
       <c r="K36" s="9" t="n"/>
       <c r="L36" s="9" t="n"/>
       <c r="M36" s="9" t="n"/>
@@ -5647,14 +5950,18 @@
       <c r="F37" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="G37" s="21" t="n">
+      <c r="G37" s="10" t="n">
         <v>1</v>
       </c>
       <c r="H37" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I37" s="9" t="n"/>
-      <c r="J37" s="9" t="n"/>
+      <c r="I37" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="J37" s="10" t="n">
+        <v>1</v>
+      </c>
       <c r="K37" s="9" t="n"/>
       <c r="L37" s="9" t="n"/>
       <c r="M37" s="9" t="n"/>
@@ -5680,14 +5987,18 @@
       <c r="F38" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="G38" s="21" t="n">
+      <c r="G38" s="10" t="n">
         <v>1</v>
       </c>
       <c r="H38" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I38" s="9" t="n"/>
-      <c r="J38" s="9" t="n"/>
+      <c r="I38" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="J38" s="10" t="n">
+        <v>1</v>
+      </c>
       <c r="K38" s="9" t="n"/>
       <c r="L38" s="9" t="n"/>
       <c r="M38" s="9" t="n"/>
@@ -5715,14 +6026,18 @@
       <c r="F39" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="G39" s="21" t="n">
+      <c r="G39" s="10" t="n">
         <v>1</v>
       </c>
       <c r="H39" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I39" s="9" t="n"/>
-      <c r="J39" s="9" t="n"/>
+      <c r="I39" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="J39" s="10" t="n">
+        <v>1</v>
+      </c>
       <c r="K39" s="9" t="n"/>
       <c r="L39" s="9" t="n"/>
       <c r="M39" s="9" t="n"/>
@@ -5750,14 +6065,16 @@
       <c r="F40" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="G40" s="21" t="n">
+      <c r="G40" s="10" t="n">
         <v>1</v>
       </c>
       <c r="H40" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I40" s="9" t="n"/>
-      <c r="J40" s="9" t="n"/>
+      <c r="I40" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="J40" s="10" t="n"/>
       <c r="K40" s="9" t="n"/>
       <c r="L40" s="9" t="n"/>
       <c r="M40" s="9" t="n"/>
@@ -5785,14 +6102,18 @@
       <c r="F41" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="G41" s="21" t="n">
+      <c r="G41" s="10" t="n">
         <v>1</v>
       </c>
       <c r="H41" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I41" s="9" t="n"/>
-      <c r="J41" s="9" t="n"/>
+      <c r="I41" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="J41" s="10" t="n">
+        <v>1</v>
+      </c>
       <c r="K41" s="9" t="n"/>
       <c r="L41" s="9" t="n"/>
       <c r="M41" s="9" t="n"/>
@@ -5820,14 +6141,18 @@
       <c r="F42" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="G42" s="21" t="n">
+      <c r="G42" s="10" t="n">
         <v>1</v>
       </c>
       <c r="H42" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I42" s="9" t="n"/>
-      <c r="J42" s="9" t="n"/>
+      <c r="I42" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="J42" s="10" t="n">
+        <v>1</v>
+      </c>
       <c r="K42" s="9" t="n"/>
       <c r="L42" s="9" t="n"/>
       <c r="M42" s="9" t="n"/>
@@ -5855,14 +6180,18 @@
       <c r="F43" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="G43" s="21" t="n">
+      <c r="G43" s="10" t="n">
         <v>1</v>
       </c>
       <c r="H43" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I43" s="9" t="n"/>
-      <c r="J43" s="9" t="n"/>
+      <c r="I43" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="J43" s="10" t="n">
+        <v>1</v>
+      </c>
       <c r="K43" s="9" t="n"/>
       <c r="L43" s="9" t="n"/>
       <c r="M43" s="9" t="n"/>
@@ -5890,14 +6219,18 @@
       <c r="F44" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="G44" s="21" t="n">
+      <c r="G44" s="10" t="n">
         <v>1</v>
       </c>
       <c r="H44" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I44" s="9" t="n"/>
-      <c r="J44" s="9" t="n"/>
+      <c r="I44" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="J44" s="10" t="n">
+        <v>1</v>
+      </c>
       <c r="K44" s="9" t="n"/>
       <c r="L44" s="9" t="n"/>
       <c r="M44" s="9" t="n"/>
@@ -5925,14 +6258,18 @@
       <c r="F45" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="G45" s="21" t="n">
+      <c r="G45" s="10" t="n">
         <v>1</v>
       </c>
       <c r="H45" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I45" s="9" t="n"/>
-      <c r="J45" s="9" t="n"/>
+      <c r="I45" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="J45" s="10" t="n">
+        <v>1</v>
+      </c>
       <c r="K45" s="9" t="n"/>
       <c r="L45" s="9" t="n"/>
       <c r="M45" s="9" t="n"/>
@@ -5960,14 +6297,18 @@
       <c r="F46" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="G46" s="21" t="n">
+      <c r="G46" s="10" t="n">
         <v>1</v>
       </c>
       <c r="H46" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I46" s="9" t="n"/>
-      <c r="J46" s="9" t="n"/>
+      <c r="I46" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="J46" s="10" t="n">
+        <v>1</v>
+      </c>
       <c r="K46" s="9" t="n"/>
       <c r="L46" s="9" t="n"/>
       <c r="M46" s="9" t="n"/>
@@ -5995,14 +6336,18 @@
       <c r="F47" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="G47" s="21" t="n">
+      <c r="G47" s="10" t="n">
         <v>1</v>
       </c>
       <c r="H47" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I47" s="9" t="n"/>
-      <c r="J47" s="9" t="n"/>
+      <c r="I47" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="J47" s="10" t="n">
+        <v>1</v>
+      </c>
       <c r="K47" s="9" t="n"/>
       <c r="L47" s="9" t="n"/>
       <c r="M47" s="9" t="n"/>
@@ -6030,14 +6375,18 @@
       <c r="F48" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="G48" s="21" t="n">
+      <c r="G48" s="10" t="n">
         <v>1</v>
       </c>
       <c r="H48" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I48" s="9" t="n"/>
-      <c r="J48" s="9" t="n"/>
+      <c r="I48" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="J48" s="10" t="n">
+        <v>1</v>
+      </c>
       <c r="K48" s="9" t="n"/>
       <c r="L48" s="9" t="n"/>
       <c r="M48" s="9" t="n"/>
@@ -6065,14 +6414,18 @@
       <c r="F49" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="G49" s="21" t="n">
+      <c r="G49" s="10" t="n">
         <v>1</v>
       </c>
       <c r="H49" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I49" s="9" t="n"/>
-      <c r="J49" s="9" t="n"/>
+      <c r="I49" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="J49" s="10" t="n">
+        <v>1</v>
+      </c>
       <c r="K49" s="9" t="n"/>
       <c r="L49" s="9" t="n"/>
       <c r="M49" s="9" t="n"/>
@@ -6100,14 +6453,18 @@
       <c r="F50" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="G50" s="21" t="n">
+      <c r="G50" s="10" t="n">
         <v>1</v>
       </c>
       <c r="H50" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I50" s="9" t="n"/>
-      <c r="J50" s="9" t="n"/>
+      <c r="I50" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="J50" s="10" t="n">
+        <v>1</v>
+      </c>
       <c r="K50" s="9" t="n"/>
       <c r="L50" s="9" t="n"/>
       <c r="M50" s="9" t="n"/>
@@ -6135,14 +6492,18 @@
       <c r="F51" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="G51" s="21" t="n">
+      <c r="G51" s="10" t="n">
         <v>1</v>
       </c>
       <c r="H51" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I51" s="9" t="n"/>
-      <c r="J51" s="9" t="n"/>
+      <c r="I51" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="J51" s="10" t="n">
+        <v>1</v>
+      </c>
       <c r="K51" s="9" t="n"/>
       <c r="L51" s="9" t="n"/>
       <c r="M51" s="9" t="n"/>
@@ -6170,14 +6531,18 @@
       <c r="F52" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="G52" s="21" t="n">
+      <c r="G52" s="10" t="n">
         <v>1</v>
       </c>
       <c r="H52" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I52" s="9" t="n"/>
-      <c r="J52" s="9" t="n"/>
+      <c r="I52" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="J52" s="10" t="n">
+        <v>1</v>
+      </c>
       <c r="K52" s="9" t="n"/>
       <c r="L52" s="9" t="n"/>
       <c r="M52" s="9" t="n"/>
@@ -6205,14 +6570,18 @@
       <c r="F53" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="G53" s="21" t="n">
+      <c r="G53" s="10" t="n">
         <v>1</v>
       </c>
       <c r="H53" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I53" s="9" t="n"/>
-      <c r="J53" s="9" t="n"/>
+      <c r="I53" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="J53" s="10" t="n">
+        <v>1</v>
+      </c>
       <c r="K53" s="9" t="n"/>
       <c r="L53" s="9" t="n"/>
       <c r="M53" s="9" t="n"/>
@@ -6247,2204 +6616,2204 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="43" t="inlineStr">
+      <c r="A1" s="45" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B1" s="43" t="inlineStr">
+      <c r="B1" s="45" t="inlineStr">
         <is>
           <t>Student ID</t>
         </is>
       </c>
-      <c r="C1" s="43" t="inlineStr">
+      <c r="C1" s="45" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="D1" s="43" t="inlineStr">
+      <c r="D1" s="45" t="inlineStr">
         <is>
           <t>Exercise Raw</t>
         </is>
       </c>
-      <c r="E1" s="43" t="inlineStr">
+      <c r="E1" s="45" t="inlineStr">
         <is>
           <t>Exercise %</t>
         </is>
       </c>
-      <c r="F1" s="43" t="inlineStr">
+      <c r="F1" s="45" t="inlineStr">
         <is>
           <t>Exercise 70%</t>
         </is>
       </c>
-      <c r="G1" s="43" t="inlineStr">
+      <c r="G1" s="45" t="inlineStr">
         <is>
           <t>Attendance</t>
         </is>
       </c>
-      <c r="H1" s="43" t="inlineStr">
+      <c r="H1" s="45" t="inlineStr">
         <is>
           <t>Attendance %</t>
         </is>
       </c>
-      <c r="I1" s="43" t="inlineStr">
+      <c r="I1" s="45" t="inlineStr">
         <is>
           <t>Attendance 30%</t>
         </is>
       </c>
-      <c r="J1" s="43" t="inlineStr">
+      <c r="J1" s="45" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="K1" s="43" t="inlineStr">
+      <c r="K1" s="45" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="44" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="44" t="inlineStr">
+      <c r="A2" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="46" t="inlineStr">
         <is>
           <t>6610553157</t>
         </is>
       </c>
-      <c r="C2" s="45" t="inlineStr">
+      <c r="C2" s="47" t="inlineStr">
         <is>
           <t>----</t>
         </is>
       </c>
-      <c r="D2" s="44" t="inlineStr">
-        <is>
-          <t>31.00/98.00</t>
-        </is>
-      </c>
-      <c r="E2" s="46" t="n">
-        <v>31.63265306122449</v>
-      </c>
-      <c r="F2" s="46" t="n">
-        <v>22.14285714285715</v>
-      </c>
-      <c r="G2" s="44" t="inlineStr">
-        <is>
-          <t>3/5</t>
-        </is>
-      </c>
-      <c r="H2" s="46" t="n">
-        <v>60</v>
-      </c>
-      <c r="I2" s="46" t="n">
+      <c r="D2" s="46" t="inlineStr">
+        <is>
+          <t>47.00/118.00</t>
+        </is>
+      </c>
+      <c r="E2" s="48" t="n">
+        <v>39.83050847457627</v>
+      </c>
+      <c r="F2" s="48" t="n">
+        <v>27.88135593220339</v>
+      </c>
+      <c r="G2" s="46" t="inlineStr">
+        <is>
+          <t>4/7</t>
+        </is>
+      </c>
+      <c r="H2" s="48" t="n">
+        <v>57.14285714285714</v>
+      </c>
+      <c r="I2" s="48" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="J2" s="48" t="n">
+        <v>45.02421307506053</v>
+      </c>
+      <c r="K2" s="46" t="inlineStr">
+        <is>
+          <t>★☆☆☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="46" t="inlineStr">
+        <is>
+          <t>6610553165</t>
+        </is>
+      </c>
+      <c r="C3" s="47" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D3" s="46" t="inlineStr">
+        <is>
+          <t>53.00/118.00</t>
+        </is>
+      </c>
+      <c r="E3" s="48" t="n">
+        <v>44.91525423728814</v>
+      </c>
+      <c r="F3" s="48" t="n">
+        <v>31.4406779661017</v>
+      </c>
+      <c r="G3" s="46" t="inlineStr">
+        <is>
+          <t>5/7</t>
+        </is>
+      </c>
+      <c r="H3" s="48" t="n">
+        <v>71.42857142857143</v>
+      </c>
+      <c r="I3" s="48" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="J3" s="48" t="n">
+        <v>52.86924939467313</v>
+      </c>
+      <c r="K3" s="46" t="inlineStr">
+        <is>
+          <t>★☆☆☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="46" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="46" t="inlineStr">
+        <is>
+          <t>6610553173</t>
+        </is>
+      </c>
+      <c r="C4" s="47" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D4" s="46" t="inlineStr">
+        <is>
+          <t>50.00/118.00</t>
+        </is>
+      </c>
+      <c r="E4" s="48" t="n">
+        <v>42.3728813559322</v>
+      </c>
+      <c r="F4" s="48" t="n">
+        <v>29.66101694915254</v>
+      </c>
+      <c r="G4" s="46" t="inlineStr">
+        <is>
+          <t>3/7</t>
+        </is>
+      </c>
+      <c r="H4" s="48" t="n">
+        <v>42.85714285714285</v>
+      </c>
+      <c r="I4" s="48" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="J4" s="48" t="n">
+        <v>42.51815980629539</v>
+      </c>
+      <c r="K4" s="46" t="inlineStr">
+        <is>
+          <t>★☆☆☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="46" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="46" t="inlineStr">
+        <is>
+          <t>6610553181</t>
+        </is>
+      </c>
+      <c r="C5" s="47" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D5" s="46" t="inlineStr">
+        <is>
+          <t>78.00/118.00</t>
+        </is>
+      </c>
+      <c r="E5" s="48" t="n">
+        <v>66.10169491525424</v>
+      </c>
+      <c r="F5" s="48" t="n">
+        <v>46.27118644067797</v>
+      </c>
+      <c r="G5" s="46" t="inlineStr">
+        <is>
+          <t>7/7</t>
+        </is>
+      </c>
+      <c r="H5" s="48" t="n">
+        <v>100</v>
+      </c>
+      <c r="I5" s="48" t="n">
+        <v>30</v>
+      </c>
+      <c r="J5" s="48" t="n">
+        <v>76.27118644067797</v>
+      </c>
+      <c r="K5" s="46" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="46" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="46" t="inlineStr">
+        <is>
+          <t>6610553203</t>
+        </is>
+      </c>
+      <c r="C6" s="47" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D6" s="46" t="inlineStr">
+        <is>
+          <t>61.00/118.00</t>
+        </is>
+      </c>
+      <c r="E6" s="48" t="n">
+        <v>51.69491525423729</v>
+      </c>
+      <c r="F6" s="48" t="n">
+        <v>36.1864406779661</v>
+      </c>
+      <c r="G6" s="46" t="inlineStr">
+        <is>
+          <t>7/7</t>
+        </is>
+      </c>
+      <c r="H6" s="48" t="n">
+        <v>100</v>
+      </c>
+      <c r="I6" s="48" t="n">
+        <v>30</v>
+      </c>
+      <c r="J6" s="48" t="n">
+        <v>66.18644067796609</v>
+      </c>
+      <c r="K6" s="46" t="inlineStr">
+        <is>
+          <t>★★☆☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="46" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="46" t="inlineStr">
+        <is>
+          <t>6610553220</t>
+        </is>
+      </c>
+      <c r="C7" s="47" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D7" s="46" t="inlineStr">
+        <is>
+          <t>29.00/118.00</t>
+        </is>
+      </c>
+      <c r="E7" s="48" t="n">
+        <v>24.57627118644068</v>
+      </c>
+      <c r="F7" s="48" t="n">
+        <v>17.20338983050847</v>
+      </c>
+      <c r="G7" s="46" t="inlineStr">
+        <is>
+          <t>5/7</t>
+        </is>
+      </c>
+      <c r="H7" s="48" t="n">
+        <v>71.42857142857143</v>
+      </c>
+      <c r="I7" s="48" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="J7" s="48" t="n">
+        <v>38.6319612590799</v>
+      </c>
+      <c r="K7" s="46" t="inlineStr">
+        <is>
+          <t>★☆☆☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="46" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="46" t="inlineStr">
+        <is>
+          <t>6610553238</t>
+        </is>
+      </c>
+      <c r="C8" s="47" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D8" s="46" t="inlineStr">
+        <is>
+          <t>46.00/118.00</t>
+        </is>
+      </c>
+      <c r="E8" s="48" t="n">
+        <v>38.98305084745763</v>
+      </c>
+      <c r="F8" s="48" t="n">
+        <v>27.28813559322034</v>
+      </c>
+      <c r="G8" s="46" t="inlineStr">
+        <is>
+          <t>5/7</t>
+        </is>
+      </c>
+      <c r="H8" s="48" t="n">
+        <v>71.42857142857143</v>
+      </c>
+      <c r="I8" s="48" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="J8" s="48" t="n">
+        <v>48.71670702179177</v>
+      </c>
+      <c r="K8" s="46" t="inlineStr">
+        <is>
+          <t>★☆☆☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="46" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="46" t="inlineStr">
+        <is>
+          <t>6610553254</t>
+        </is>
+      </c>
+      <c r="C9" s="47" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D9" s="46" t="inlineStr">
+        <is>
+          <t>75.00/118.00</t>
+        </is>
+      </c>
+      <c r="E9" s="48" t="n">
+        <v>63.5593220338983</v>
+      </c>
+      <c r="F9" s="48" t="n">
+        <v>44.49152542372881</v>
+      </c>
+      <c r="G9" s="46" t="inlineStr">
+        <is>
+          <t>7/7</t>
+        </is>
+      </c>
+      <c r="H9" s="48" t="n">
+        <v>100</v>
+      </c>
+      <c r="I9" s="48" t="n">
+        <v>30</v>
+      </c>
+      <c r="J9" s="48" t="n">
+        <v>74.4915254237288</v>
+      </c>
+      <c r="K9" s="46" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="46" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="46" t="inlineStr">
+        <is>
+          <t>6610553262</t>
+        </is>
+      </c>
+      <c r="C10" s="47" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D10" s="46" t="inlineStr">
+        <is>
+          <t>62.00/118.00</t>
+        </is>
+      </c>
+      <c r="E10" s="48" t="n">
+        <v>52.54237288135594</v>
+      </c>
+      <c r="F10" s="48" t="n">
+        <v>36.77966101694916</v>
+      </c>
+      <c r="G10" s="46" t="inlineStr">
+        <is>
+          <t>7/7</t>
+        </is>
+      </c>
+      <c r="H10" s="48" t="n">
+        <v>100</v>
+      </c>
+      <c r="I10" s="48" t="n">
+        <v>30</v>
+      </c>
+      <c r="J10" s="48" t="n">
+        <v>66.77966101694915</v>
+      </c>
+      <c r="K10" s="46" t="inlineStr">
+        <is>
+          <t>★★☆☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="46" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="46" t="inlineStr">
+        <is>
+          <t>6610553271</t>
+        </is>
+      </c>
+      <c r="C11" s="47" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D11" s="46" t="inlineStr">
+        <is>
+          <t>80.00/118.00</t>
+        </is>
+      </c>
+      <c r="E11" s="48" t="n">
+        <v>67.79661016949152</v>
+      </c>
+      <c r="F11" s="48" t="n">
+        <v>47.45762711864407</v>
+      </c>
+      <c r="G11" s="46" t="inlineStr">
+        <is>
+          <t>7/7</t>
+        </is>
+      </c>
+      <c r="H11" s="48" t="n">
+        <v>100</v>
+      </c>
+      <c r="I11" s="48" t="n">
+        <v>30</v>
+      </c>
+      <c r="J11" s="48" t="n">
+        <v>77.45762711864407</v>
+      </c>
+      <c r="K11" s="46" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="46" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="46" t="inlineStr">
+        <is>
+          <t>6610553289</t>
+        </is>
+      </c>
+      <c r="C12" s="47" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D12" s="46" t="inlineStr">
+        <is>
+          <t>57.00/118.00</t>
+        </is>
+      </c>
+      <c r="E12" s="48" t="n">
+        <v>48.30508474576271</v>
+      </c>
+      <c r="F12" s="48" t="n">
+        <v>33.8135593220339</v>
+      </c>
+      <c r="G12" s="46" t="inlineStr">
+        <is>
+          <t>6/7</t>
+        </is>
+      </c>
+      <c r="H12" s="48" t="n">
+        <v>85.71428571428571</v>
+      </c>
+      <c r="I12" s="48" t="n">
+        <v>25.71428571428571</v>
+      </c>
+      <c r="J12" s="48" t="n">
+        <v>59.5278450363196</v>
+      </c>
+      <c r="K12" s="46" t="inlineStr">
+        <is>
+          <t>★☆☆☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="46" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="46" t="inlineStr">
+        <is>
+          <t>6610553327</t>
+        </is>
+      </c>
+      <c r="C13" s="47" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D13" s="46" t="inlineStr">
+        <is>
+          <t>34.00/118.00</t>
+        </is>
+      </c>
+      <c r="E13" s="48" t="n">
+        <v>28.8135593220339</v>
+      </c>
+      <c r="F13" s="48" t="n">
+        <v>20.16949152542373</v>
+      </c>
+      <c r="G13" s="46" t="inlineStr">
+        <is>
+          <t>5/7</t>
+        </is>
+      </c>
+      <c r="H13" s="48" t="n">
+        <v>71.42857142857143</v>
+      </c>
+      <c r="I13" s="48" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="J13" s="48" t="n">
+        <v>41.59806295399516</v>
+      </c>
+      <c r="K13" s="46" t="inlineStr">
+        <is>
+          <t>★☆☆☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="46" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="46" t="inlineStr">
+        <is>
+          <t>6610554153</t>
+        </is>
+      </c>
+      <c r="C14" s="47" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D14" s="46" t="inlineStr">
+        <is>
+          <t>64.00/118.00</t>
+        </is>
+      </c>
+      <c r="E14" s="48" t="n">
+        <v>54.23728813559322</v>
+      </c>
+      <c r="F14" s="48" t="n">
+        <v>37.96610169491525</v>
+      </c>
+      <c r="G14" s="46" t="inlineStr">
+        <is>
+          <t>5/7</t>
+        </is>
+      </c>
+      <c r="H14" s="48" t="n">
+        <v>71.42857142857143</v>
+      </c>
+      <c r="I14" s="48" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="J14" s="48" t="n">
+        <v>59.39467312348668</v>
+      </c>
+      <c r="K14" s="46" t="inlineStr">
+        <is>
+          <t>★☆☆☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="46" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="46" t="inlineStr">
+        <is>
+          <t>6610554161</t>
+        </is>
+      </c>
+      <c r="C15" s="47" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D15" s="46" t="inlineStr">
+        <is>
+          <t>54.00/118.00</t>
+        </is>
+      </c>
+      <c r="E15" s="48" t="n">
+        <v>45.76271186440678</v>
+      </c>
+      <c r="F15" s="48" t="n">
+        <v>32.03389830508475</v>
+      </c>
+      <c r="G15" s="46" t="inlineStr">
+        <is>
+          <t>3/7</t>
+        </is>
+      </c>
+      <c r="H15" s="48" t="n">
+        <v>42.85714285714285</v>
+      </c>
+      <c r="I15" s="48" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="J15" s="48" t="n">
+        <v>44.8910411622276</v>
+      </c>
+      <c r="K15" s="46" t="inlineStr">
+        <is>
+          <t>★☆☆☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="46" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="46" t="inlineStr">
+        <is>
+          <t>6710552942</t>
+        </is>
+      </c>
+      <c r="C16" s="47" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D16" s="46" t="inlineStr">
+        <is>
+          <t>65.00/118.00</t>
+        </is>
+      </c>
+      <c r="E16" s="48" t="n">
+        <v>55.08474576271186</v>
+      </c>
+      <c r="F16" s="48" t="n">
+        <v>38.5593220338983</v>
+      </c>
+      <c r="G16" s="46" t="inlineStr">
+        <is>
+          <t>6/7</t>
+        </is>
+      </c>
+      <c r="H16" s="48" t="n">
+        <v>85.71428571428571</v>
+      </c>
+      <c r="I16" s="48" t="n">
+        <v>25.71428571428571</v>
+      </c>
+      <c r="J16" s="48" t="n">
+        <v>64.27360774818402</v>
+      </c>
+      <c r="K16" s="46" t="inlineStr">
+        <is>
+          <t>★★☆☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="46" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="46" t="inlineStr">
+        <is>
+          <t>6710552951</t>
+        </is>
+      </c>
+      <c r="C17" s="47" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D17" s="46" t="inlineStr">
+        <is>
+          <t>101.00/118.00</t>
+        </is>
+      </c>
+      <c r="E17" s="48" t="n">
+        <v>85.59322033898306</v>
+      </c>
+      <c r="F17" s="48" t="n">
+        <v>59.91525423728814</v>
+      </c>
+      <c r="G17" s="46" t="inlineStr">
+        <is>
+          <t>7/7</t>
+        </is>
+      </c>
+      <c r="H17" s="48" t="n">
+        <v>100</v>
+      </c>
+      <c r="I17" s="48" t="n">
+        <v>30</v>
+      </c>
+      <c r="J17" s="48" t="n">
+        <v>89.91525423728814</v>
+      </c>
+      <c r="K17" s="46" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="46" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="46" t="inlineStr">
+        <is>
+          <t>6710552969</t>
+        </is>
+      </c>
+      <c r="C18" s="47" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D18" s="46" t="inlineStr">
+        <is>
+          <t>100.00/118.00</t>
+        </is>
+      </c>
+      <c r="E18" s="48" t="n">
+        <v>84.7457627118644</v>
+      </c>
+      <c r="F18" s="48" t="n">
+        <v>59.32203389830508</v>
+      </c>
+      <c r="G18" s="46" t="inlineStr">
+        <is>
+          <t>7/7</t>
+        </is>
+      </c>
+      <c r="H18" s="48" t="n">
+        <v>100</v>
+      </c>
+      <c r="I18" s="48" t="n">
+        <v>30</v>
+      </c>
+      <c r="J18" s="48" t="n">
+        <v>89.32203389830508</v>
+      </c>
+      <c r="K18" s="46" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="46" t="n">
         <v>18</v>
       </c>
-      <c r="J2" s="46" t="n">
-        <v>40.14285714285715</v>
-      </c>
-      <c r="K2" s="44" t="inlineStr">
+      <c r="B19" s="46" t="inlineStr">
+        <is>
+          <t>6710552977</t>
+        </is>
+      </c>
+      <c r="C19" s="47" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D19" s="46" t="inlineStr">
+        <is>
+          <t>74.00/118.00</t>
+        </is>
+      </c>
+      <c r="E19" s="48" t="n">
+        <v>62.71186440677966</v>
+      </c>
+      <c r="F19" s="48" t="n">
+        <v>43.89830508474576</v>
+      </c>
+      <c r="G19" s="46" t="inlineStr">
+        <is>
+          <t>7/7</t>
+        </is>
+      </c>
+      <c r="H19" s="48" t="n">
+        <v>100</v>
+      </c>
+      <c r="I19" s="48" t="n">
+        <v>30</v>
+      </c>
+      <c r="J19" s="48" t="n">
+        <v>73.89830508474577</v>
+      </c>
+      <c r="K19" s="46" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="46" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="46" t="inlineStr">
+        <is>
+          <t>6710552985</t>
+        </is>
+      </c>
+      <c r="C20" s="47" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D20" s="46" t="inlineStr">
+        <is>
+          <t>84.00/118.00</t>
+        </is>
+      </c>
+      <c r="E20" s="48" t="n">
+        <v>71.1864406779661</v>
+      </c>
+      <c r="F20" s="48" t="n">
+        <v>49.83050847457627</v>
+      </c>
+      <c r="G20" s="46" t="inlineStr">
+        <is>
+          <t>7/7</t>
+        </is>
+      </c>
+      <c r="H20" s="48" t="n">
+        <v>100</v>
+      </c>
+      <c r="I20" s="48" t="n">
+        <v>30</v>
+      </c>
+      <c r="J20" s="48" t="n">
+        <v>79.83050847457628</v>
+      </c>
+      <c r="K20" s="46" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="46" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="46" t="inlineStr">
+        <is>
+          <t>6710552993</t>
+        </is>
+      </c>
+      <c r="C21" s="47" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D21" s="46" t="inlineStr">
+        <is>
+          <t>71.00/118.00</t>
+        </is>
+      </c>
+      <c r="E21" s="48" t="n">
+        <v>60.16949152542372</v>
+      </c>
+      <c r="F21" s="48" t="n">
+        <v>42.11864406779661</v>
+      </c>
+      <c r="G21" s="46" t="inlineStr">
+        <is>
+          <t>6/7</t>
+        </is>
+      </c>
+      <c r="H21" s="48" t="n">
+        <v>85.71428571428571</v>
+      </c>
+      <c r="I21" s="48" t="n">
+        <v>25.71428571428571</v>
+      </c>
+      <c r="J21" s="48" t="n">
+        <v>67.83292978208232</v>
+      </c>
+      <c r="K21" s="46" t="inlineStr">
+        <is>
+          <t>★★☆☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="46" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="46" t="inlineStr">
+        <is>
+          <t>6710553001</t>
+        </is>
+      </c>
+      <c r="C22" s="47" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D22" s="46" t="inlineStr">
+        <is>
+          <t>46.00/118.00</t>
+        </is>
+      </c>
+      <c r="E22" s="48" t="n">
+        <v>38.98305084745763</v>
+      </c>
+      <c r="F22" s="48" t="n">
+        <v>27.28813559322034</v>
+      </c>
+      <c r="G22" s="46" t="inlineStr">
+        <is>
+          <t>4/7</t>
+        </is>
+      </c>
+      <c r="H22" s="48" t="n">
+        <v>57.14285714285714</v>
+      </c>
+      <c r="I22" s="48" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="J22" s="48" t="n">
+        <v>44.43099273607749</v>
+      </c>
+      <c r="K22" s="46" t="inlineStr">
         <is>
           <t>★☆☆☆☆</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="44" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="44" t="inlineStr">
-        <is>
-          <t>6610553165</t>
-        </is>
-      </c>
-      <c r="C3" s="45" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="46" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="46" t="inlineStr">
+        <is>
+          <t>6710553027</t>
+        </is>
+      </c>
+      <c r="C23" s="47" t="inlineStr">
         <is>
           <t>----</t>
         </is>
       </c>
-      <c r="D3" s="44" t="inlineStr">
-        <is>
-          <t>37.00/98.00</t>
-        </is>
-      </c>
-      <c r="E3" s="46" t="n">
-        <v>37.75510204081633</v>
-      </c>
-      <c r="F3" s="46" t="n">
-        <v>26.42857142857143</v>
-      </c>
-      <c r="G3" s="44" t="inlineStr">
-        <is>
-          <t>3/5</t>
-        </is>
-      </c>
-      <c r="H3" s="46" t="n">
-        <v>60</v>
-      </c>
-      <c r="I3" s="46" t="n">
-        <v>18</v>
-      </c>
-      <c r="J3" s="46" t="n">
-        <v>44.42857142857143</v>
-      </c>
-      <c r="K3" s="44" t="inlineStr">
+      <c r="D23" s="46" t="inlineStr">
+        <is>
+          <t>93.00/118.00</t>
+        </is>
+      </c>
+      <c r="E23" s="48" t="n">
+        <v>78.8135593220339</v>
+      </c>
+      <c r="F23" s="48" t="n">
+        <v>55.16949152542373</v>
+      </c>
+      <c r="G23" s="46" t="inlineStr">
+        <is>
+          <t>7/7</t>
+        </is>
+      </c>
+      <c r="H23" s="48" t="n">
+        <v>100</v>
+      </c>
+      <c r="I23" s="48" t="n">
+        <v>30</v>
+      </c>
+      <c r="J23" s="48" t="n">
+        <v>85.16949152542372</v>
+      </c>
+      <c r="K23" s="46" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="46" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="46" t="inlineStr">
+        <is>
+          <t>6710553035</t>
+        </is>
+      </c>
+      <c r="C24" s="47" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D24" s="46" t="inlineStr">
+        <is>
+          <t>101.00/118.00</t>
+        </is>
+      </c>
+      <c r="E24" s="48" t="n">
+        <v>85.59322033898306</v>
+      </c>
+      <c r="F24" s="48" t="n">
+        <v>59.91525423728814</v>
+      </c>
+      <c r="G24" s="46" t="inlineStr">
+        <is>
+          <t>7/7</t>
+        </is>
+      </c>
+      <c r="H24" s="48" t="n">
+        <v>100</v>
+      </c>
+      <c r="I24" s="48" t="n">
+        <v>30</v>
+      </c>
+      <c r="J24" s="48" t="n">
+        <v>89.91525423728814</v>
+      </c>
+      <c r="K24" s="46" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="46" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="46" t="inlineStr">
+        <is>
+          <t>6710553051</t>
+        </is>
+      </c>
+      <c r="C25" s="47" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D25" s="46" t="inlineStr">
+        <is>
+          <t>0.00/118.00</t>
+        </is>
+      </c>
+      <c r="E25" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="46" t="inlineStr">
+        <is>
+          <t>0/7</t>
+        </is>
+      </c>
+      <c r="H25" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" s="46" t="inlineStr">
         <is>
           <t>★☆☆☆☆</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="44" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="44" t="inlineStr">
-        <is>
-          <t>6610553173</t>
-        </is>
-      </c>
-      <c r="C4" s="45" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="46" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="46" t="inlineStr">
+        <is>
+          <t>6710553078</t>
+        </is>
+      </c>
+      <c r="C26" s="47" t="inlineStr">
         <is>
           <t>----</t>
         </is>
       </c>
-      <c r="D4" s="44" t="inlineStr">
-        <is>
-          <t>30.00/98.00</t>
-        </is>
-      </c>
-      <c r="E4" s="46" t="n">
-        <v>30.61224489795918</v>
-      </c>
-      <c r="F4" s="46" t="n">
-        <v>21.42857142857143</v>
-      </c>
-      <c r="G4" s="44" t="inlineStr">
-        <is>
-          <t>2/5</t>
-        </is>
-      </c>
-      <c r="H4" s="46" t="n">
+      <c r="D26" s="46" t="inlineStr">
+        <is>
+          <t>94.00/118.00</t>
+        </is>
+      </c>
+      <c r="E26" s="48" t="n">
+        <v>79.66101694915254</v>
+      </c>
+      <c r="F26" s="48" t="n">
+        <v>55.76271186440678</v>
+      </c>
+      <c r="G26" s="46" t="inlineStr">
+        <is>
+          <t>7/7</t>
+        </is>
+      </c>
+      <c r="H26" s="48" t="n">
+        <v>100</v>
+      </c>
+      <c r="I26" s="48" t="n">
+        <v>30</v>
+      </c>
+      <c r="J26" s="48" t="n">
+        <v>85.76271186440678</v>
+      </c>
+      <c r="K26" s="46" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="46" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="46" t="inlineStr">
+        <is>
+          <t>6710553086</t>
+        </is>
+      </c>
+      <c r="C27" s="47" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D27" s="46" t="inlineStr">
+        <is>
+          <t>68.00/118.00</t>
+        </is>
+      </c>
+      <c r="E27" s="48" t="n">
+        <v>57.6271186440678</v>
+      </c>
+      <c r="F27" s="48" t="n">
+        <v>40.33898305084746</v>
+      </c>
+      <c r="G27" s="46" t="inlineStr">
+        <is>
+          <t>6/7</t>
+        </is>
+      </c>
+      <c r="H27" s="48" t="n">
+        <v>85.71428571428571</v>
+      </c>
+      <c r="I27" s="48" t="n">
+        <v>25.71428571428571</v>
+      </c>
+      <c r="J27" s="48" t="n">
+        <v>66.05326876513317</v>
+      </c>
+      <c r="K27" s="46" t="inlineStr">
+        <is>
+          <t>★★☆☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="46" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="46" t="inlineStr">
+        <is>
+          <t>6710553094</t>
+        </is>
+      </c>
+      <c r="C28" s="47" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D28" s="46" t="inlineStr">
+        <is>
+          <t>112.00/118.00</t>
+        </is>
+      </c>
+      <c r="E28" s="48" t="n">
+        <v>94.91525423728814</v>
+      </c>
+      <c r="F28" s="48" t="n">
+        <v>66.4406779661017</v>
+      </c>
+      <c r="G28" s="46" t="inlineStr">
+        <is>
+          <t>7/7</t>
+        </is>
+      </c>
+      <c r="H28" s="48" t="n">
+        <v>100</v>
+      </c>
+      <c r="I28" s="48" t="n">
+        <v>30</v>
+      </c>
+      <c r="J28" s="48" t="n">
+        <v>96.4406779661017</v>
+      </c>
+      <c r="K28" s="46" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="46" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="46" t="inlineStr">
+        <is>
+          <t>6710553108</t>
+        </is>
+      </c>
+      <c r="C29" s="47" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D29" s="46" t="inlineStr">
+        <is>
+          <t>98.00/118.00</t>
+        </is>
+      </c>
+      <c r="E29" s="48" t="n">
+        <v>83.05084745762711</v>
+      </c>
+      <c r="F29" s="48" t="n">
+        <v>58.13559322033898</v>
+      </c>
+      <c r="G29" s="46" t="inlineStr">
+        <is>
+          <t>7/7</t>
+        </is>
+      </c>
+      <c r="H29" s="48" t="n">
+        <v>100</v>
+      </c>
+      <c r="I29" s="48" t="n">
+        <v>30</v>
+      </c>
+      <c r="J29" s="48" t="n">
+        <v>88.13559322033899</v>
+      </c>
+      <c r="K29" s="46" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="46" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="46" t="inlineStr">
+        <is>
+          <t>6710553124</t>
+        </is>
+      </c>
+      <c r="C30" s="47" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D30" s="46" t="inlineStr">
+        <is>
+          <t>88.00/118.00</t>
+        </is>
+      </c>
+      <c r="E30" s="48" t="n">
+        <v>74.57627118644068</v>
+      </c>
+      <c r="F30" s="48" t="n">
+        <v>52.20338983050848</v>
+      </c>
+      <c r="G30" s="46" t="inlineStr">
+        <is>
+          <t>6/7</t>
+        </is>
+      </c>
+      <c r="H30" s="48" t="n">
+        <v>85.71428571428571</v>
+      </c>
+      <c r="I30" s="48" t="n">
+        <v>25.71428571428571</v>
+      </c>
+      <c r="J30" s="48" t="n">
+        <v>77.91767554479419</v>
+      </c>
+      <c r="K30" s="46" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="46" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="46" t="inlineStr">
+        <is>
+          <t>6710553141</t>
+        </is>
+      </c>
+      <c r="C31" s="47" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D31" s="46" t="inlineStr">
+        <is>
+          <t>98.00/118.00</t>
+        </is>
+      </c>
+      <c r="E31" s="48" t="n">
+        <v>83.05084745762711</v>
+      </c>
+      <c r="F31" s="48" t="n">
+        <v>58.13559322033898</v>
+      </c>
+      <c r="G31" s="46" t="inlineStr">
+        <is>
+          <t>7/7</t>
+        </is>
+      </c>
+      <c r="H31" s="48" t="n">
+        <v>100</v>
+      </c>
+      <c r="I31" s="48" t="n">
+        <v>30</v>
+      </c>
+      <c r="J31" s="48" t="n">
+        <v>88.13559322033899</v>
+      </c>
+      <c r="K31" s="46" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="46" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="46" t="inlineStr">
+        <is>
+          <t>6710553167</t>
+        </is>
+      </c>
+      <c r="C32" s="47" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D32" s="46" t="inlineStr">
+        <is>
+          <t>76.00/118.00</t>
+        </is>
+      </c>
+      <c r="E32" s="48" t="n">
+        <v>64.40677966101694</v>
+      </c>
+      <c r="F32" s="48" t="n">
+        <v>45.08474576271186</v>
+      </c>
+      <c r="G32" s="46" t="inlineStr">
+        <is>
+          <t>6/7</t>
+        </is>
+      </c>
+      <c r="H32" s="48" t="n">
+        <v>85.71428571428571</v>
+      </c>
+      <c r="I32" s="48" t="n">
+        <v>25.71428571428571</v>
+      </c>
+      <c r="J32" s="48" t="n">
+        <v>70.79903147699757</v>
+      </c>
+      <c r="K32" s="46" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="46" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="46" t="inlineStr">
+        <is>
+          <t>6710553191</t>
+        </is>
+      </c>
+      <c r="C33" s="47" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D33" s="46" t="inlineStr">
+        <is>
+          <t>114.00/118.00</t>
+        </is>
+      </c>
+      <c r="E33" s="48" t="n">
+        <v>96.61016949152543</v>
+      </c>
+      <c r="F33" s="48" t="n">
+        <v>67.62711864406779</v>
+      </c>
+      <c r="G33" s="46" t="inlineStr">
+        <is>
+          <t>7/7</t>
+        </is>
+      </c>
+      <c r="H33" s="48" t="n">
+        <v>100</v>
+      </c>
+      <c r="I33" s="48" t="n">
+        <v>30</v>
+      </c>
+      <c r="J33" s="48" t="n">
+        <v>97.62711864406779</v>
+      </c>
+      <c r="K33" s="46" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="46" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="46" t="inlineStr">
+        <is>
+          <t>6710553205</t>
+        </is>
+      </c>
+      <c r="C34" s="47" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D34" s="46" t="inlineStr">
+        <is>
+          <t>96.00/118.00</t>
+        </is>
+      </c>
+      <c r="E34" s="48" t="n">
+        <v>81.35593220338984</v>
+      </c>
+      <c r="F34" s="48" t="n">
+        <v>56.94915254237289</v>
+      </c>
+      <c r="G34" s="46" t="inlineStr">
+        <is>
+          <t>6/7</t>
+        </is>
+      </c>
+      <c r="H34" s="48" t="n">
+        <v>85.71428571428571</v>
+      </c>
+      <c r="I34" s="48" t="n">
+        <v>25.71428571428571</v>
+      </c>
+      <c r="J34" s="48" t="n">
+        <v>82.66343825665859</v>
+      </c>
+      <c r="K34" s="46" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="46" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="46" t="inlineStr">
+        <is>
+          <t>6710553213</t>
+        </is>
+      </c>
+      <c r="C35" s="47" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D35" s="46" t="inlineStr">
+        <is>
+          <t>87.00/118.00</t>
+        </is>
+      </c>
+      <c r="E35" s="48" t="n">
+        <v>73.72881355932203</v>
+      </c>
+      <c r="F35" s="48" t="n">
+        <v>51.61016949152543</v>
+      </c>
+      <c r="G35" s="46" t="inlineStr">
+        <is>
+          <t>7/7</t>
+        </is>
+      </c>
+      <c r="H35" s="48" t="n">
+        <v>100</v>
+      </c>
+      <c r="I35" s="48" t="n">
+        <v>30</v>
+      </c>
+      <c r="J35" s="48" t="n">
+        <v>81.61016949152543</v>
+      </c>
+      <c r="K35" s="46" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="46" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="46" t="inlineStr">
+        <is>
+          <t>6710553264</t>
+        </is>
+      </c>
+      <c r="C36" s="47" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D36" s="46" t="inlineStr">
+        <is>
+          <t>62.00/118.00</t>
+        </is>
+      </c>
+      <c r="E36" s="48" t="n">
+        <v>52.54237288135594</v>
+      </c>
+      <c r="F36" s="48" t="n">
+        <v>36.77966101694916</v>
+      </c>
+      <c r="G36" s="46" t="inlineStr">
+        <is>
+          <t>7/7</t>
+        </is>
+      </c>
+      <c r="H36" s="48" t="n">
+        <v>100</v>
+      </c>
+      <c r="I36" s="48" t="n">
+        <v>30</v>
+      </c>
+      <c r="J36" s="48" t="n">
+        <v>66.77966101694915</v>
+      </c>
+      <c r="K36" s="46" t="inlineStr">
+        <is>
+          <t>★★☆☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="46" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="46" t="inlineStr">
+        <is>
+          <t>6710553272</t>
+        </is>
+      </c>
+      <c r="C37" s="47" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D37" s="46" t="inlineStr">
+        <is>
+          <t>66.00/118.00</t>
+        </is>
+      </c>
+      <c r="E37" s="48" t="n">
+        <v>55.93220338983051</v>
+      </c>
+      <c r="F37" s="48" t="n">
+        <v>39.15254237288135</v>
+      </c>
+      <c r="G37" s="46" t="inlineStr">
+        <is>
+          <t>7/7</t>
+        </is>
+      </c>
+      <c r="H37" s="48" t="n">
+        <v>100</v>
+      </c>
+      <c r="I37" s="48" t="n">
+        <v>30</v>
+      </c>
+      <c r="J37" s="48" t="n">
+        <v>69.15254237288136</v>
+      </c>
+      <c r="K37" s="46" t="inlineStr">
+        <is>
+          <t>★★☆☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="46" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="46" t="inlineStr">
+        <is>
+          <t>6710553281</t>
+        </is>
+      </c>
+      <c r="C38" s="47" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D38" s="46" t="inlineStr">
+        <is>
+          <t>78.00/118.00</t>
+        </is>
+      </c>
+      <c r="E38" s="48" t="n">
+        <v>66.10169491525424</v>
+      </c>
+      <c r="F38" s="48" t="n">
+        <v>46.27118644067797</v>
+      </c>
+      <c r="G38" s="46" t="inlineStr">
+        <is>
+          <t>7/7</t>
+        </is>
+      </c>
+      <c r="H38" s="48" t="n">
+        <v>100</v>
+      </c>
+      <c r="I38" s="48" t="n">
+        <v>30</v>
+      </c>
+      <c r="J38" s="48" t="n">
+        <v>76.27118644067797</v>
+      </c>
+      <c r="K38" s="46" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="46" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="46" t="inlineStr">
+        <is>
+          <t>6710553299</t>
+        </is>
+      </c>
+      <c r="C39" s="47" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D39" s="46" t="inlineStr">
+        <is>
+          <t>104.00/118.00</t>
+        </is>
+      </c>
+      <c r="E39" s="48" t="n">
+        <v>88.13559322033898</v>
+      </c>
+      <c r="F39" s="48" t="n">
+        <v>61.69491525423729</v>
+      </c>
+      <c r="G39" s="46" t="inlineStr">
+        <is>
+          <t>7/7</t>
+        </is>
+      </c>
+      <c r="H39" s="48" t="n">
+        <v>100</v>
+      </c>
+      <c r="I39" s="48" t="n">
+        <v>30</v>
+      </c>
+      <c r="J39" s="48" t="n">
+        <v>91.69491525423729</v>
+      </c>
+      <c r="K39" s="46" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="46" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="46" t="inlineStr">
+        <is>
+          <t>6710553329</t>
+        </is>
+      </c>
+      <c r="C40" s="47" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D40" s="46" t="inlineStr">
+        <is>
+          <t>86.00/118.00</t>
+        </is>
+      </c>
+      <c r="E40" s="48" t="n">
+        <v>72.88135593220339</v>
+      </c>
+      <c r="F40" s="48" t="n">
+        <v>51.01694915254237</v>
+      </c>
+      <c r="G40" s="46" t="inlineStr">
+        <is>
+          <t>7/7</t>
+        </is>
+      </c>
+      <c r="H40" s="48" t="n">
+        <v>100</v>
+      </c>
+      <c r="I40" s="48" t="n">
+        <v>30</v>
+      </c>
+      <c r="J40" s="48" t="n">
+        <v>81.01694915254237</v>
+      </c>
+      <c r="K40" s="46" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="46" t="n">
         <v>40</v>
       </c>
-      <c r="I4" s="46" t="n">
-        <v>12</v>
-      </c>
-      <c r="J4" s="46" t="n">
-        <v>33.42857142857143</v>
-      </c>
-      <c r="K4" s="44" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="44" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="44" t="inlineStr">
-        <is>
-          <t>6610553181</t>
-        </is>
-      </c>
-      <c r="C5" s="45" t="inlineStr">
+      <c r="B41" s="46" t="inlineStr">
+        <is>
+          <t>6710553337</t>
+        </is>
+      </c>
+      <c r="C41" s="47" t="inlineStr">
         <is>
           <t>----</t>
         </is>
       </c>
-      <c r="D5" s="44" t="inlineStr">
-        <is>
-          <t>64.00/98.00</t>
-        </is>
-      </c>
-      <c r="E5" s="46" t="n">
-        <v>65.30612244897959</v>
-      </c>
-      <c r="F5" s="46" t="n">
-        <v>45.71428571428571</v>
-      </c>
-      <c r="G5" s="44" t="inlineStr">
-        <is>
-          <t>5/5</t>
-        </is>
-      </c>
-      <c r="H5" s="46" t="n">
+      <c r="D41" s="46" t="inlineStr">
+        <is>
+          <t>94.00/118.00</t>
+        </is>
+      </c>
+      <c r="E41" s="48" t="n">
+        <v>79.66101694915254</v>
+      </c>
+      <c r="F41" s="48" t="n">
+        <v>55.76271186440678</v>
+      </c>
+      <c r="G41" s="46" t="inlineStr">
+        <is>
+          <t>7/7</t>
+        </is>
+      </c>
+      <c r="H41" s="48" t="n">
         <v>100</v>
       </c>
-      <c r="I5" s="46" t="n">
+      <c r="I41" s="48" t="n">
         <v>30</v>
       </c>
-      <c r="J5" s="46" t="n">
-        <v>75.71428571428571</v>
-      </c>
-      <c r="K5" s="44" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="44" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="44" t="inlineStr">
-        <is>
-          <t>6610553203</t>
-        </is>
-      </c>
-      <c r="C6" s="45" t="inlineStr">
+      <c r="J41" s="48" t="n">
+        <v>85.76271186440678</v>
+      </c>
+      <c r="K41" s="46" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="46" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="46" t="inlineStr">
+        <is>
+          <t>6710553345</t>
+        </is>
+      </c>
+      <c r="C42" s="47" t="inlineStr">
         <is>
           <t>----</t>
         </is>
       </c>
-      <c r="D6" s="44" t="inlineStr">
-        <is>
-          <t>46.00/98.00</t>
-        </is>
-      </c>
-      <c r="E6" s="46" t="n">
-        <v>46.93877551020408</v>
-      </c>
-      <c r="F6" s="46" t="n">
-        <v>32.85714285714286</v>
-      </c>
-      <c r="G6" s="44" t="inlineStr">
-        <is>
-          <t>5/5</t>
-        </is>
-      </c>
-      <c r="H6" s="46" t="n">
+      <c r="D42" s="46" t="inlineStr">
+        <is>
+          <t>90.00/118.00</t>
+        </is>
+      </c>
+      <c r="E42" s="48" t="n">
+        <v>76.27118644067797</v>
+      </c>
+      <c r="F42" s="48" t="n">
+        <v>53.38983050847457</v>
+      </c>
+      <c r="G42" s="46" t="inlineStr">
+        <is>
+          <t>7/7</t>
+        </is>
+      </c>
+      <c r="H42" s="48" t="n">
         <v>100</v>
       </c>
-      <c r="I6" s="46" t="n">
+      <c r="I42" s="48" t="n">
         <v>30</v>
       </c>
-      <c r="J6" s="46" t="n">
-        <v>62.85714285714286</v>
-      </c>
-      <c r="K6" s="44" t="inlineStr">
+      <c r="J42" s="48" t="n">
+        <v>83.38983050847457</v>
+      </c>
+      <c r="K42" s="46" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="46" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="46" t="inlineStr">
+        <is>
+          <t>6710553353</t>
+        </is>
+      </c>
+      <c r="C43" s="47" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D43" s="46" t="inlineStr">
+        <is>
+          <t>101.00/118.00</t>
+        </is>
+      </c>
+      <c r="E43" s="48" t="n">
+        <v>85.59322033898306</v>
+      </c>
+      <c r="F43" s="48" t="n">
+        <v>59.91525423728814</v>
+      </c>
+      <c r="G43" s="46" t="inlineStr">
+        <is>
+          <t>7/7</t>
+        </is>
+      </c>
+      <c r="H43" s="48" t="n">
+        <v>100</v>
+      </c>
+      <c r="I43" s="48" t="n">
+        <v>30</v>
+      </c>
+      <c r="J43" s="48" t="n">
+        <v>89.91525423728814</v>
+      </c>
+      <c r="K43" s="46" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="46" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="46" t="inlineStr">
+        <is>
+          <t>6710553361</t>
+        </is>
+      </c>
+      <c r="C44" s="47" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D44" s="46" t="inlineStr">
+        <is>
+          <t>103.00/118.00</t>
+        </is>
+      </c>
+      <c r="E44" s="48" t="n">
+        <v>87.28813559322035</v>
+      </c>
+      <c r="F44" s="48" t="n">
+        <v>61.10169491525424</v>
+      </c>
+      <c r="G44" s="46" t="inlineStr">
+        <is>
+          <t>7/7</t>
+        </is>
+      </c>
+      <c r="H44" s="48" t="n">
+        <v>100</v>
+      </c>
+      <c r="I44" s="48" t="n">
+        <v>30</v>
+      </c>
+      <c r="J44" s="48" t="n">
+        <v>91.10169491525423</v>
+      </c>
+      <c r="K44" s="46" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="46" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="46" t="inlineStr">
+        <is>
+          <t>6710553370</t>
+        </is>
+      </c>
+      <c r="C45" s="47" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D45" s="46" t="inlineStr">
+        <is>
+          <t>52.00/118.00</t>
+        </is>
+      </c>
+      <c r="E45" s="48" t="n">
+        <v>44.06779661016949</v>
+      </c>
+      <c r="F45" s="48" t="n">
+        <v>30.84745762711864</v>
+      </c>
+      <c r="G45" s="46" t="inlineStr">
+        <is>
+          <t>7/7</t>
+        </is>
+      </c>
+      <c r="H45" s="48" t="n">
+        <v>100</v>
+      </c>
+      <c r="I45" s="48" t="n">
+        <v>30</v>
+      </c>
+      <c r="J45" s="48" t="n">
+        <v>60.84745762711864</v>
+      </c>
+      <c r="K45" s="46" t="inlineStr">
         <is>
           <t>★★☆☆☆</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="44" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="44" t="inlineStr">
-        <is>
-          <t>6610553220</t>
-        </is>
-      </c>
-      <c r="C7" s="45" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="46" t="inlineStr">
+        <is>
+          <t>6710553388</t>
+        </is>
+      </c>
+      <c r="C46" s="47" t="inlineStr">
         <is>
           <t>----</t>
         </is>
       </c>
-      <c r="D7" s="44" t="inlineStr">
-        <is>
-          <t>15.00/98.00</t>
-        </is>
-      </c>
-      <c r="E7" s="46" t="n">
-        <v>15.30612244897959</v>
-      </c>
-      <c r="F7" s="46" t="n">
-        <v>10.71428571428572</v>
-      </c>
-      <c r="G7" s="44" t="inlineStr">
-        <is>
-          <t>3/5</t>
-        </is>
-      </c>
-      <c r="H7" s="46" t="n">
-        <v>60</v>
-      </c>
-      <c r="I7" s="46" t="n">
-        <v>18</v>
-      </c>
-      <c r="J7" s="46" t="n">
-        <v>28.71428571428572</v>
-      </c>
-      <c r="K7" s="44" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="44" t="n">
+      <c r="D46" s="46" t="inlineStr">
+        <is>
+          <t>107.00/118.00</t>
+        </is>
+      </c>
+      <c r="E46" s="48" t="n">
+        <v>90.67796610169492</v>
+      </c>
+      <c r="F46" s="48" t="n">
+        <v>63.47457627118644</v>
+      </c>
+      <c r="G46" s="46" t="inlineStr">
+        <is>
+          <t>7/7</t>
+        </is>
+      </c>
+      <c r="H46" s="48" t="n">
+        <v>100</v>
+      </c>
+      <c r="I46" s="48" t="n">
+        <v>30</v>
+      </c>
+      <c r="J46" s="48" t="n">
+        <v>93.47457627118644</v>
+      </c>
+      <c r="K46" s="46" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="46" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="46" t="inlineStr">
+        <is>
+          <t>6710553396</t>
+        </is>
+      </c>
+      <c r="C47" s="47" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D47" s="46" t="inlineStr">
+        <is>
+          <t>96.00/118.00</t>
+        </is>
+      </c>
+      <c r="E47" s="48" t="n">
+        <v>81.35593220338984</v>
+      </c>
+      <c r="F47" s="48" t="n">
+        <v>56.94915254237289</v>
+      </c>
+      <c r="G47" s="46" t="inlineStr">
+        <is>
+          <t>7/7</t>
+        </is>
+      </c>
+      <c r="H47" s="48" t="n">
+        <v>100</v>
+      </c>
+      <c r="I47" s="48" t="n">
+        <v>30</v>
+      </c>
+      <c r="J47" s="48" t="n">
+        <v>86.94915254237289</v>
+      </c>
+      <c r="K47" s="46" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="49" t="inlineStr">
+        <is>
+          <t>Exercise maximum score</t>
+        </is>
+      </c>
+      <c r="B50" s="50" t="n">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="49" t="inlineStr">
+        <is>
+          <t>Exercise weight</t>
+        </is>
+      </c>
+      <c r="B51" s="51" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="49" t="inlineStr">
+        <is>
+          <t>Attendance sessions</t>
+        </is>
+      </c>
+      <c r="B52" s="50" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="44" t="inlineStr">
-        <is>
-          <t>6610553238</t>
-        </is>
-      </c>
-      <c r="C8" s="45" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D8" s="44" t="inlineStr">
-        <is>
-          <t>32.00/98.00</t>
-        </is>
-      </c>
-      <c r="E8" s="46" t="n">
-        <v>32.6530612244898</v>
-      </c>
-      <c r="F8" s="46" t="n">
-        <v>22.85714285714285</v>
-      </c>
-      <c r="G8" s="44" t="inlineStr">
-        <is>
-          <t>3/5</t>
-        </is>
-      </c>
-      <c r="H8" s="46" t="n">
-        <v>60</v>
-      </c>
-      <c r="I8" s="46" t="n">
-        <v>18</v>
-      </c>
-      <c r="J8" s="46" t="n">
-        <v>40.85714285714285</v>
-      </c>
-      <c r="K8" s="44" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="44" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="44" t="inlineStr">
-        <is>
-          <t>6610553254</t>
-        </is>
-      </c>
-      <c r="C9" s="45" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D9" s="44" t="inlineStr">
-        <is>
-          <t>62.00/98.00</t>
-        </is>
-      </c>
-      <c r="E9" s="46" t="n">
-        <v>63.26530612244898</v>
-      </c>
-      <c r="F9" s="46" t="n">
-        <v>44.28571428571429</v>
-      </c>
-      <c r="G9" s="44" t="inlineStr">
-        <is>
-          <t>5/5</t>
-        </is>
-      </c>
-      <c r="H9" s="46" t="n">
-        <v>100</v>
-      </c>
-      <c r="I9" s="46" t="n">
-        <v>30</v>
-      </c>
-      <c r="J9" s="46" t="n">
-        <v>74.28571428571429</v>
-      </c>
-      <c r="K9" s="44" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="44" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="44" t="inlineStr">
-        <is>
-          <t>6610553262</t>
-        </is>
-      </c>
-      <c r="C10" s="45" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D10" s="44" t="inlineStr">
-        <is>
-          <t>49.00/98.00</t>
-        </is>
-      </c>
-      <c r="E10" s="46" t="n">
-        <v>50</v>
-      </c>
-      <c r="F10" s="46" t="n">
-        <v>35</v>
-      </c>
-      <c r="G10" s="44" t="inlineStr">
-        <is>
-          <t>5/5</t>
-        </is>
-      </c>
-      <c r="H10" s="46" t="n">
-        <v>100</v>
-      </c>
-      <c r="I10" s="46" t="n">
-        <v>30</v>
-      </c>
-      <c r="J10" s="46" t="n">
-        <v>65</v>
-      </c>
-      <c r="K10" s="44" t="inlineStr">
-        <is>
-          <t>★★☆☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="44" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="44" t="inlineStr">
-        <is>
-          <t>6610553271</t>
-        </is>
-      </c>
-      <c r="C11" s="45" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D11" s="44" t="inlineStr">
-        <is>
-          <t>67.00/98.00</t>
-        </is>
-      </c>
-      <c r="E11" s="46" t="n">
-        <v>68.36734693877551</v>
-      </c>
-      <c r="F11" s="46" t="n">
-        <v>47.85714285714285</v>
-      </c>
-      <c r="G11" s="44" t="inlineStr">
-        <is>
-          <t>5/5</t>
-        </is>
-      </c>
-      <c r="H11" s="46" t="n">
-        <v>100</v>
-      </c>
-      <c r="I11" s="46" t="n">
-        <v>30</v>
-      </c>
-      <c r="J11" s="46" t="n">
-        <v>77.85714285714286</v>
-      </c>
-      <c r="K11" s="44" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="44" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="44" t="inlineStr">
-        <is>
-          <t>6610553289</t>
-        </is>
-      </c>
-      <c r="C12" s="45" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D12" s="44" t="inlineStr">
-        <is>
-          <t>41.00/98.00</t>
-        </is>
-      </c>
-      <c r="E12" s="46" t="n">
-        <v>41.83673469387755</v>
-      </c>
-      <c r="F12" s="46" t="n">
-        <v>29.28571428571429</v>
-      </c>
-      <c r="G12" s="44" t="inlineStr">
-        <is>
-          <t>4/5</t>
-        </is>
-      </c>
-      <c r="H12" s="46" t="n">
-        <v>80</v>
-      </c>
-      <c r="I12" s="46" t="n">
-        <v>24</v>
-      </c>
-      <c r="J12" s="46" t="n">
-        <v>53.28571428571429</v>
-      </c>
-      <c r="K12" s="44" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="44" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="44" t="inlineStr">
-        <is>
-          <t>6610553327</t>
-        </is>
-      </c>
-      <c r="C13" s="45" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D13" s="44" t="inlineStr">
-        <is>
-          <t>20.00/98.00</t>
-        </is>
-      </c>
-      <c r="E13" s="46" t="n">
-        <v>20.40816326530612</v>
-      </c>
-      <c r="F13" s="46" t="n">
-        <v>14.28571428571429</v>
-      </c>
-      <c r="G13" s="44" t="inlineStr">
-        <is>
-          <t>3/5</t>
-        </is>
-      </c>
-      <c r="H13" s="46" t="n">
-        <v>60</v>
-      </c>
-      <c r="I13" s="46" t="n">
-        <v>18</v>
-      </c>
-      <c r="J13" s="46" t="n">
-        <v>32.28571428571428</v>
-      </c>
-      <c r="K13" s="44" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="44" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="44" t="inlineStr">
-        <is>
-          <t>6610554153</t>
-        </is>
-      </c>
-      <c r="C14" s="45" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D14" s="44" t="inlineStr">
-        <is>
-          <t>50.00/98.00</t>
-        </is>
-      </c>
-      <c r="E14" s="46" t="n">
-        <v>51.02040816326531</v>
-      </c>
-      <c r="F14" s="46" t="n">
-        <v>35.71428571428572</v>
-      </c>
-      <c r="G14" s="44" t="inlineStr">
-        <is>
-          <t>3/5</t>
-        </is>
-      </c>
-      <c r="H14" s="46" t="n">
-        <v>60</v>
-      </c>
-      <c r="I14" s="46" t="n">
-        <v>18</v>
-      </c>
-      <c r="J14" s="46" t="n">
-        <v>53.71428571428572</v>
-      </c>
-      <c r="K14" s="44" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="44" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="44" t="inlineStr">
-        <is>
-          <t>6610554161</t>
-        </is>
-      </c>
-      <c r="C15" s="45" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D15" s="44" t="inlineStr">
-        <is>
-          <t>38.00/98.00</t>
-        </is>
-      </c>
-      <c r="E15" s="46" t="n">
-        <v>38.77551020408163</v>
-      </c>
-      <c r="F15" s="46" t="n">
-        <v>27.14285714285714</v>
-      </c>
-      <c r="G15" s="44" t="inlineStr">
-        <is>
-          <t>2/5</t>
-        </is>
-      </c>
-      <c r="H15" s="46" t="n">
-        <v>40</v>
-      </c>
-      <c r="I15" s="46" t="n">
-        <v>12</v>
-      </c>
-      <c r="J15" s="46" t="n">
-        <v>39.14285714285714</v>
-      </c>
-      <c r="K15" s="44" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="44" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="44" t="inlineStr">
-        <is>
-          <t>6710552942</t>
-        </is>
-      </c>
-      <c r="C16" s="45" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D16" s="44" t="inlineStr">
-        <is>
-          <t>65.00/98.00</t>
-        </is>
-      </c>
-      <c r="E16" s="46" t="n">
-        <v>66.32653061224489</v>
-      </c>
-      <c r="F16" s="46" t="n">
-        <v>46.42857142857142</v>
-      </c>
-      <c r="G16" s="44" t="inlineStr">
-        <is>
-          <t>5/5</t>
-        </is>
-      </c>
-      <c r="H16" s="46" t="n">
-        <v>100</v>
-      </c>
-      <c r="I16" s="46" t="n">
-        <v>30</v>
-      </c>
-      <c r="J16" s="46" t="n">
-        <v>76.42857142857142</v>
-      </c>
-      <c r="K16" s="44" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="44" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="44" t="inlineStr">
-        <is>
-          <t>6710552951</t>
-        </is>
-      </c>
-      <c r="C17" s="45" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D17" s="44" t="inlineStr">
-        <is>
-          <t>81.00/98.00</t>
-        </is>
-      </c>
-      <c r="E17" s="46" t="n">
-        <v>82.6530612244898</v>
-      </c>
-      <c r="F17" s="46" t="n">
-        <v>57.85714285714286</v>
-      </c>
-      <c r="G17" s="44" t="inlineStr">
-        <is>
-          <t>5/5</t>
-        </is>
-      </c>
-      <c r="H17" s="46" t="n">
-        <v>100</v>
-      </c>
-      <c r="I17" s="46" t="n">
-        <v>30</v>
-      </c>
-      <c r="J17" s="46" t="n">
-        <v>87.85714285714286</v>
-      </c>
-      <c r="K17" s="44" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="44" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" s="44" t="inlineStr">
-        <is>
-          <t>6710552969</t>
-        </is>
-      </c>
-      <c r="C18" s="45" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D18" s="44" t="inlineStr">
-        <is>
-          <t>80.00/98.00</t>
-        </is>
-      </c>
-      <c r="E18" s="46" t="n">
-        <v>81.63265306122449</v>
-      </c>
-      <c r="F18" s="46" t="n">
-        <v>57.14285714285715</v>
-      </c>
-      <c r="G18" s="44" t="inlineStr">
-        <is>
-          <t>5/5</t>
-        </is>
-      </c>
-      <c r="H18" s="46" t="n">
-        <v>100</v>
-      </c>
-      <c r="I18" s="46" t="n">
-        <v>30</v>
-      </c>
-      <c r="J18" s="46" t="n">
-        <v>87.14285714285714</v>
-      </c>
-      <c r="K18" s="44" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="44" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" s="44" t="inlineStr">
-        <is>
-          <t>6710552977</t>
-        </is>
-      </c>
-      <c r="C19" s="45" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D19" s="44" t="inlineStr">
-        <is>
-          <t>59.00/98.00</t>
-        </is>
-      </c>
-      <c r="E19" s="46" t="n">
-        <v>60.20408163265306</v>
-      </c>
-      <c r="F19" s="46" t="n">
-        <v>42.14285714285715</v>
-      </c>
-      <c r="G19" s="44" t="inlineStr">
-        <is>
-          <t>5/5</t>
-        </is>
-      </c>
-      <c r="H19" s="46" t="n">
-        <v>100</v>
-      </c>
-      <c r="I19" s="46" t="n">
-        <v>30</v>
-      </c>
-      <c r="J19" s="46" t="n">
-        <v>72.14285714285714</v>
-      </c>
-      <c r="K19" s="44" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="44" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" s="44" t="inlineStr">
-        <is>
-          <t>6710552985</t>
-        </is>
-      </c>
-      <c r="C20" s="45" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D20" s="44" t="inlineStr">
-        <is>
-          <t>68.00/98.00</t>
-        </is>
-      </c>
-      <c r="E20" s="46" t="n">
-        <v>69.38775510204081</v>
-      </c>
-      <c r="F20" s="46" t="n">
-        <v>48.57142857142857</v>
-      </c>
-      <c r="G20" s="44" t="inlineStr">
-        <is>
-          <t>5/5</t>
-        </is>
-      </c>
-      <c r="H20" s="46" t="n">
-        <v>100</v>
-      </c>
-      <c r="I20" s="46" t="n">
-        <v>30</v>
-      </c>
-      <c r="J20" s="46" t="n">
-        <v>78.57142857142857</v>
-      </c>
-      <c r="K20" s="44" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="44" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" s="44" t="inlineStr">
-        <is>
-          <t>6710552993</t>
-        </is>
-      </c>
-      <c r="C21" s="45" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D21" s="44" t="inlineStr">
-        <is>
-          <t>53.00/98.00</t>
-        </is>
-      </c>
-      <c r="E21" s="46" t="n">
-        <v>54.08163265306123</v>
-      </c>
-      <c r="F21" s="46" t="n">
-        <v>37.85714285714286</v>
-      </c>
-      <c r="G21" s="44" t="inlineStr">
-        <is>
-          <t>4/5</t>
-        </is>
-      </c>
-      <c r="H21" s="46" t="n">
-        <v>80</v>
-      </c>
-      <c r="I21" s="46" t="n">
-        <v>24</v>
-      </c>
-      <c r="J21" s="46" t="n">
-        <v>61.85714285714286</v>
-      </c>
-      <c r="K21" s="44" t="inlineStr">
-        <is>
-          <t>★★☆☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="44" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" s="44" t="inlineStr">
-        <is>
-          <t>6710553001</t>
-        </is>
-      </c>
-      <c r="C22" s="45" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D22" s="44" t="inlineStr">
-        <is>
-          <t>46.00/98.00</t>
-        </is>
-      </c>
-      <c r="E22" s="46" t="n">
-        <v>46.93877551020408</v>
-      </c>
-      <c r="F22" s="46" t="n">
-        <v>32.85714285714286</v>
-      </c>
-      <c r="G22" s="44" t="inlineStr">
-        <is>
-          <t>3/5</t>
-        </is>
-      </c>
-      <c r="H22" s="46" t="n">
-        <v>60</v>
-      </c>
-      <c r="I22" s="46" t="n">
-        <v>18</v>
-      </c>
-      <c r="J22" s="46" t="n">
-        <v>50.85714285714286</v>
-      </c>
-      <c r="K22" s="44" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="44" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" s="44" t="inlineStr">
-        <is>
-          <t>6710553027</t>
-        </is>
-      </c>
-      <c r="C23" s="45" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D23" s="44" t="inlineStr">
-        <is>
-          <t>73.00/98.00</t>
-        </is>
-      </c>
-      <c r="E23" s="46" t="n">
-        <v>74.48979591836735</v>
-      </c>
-      <c r="F23" s="46" t="n">
-        <v>52.14285714285715</v>
-      </c>
-      <c r="G23" s="44" t="inlineStr">
-        <is>
-          <t>5/5</t>
-        </is>
-      </c>
-      <c r="H23" s="46" t="n">
-        <v>100</v>
-      </c>
-      <c r="I23" s="46" t="n">
-        <v>30</v>
-      </c>
-      <c r="J23" s="46" t="n">
-        <v>82.14285714285714</v>
-      </c>
-      <c r="K23" s="44" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="44" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" s="44" t="inlineStr">
-        <is>
-          <t>6710553035</t>
-        </is>
-      </c>
-      <c r="C24" s="45" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D24" s="44" t="inlineStr">
-        <is>
-          <t>83.00/98.00</t>
-        </is>
-      </c>
-      <c r="E24" s="46" t="n">
-        <v>84.69387755102041</v>
-      </c>
-      <c r="F24" s="46" t="n">
-        <v>59.28571428571429</v>
-      </c>
-      <c r="G24" s="44" t="inlineStr">
-        <is>
-          <t>5/5</t>
-        </is>
-      </c>
-      <c r="H24" s="46" t="n">
-        <v>100</v>
-      </c>
-      <c r="I24" s="46" t="n">
-        <v>30</v>
-      </c>
-      <c r="J24" s="46" t="n">
-        <v>89.28571428571429</v>
-      </c>
-      <c r="K24" s="44" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="44" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" s="44" t="inlineStr">
-        <is>
-          <t>6710553051</t>
-        </is>
-      </c>
-      <c r="C25" s="45" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D25" s="44" t="inlineStr">
-        <is>
-          <t>0.00/98.00</t>
-        </is>
-      </c>
-      <c r="E25" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" s="44" t="inlineStr">
-        <is>
-          <t>0/5</t>
-        </is>
-      </c>
-      <c r="H25" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" s="44" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="44" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" s="44" t="inlineStr">
-        <is>
-          <t>6710553078</t>
-        </is>
-      </c>
-      <c r="C26" s="45" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D26" s="44" t="inlineStr">
-        <is>
-          <t>80.00/98.00</t>
-        </is>
-      </c>
-      <c r="E26" s="46" t="n">
-        <v>81.63265306122449</v>
-      </c>
-      <c r="F26" s="46" t="n">
-        <v>57.14285714285715</v>
-      </c>
-      <c r="G26" s="44" t="inlineStr">
-        <is>
-          <t>5/5</t>
-        </is>
-      </c>
-      <c r="H26" s="46" t="n">
-        <v>100</v>
-      </c>
-      <c r="I26" s="46" t="n">
-        <v>30</v>
-      </c>
-      <c r="J26" s="46" t="n">
-        <v>87.14285714285714</v>
-      </c>
-      <c r="K26" s="44" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="44" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" s="44" t="inlineStr">
-        <is>
-          <t>6710553086</t>
-        </is>
-      </c>
-      <c r="C27" s="45" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D27" s="44" t="inlineStr">
-        <is>
-          <t>58.00/98.00</t>
-        </is>
-      </c>
-      <c r="E27" s="46" t="n">
-        <v>59.18367346938776</v>
-      </c>
-      <c r="F27" s="46" t="n">
-        <v>41.42857142857143</v>
-      </c>
-      <c r="G27" s="44" t="inlineStr">
-        <is>
-          <t>4/5</t>
-        </is>
-      </c>
-      <c r="H27" s="46" t="n">
-        <v>80</v>
-      </c>
-      <c r="I27" s="46" t="n">
-        <v>24</v>
-      </c>
-      <c r="J27" s="46" t="n">
-        <v>65.42857142857143</v>
-      </c>
-      <c r="K27" s="44" t="inlineStr">
-        <is>
-          <t>★★☆☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="44" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" s="44" t="inlineStr">
-        <is>
-          <t>6710553094</t>
-        </is>
-      </c>
-      <c r="C28" s="45" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D28" s="44" t="inlineStr">
-        <is>
-          <t>95.00/98.00</t>
-        </is>
-      </c>
-      <c r="E28" s="46" t="n">
-        <v>96.93877551020408</v>
-      </c>
-      <c r="F28" s="46" t="n">
-        <v>67.85714285714286</v>
-      </c>
-      <c r="G28" s="44" t="inlineStr">
-        <is>
-          <t>5/5</t>
-        </is>
-      </c>
-      <c r="H28" s="46" t="n">
-        <v>100</v>
-      </c>
-      <c r="I28" s="46" t="n">
-        <v>30</v>
-      </c>
-      <c r="J28" s="46" t="n">
-        <v>97.85714285714286</v>
-      </c>
-      <c r="K28" s="44" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="44" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" s="44" t="inlineStr">
-        <is>
-          <t>6710553108</t>
-        </is>
-      </c>
-      <c r="C29" s="45" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D29" s="44" t="inlineStr">
-        <is>
-          <t>82.00/98.00</t>
-        </is>
-      </c>
-      <c r="E29" s="46" t="n">
-        <v>83.67346938775511</v>
-      </c>
-      <c r="F29" s="46" t="n">
-        <v>58.57142857142858</v>
-      </c>
-      <c r="G29" s="44" t="inlineStr">
-        <is>
-          <t>5/5</t>
-        </is>
-      </c>
-      <c r="H29" s="46" t="n">
-        <v>100</v>
-      </c>
-      <c r="I29" s="46" t="n">
-        <v>30</v>
-      </c>
-      <c r="J29" s="46" t="n">
-        <v>88.57142857142858</v>
-      </c>
-      <c r="K29" s="44" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="44" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" s="44" t="inlineStr">
-        <is>
-          <t>6710553124</t>
-        </is>
-      </c>
-      <c r="C30" s="45" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D30" s="44" t="inlineStr">
-        <is>
-          <t>74.00/98.00</t>
-        </is>
-      </c>
-      <c r="E30" s="46" t="n">
-        <v>75.51020408163265</v>
-      </c>
-      <c r="F30" s="46" t="n">
-        <v>52.85714285714285</v>
-      </c>
-      <c r="G30" s="44" t="inlineStr">
-        <is>
-          <t>4/5</t>
-        </is>
-      </c>
-      <c r="H30" s="46" t="n">
-        <v>80</v>
-      </c>
-      <c r="I30" s="46" t="n">
-        <v>24</v>
-      </c>
-      <c r="J30" s="46" t="n">
-        <v>76.85714285714286</v>
-      </c>
-      <c r="K30" s="44" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="44" t="n">
-        <v>30</v>
-      </c>
-      <c r="B31" s="44" t="inlineStr">
-        <is>
-          <t>6710553141</t>
-        </is>
-      </c>
-      <c r="C31" s="45" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D31" s="44" t="inlineStr">
-        <is>
-          <t>85.00/98.00</t>
-        </is>
-      </c>
-      <c r="E31" s="46" t="n">
-        <v>86.73469387755102</v>
-      </c>
-      <c r="F31" s="46" t="n">
-        <v>60.71428571428571</v>
-      </c>
-      <c r="G31" s="44" t="inlineStr">
-        <is>
-          <t>5/5</t>
-        </is>
-      </c>
-      <c r="H31" s="46" t="n">
-        <v>100</v>
-      </c>
-      <c r="I31" s="46" t="n">
-        <v>30</v>
-      </c>
-      <c r="J31" s="46" t="n">
-        <v>90.71428571428571</v>
-      </c>
-      <c r="K31" s="44" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="44" t="n">
-        <v>31</v>
-      </c>
-      <c r="B32" s="44" t="inlineStr">
-        <is>
-          <t>6710553167</t>
-        </is>
-      </c>
-      <c r="C32" s="45" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D32" s="44" t="inlineStr">
-        <is>
-          <t>61.00/98.00</t>
-        </is>
-      </c>
-      <c r="E32" s="46" t="n">
-        <v>62.24489795918367</v>
-      </c>
-      <c r="F32" s="46" t="n">
-        <v>43.57142857142858</v>
-      </c>
-      <c r="G32" s="44" t="inlineStr">
-        <is>
-          <t>4/5</t>
-        </is>
-      </c>
-      <c r="H32" s="46" t="n">
-        <v>80</v>
-      </c>
-      <c r="I32" s="46" t="n">
-        <v>24</v>
-      </c>
-      <c r="J32" s="46" t="n">
-        <v>67.57142857142858</v>
-      </c>
-      <c r="K32" s="44" t="inlineStr">
-        <is>
-          <t>★★☆☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="44" t="n">
-        <v>32</v>
-      </c>
-      <c r="B33" s="44" t="inlineStr">
-        <is>
-          <t>6710553191</t>
-        </is>
-      </c>
-      <c r="C33" s="45" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D33" s="44" t="inlineStr">
-        <is>
-          <t>94.00/98.00</t>
-        </is>
-      </c>
-      <c r="E33" s="46" t="n">
-        <v>95.91836734693877</v>
-      </c>
-      <c r="F33" s="46" t="n">
-        <v>67.14285714285714</v>
-      </c>
-      <c r="G33" s="44" t="inlineStr">
-        <is>
-          <t>5/5</t>
-        </is>
-      </c>
-      <c r="H33" s="46" t="n">
-        <v>100</v>
-      </c>
-      <c r="I33" s="46" t="n">
-        <v>30</v>
-      </c>
-      <c r="J33" s="46" t="n">
-        <v>97.14285714285714</v>
-      </c>
-      <c r="K33" s="44" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="44" t="n">
-        <v>33</v>
-      </c>
-      <c r="B34" s="44" t="inlineStr">
-        <is>
-          <t>6710553205</t>
-        </is>
-      </c>
-      <c r="C34" s="45" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D34" s="44" t="inlineStr">
-        <is>
-          <t>79.00/98.00</t>
-        </is>
-      </c>
-      <c r="E34" s="46" t="n">
-        <v>80.61224489795919</v>
-      </c>
-      <c r="F34" s="46" t="n">
-        <v>56.42857142857143</v>
-      </c>
-      <c r="G34" s="44" t="inlineStr">
-        <is>
-          <t>5/5</t>
-        </is>
-      </c>
-      <c r="H34" s="46" t="n">
-        <v>100</v>
-      </c>
-      <c r="I34" s="46" t="n">
-        <v>30</v>
-      </c>
-      <c r="J34" s="46" t="n">
-        <v>86.42857142857143</v>
-      </c>
-      <c r="K34" s="44" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="44" t="n">
-        <v>34</v>
-      </c>
-      <c r="B35" s="44" t="inlineStr">
-        <is>
-          <t>6710553213</t>
-        </is>
-      </c>
-      <c r="C35" s="45" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D35" s="44" t="inlineStr">
-        <is>
-          <t>70.00/98.00</t>
-        </is>
-      </c>
-      <c r="E35" s="46" t="n">
-        <v>71.42857142857143</v>
-      </c>
-      <c r="F35" s="46" t="n">
-        <v>50</v>
-      </c>
-      <c r="G35" s="44" t="inlineStr">
-        <is>
-          <t>5/5</t>
-        </is>
-      </c>
-      <c r="H35" s="46" t="n">
-        <v>100</v>
-      </c>
-      <c r="I35" s="46" t="n">
-        <v>30</v>
-      </c>
-      <c r="J35" s="46" t="n">
-        <v>80</v>
-      </c>
-      <c r="K35" s="44" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="44" t="n">
-        <v>35</v>
-      </c>
-      <c r="B36" s="44" t="inlineStr">
-        <is>
-          <t>6710553264</t>
-        </is>
-      </c>
-      <c r="C36" s="45" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D36" s="44" t="inlineStr">
-        <is>
-          <t>48.00/98.00</t>
-        </is>
-      </c>
-      <c r="E36" s="46" t="n">
-        <v>48.97959183673469</v>
-      </c>
-      <c r="F36" s="46" t="n">
-        <v>34.28571428571428</v>
-      </c>
-      <c r="G36" s="44" t="inlineStr">
-        <is>
-          <t>5/5</t>
-        </is>
-      </c>
-      <c r="H36" s="46" t="n">
-        <v>100</v>
-      </c>
-      <c r="I36" s="46" t="n">
-        <v>30</v>
-      </c>
-      <c r="J36" s="46" t="n">
-        <v>64.28571428571428</v>
-      </c>
-      <c r="K36" s="44" t="inlineStr">
-        <is>
-          <t>★★☆☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="44" t="n">
-        <v>36</v>
-      </c>
-      <c r="B37" s="44" t="inlineStr">
-        <is>
-          <t>6710553272</t>
-        </is>
-      </c>
-      <c r="C37" s="45" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D37" s="44" t="inlineStr">
-        <is>
-          <t>54.00/98.00</t>
-        </is>
-      </c>
-      <c r="E37" s="46" t="n">
-        <v>55.10204081632652</v>
-      </c>
-      <c r="F37" s="46" t="n">
-        <v>38.57142857142857</v>
-      </c>
-      <c r="G37" s="44" t="inlineStr">
-        <is>
-          <t>5/5</t>
-        </is>
-      </c>
-      <c r="H37" s="46" t="n">
-        <v>100</v>
-      </c>
-      <c r="I37" s="46" t="n">
-        <v>30</v>
-      </c>
-      <c r="J37" s="46" t="n">
-        <v>68.57142857142857</v>
-      </c>
-      <c r="K37" s="44" t="inlineStr">
-        <is>
-          <t>★★☆☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="44" t="n">
-        <v>37</v>
-      </c>
-      <c r="B38" s="44" t="inlineStr">
-        <is>
-          <t>6710553281</t>
-        </is>
-      </c>
-      <c r="C38" s="45" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D38" s="44" t="inlineStr">
-        <is>
-          <t>58.00/98.00</t>
-        </is>
-      </c>
-      <c r="E38" s="46" t="n">
-        <v>59.18367346938776</v>
-      </c>
-      <c r="F38" s="46" t="n">
-        <v>41.42857142857143</v>
-      </c>
-      <c r="G38" s="44" t="inlineStr">
-        <is>
-          <t>5/5</t>
-        </is>
-      </c>
-      <c r="H38" s="46" t="n">
-        <v>100</v>
-      </c>
-      <c r="I38" s="46" t="n">
-        <v>30</v>
-      </c>
-      <c r="J38" s="46" t="n">
-        <v>71.42857142857143</v>
-      </c>
-      <c r="K38" s="44" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="44" t="n">
-        <v>38</v>
-      </c>
-      <c r="B39" s="44" t="inlineStr">
-        <is>
-          <t>6710553299</t>
-        </is>
-      </c>
-      <c r="C39" s="45" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D39" s="44" t="inlineStr">
-        <is>
-          <t>85.00/98.00</t>
-        </is>
-      </c>
-      <c r="E39" s="46" t="n">
-        <v>86.73469387755102</v>
-      </c>
-      <c r="F39" s="46" t="n">
-        <v>60.71428571428571</v>
-      </c>
-      <c r="G39" s="44" t="inlineStr">
-        <is>
-          <t>5/5</t>
-        </is>
-      </c>
-      <c r="H39" s="46" t="n">
-        <v>100</v>
-      </c>
-      <c r="I39" s="46" t="n">
-        <v>30</v>
-      </c>
-      <c r="J39" s="46" t="n">
-        <v>90.71428571428571</v>
-      </c>
-      <c r="K39" s="44" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="44" t="n">
-        <v>39</v>
-      </c>
-      <c r="B40" s="44" t="inlineStr">
-        <is>
-          <t>6710553329</t>
-        </is>
-      </c>
-      <c r="C40" s="45" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D40" s="44" t="inlineStr">
-        <is>
-          <t>66.00/98.00</t>
-        </is>
-      </c>
-      <c r="E40" s="46" t="n">
-        <v>67.3469387755102</v>
-      </c>
-      <c r="F40" s="46" t="n">
-        <v>47.14285714285714</v>
-      </c>
-      <c r="G40" s="44" t="inlineStr">
-        <is>
-          <t>5/5</t>
-        </is>
-      </c>
-      <c r="H40" s="46" t="n">
-        <v>100</v>
-      </c>
-      <c r="I40" s="46" t="n">
-        <v>30</v>
-      </c>
-      <c r="J40" s="46" t="n">
-        <v>77.14285714285714</v>
-      </c>
-      <c r="K40" s="44" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="44" t="n">
-        <v>40</v>
-      </c>
-      <c r="B41" s="44" t="inlineStr">
-        <is>
-          <t>6710553337</t>
-        </is>
-      </c>
-      <c r="C41" s="45" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D41" s="44" t="inlineStr">
-        <is>
-          <t>77.00/98.00</t>
-        </is>
-      </c>
-      <c r="E41" s="46" t="n">
-        <v>78.57142857142857</v>
-      </c>
-      <c r="F41" s="46" t="n">
-        <v>55</v>
-      </c>
-      <c r="G41" s="44" t="inlineStr">
-        <is>
-          <t>5/5</t>
-        </is>
-      </c>
-      <c r="H41" s="46" t="n">
-        <v>100</v>
-      </c>
-      <c r="I41" s="46" t="n">
-        <v>30</v>
-      </c>
-      <c r="J41" s="46" t="n">
-        <v>85</v>
-      </c>
-      <c r="K41" s="44" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="44" t="n">
-        <v>41</v>
-      </c>
-      <c r="B42" s="44" t="inlineStr">
-        <is>
-          <t>6710553345</t>
-        </is>
-      </c>
-      <c r="C42" s="45" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D42" s="44" t="inlineStr">
-        <is>
-          <t>71.00/98.00</t>
-        </is>
-      </c>
-      <c r="E42" s="46" t="n">
-        <v>72.44897959183673</v>
-      </c>
-      <c r="F42" s="46" t="n">
-        <v>50.71428571428572</v>
-      </c>
-      <c r="G42" s="44" t="inlineStr">
-        <is>
-          <t>5/5</t>
-        </is>
-      </c>
-      <c r="H42" s="46" t="n">
-        <v>100</v>
-      </c>
-      <c r="I42" s="46" t="n">
-        <v>30</v>
-      </c>
-      <c r="J42" s="46" t="n">
-        <v>80.71428571428572</v>
-      </c>
-      <c r="K42" s="44" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="44" t="n">
-        <v>42</v>
-      </c>
-      <c r="B43" s="44" t="inlineStr">
-        <is>
-          <t>6710553353</t>
-        </is>
-      </c>
-      <c r="C43" s="45" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D43" s="44" t="inlineStr">
-        <is>
-          <t>87.00/98.00</t>
-        </is>
-      </c>
-      <c r="E43" s="46" t="n">
-        <v>88.77551020408163</v>
-      </c>
-      <c r="F43" s="46" t="n">
-        <v>62.14285714285714</v>
-      </c>
-      <c r="G43" s="44" t="inlineStr">
-        <is>
-          <t>5/5</t>
-        </is>
-      </c>
-      <c r="H43" s="46" t="n">
-        <v>100</v>
-      </c>
-      <c r="I43" s="46" t="n">
-        <v>30</v>
-      </c>
-      <c r="J43" s="46" t="n">
-        <v>92.14285714285714</v>
-      </c>
-      <c r="K43" s="44" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="44" t="n">
-        <v>43</v>
-      </c>
-      <c r="B44" s="44" t="inlineStr">
-        <is>
-          <t>6710553361</t>
-        </is>
-      </c>
-      <c r="C44" s="45" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D44" s="44" t="inlineStr">
-        <is>
-          <t>86.00/98.00</t>
-        </is>
-      </c>
-      <c r="E44" s="46" t="n">
-        <v>87.75510204081633</v>
-      </c>
-      <c r="F44" s="46" t="n">
-        <v>61.42857142857142</v>
-      </c>
-      <c r="G44" s="44" t="inlineStr">
-        <is>
-          <t>5/5</t>
-        </is>
-      </c>
-      <c r="H44" s="46" t="n">
-        <v>100</v>
-      </c>
-      <c r="I44" s="46" t="n">
-        <v>30</v>
-      </c>
-      <c r="J44" s="46" t="n">
-        <v>91.42857142857142</v>
-      </c>
-      <c r="K44" s="44" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="44" t="n">
-        <v>44</v>
-      </c>
-      <c r="B45" s="44" t="inlineStr">
-        <is>
-          <t>6710553370</t>
-        </is>
-      </c>
-      <c r="C45" s="45" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D45" s="44" t="inlineStr">
-        <is>
-          <t>42.00/98.00</t>
-        </is>
-      </c>
-      <c r="E45" s="46" t="n">
-        <v>42.85714285714285</v>
-      </c>
-      <c r="F45" s="46" t="n">
-        <v>30</v>
-      </c>
-      <c r="G45" s="44" t="inlineStr">
-        <is>
-          <t>5/5</t>
-        </is>
-      </c>
-      <c r="H45" s="46" t="n">
-        <v>100</v>
-      </c>
-      <c r="I45" s="46" t="n">
-        <v>30</v>
-      </c>
-      <c r="J45" s="46" t="n">
-        <v>60</v>
-      </c>
-      <c r="K45" s="44" t="inlineStr">
-        <is>
-          <t>★★☆☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="44" t="n">
-        <v>45</v>
-      </c>
-      <c r="B46" s="44" t="inlineStr">
-        <is>
-          <t>6710553388</t>
-        </is>
-      </c>
-      <c r="C46" s="45" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D46" s="44" t="inlineStr">
-        <is>
-          <t>92.00/98.00</t>
-        </is>
-      </c>
-      <c r="E46" s="46" t="n">
-        <v>93.87755102040816</v>
-      </c>
-      <c r="F46" s="46" t="n">
-        <v>65.71428571428572</v>
-      </c>
-      <c r="G46" s="44" t="inlineStr">
-        <is>
-          <t>5/5</t>
-        </is>
-      </c>
-      <c r="H46" s="46" t="n">
-        <v>100</v>
-      </c>
-      <c r="I46" s="46" t="n">
-        <v>30</v>
-      </c>
-      <c r="J46" s="46" t="n">
-        <v>95.71428571428572</v>
-      </c>
-      <c r="K46" s="44" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="44" t="n">
+    </row>
+    <row r="53">
+      <c r="A53" s="49" t="inlineStr">
+        <is>
+          <t>Attendance weight</t>
+        </is>
+      </c>
+      <c r="B53" s="51" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="49" t="n"/>
+      <c r="B54" s="50" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="49" t="inlineStr">
+        <is>
+          <t>Total students</t>
+        </is>
+      </c>
+      <c r="B55" s="50" t="n">
         <v>46</v>
       </c>
-      <c r="B47" s="44" t="inlineStr">
-        <is>
-          <t>6710553396</t>
-        </is>
-      </c>
-      <c r="C47" s="45" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D47" s="44" t="inlineStr">
-        <is>
-          <t>86.00/98.00</t>
-        </is>
-      </c>
-      <c r="E47" s="46" t="n">
-        <v>87.75510204081633</v>
-      </c>
-      <c r="F47" s="46" t="n">
-        <v>61.42857142857142</v>
-      </c>
-      <c r="G47" s="44" t="inlineStr">
-        <is>
-          <t>5/5</t>
-        </is>
-      </c>
-      <c r="H47" s="46" t="n">
-        <v>100</v>
-      </c>
-      <c r="I47" s="46" t="n">
-        <v>30</v>
-      </c>
-      <c r="J47" s="46" t="n">
-        <v>91.42857142857142</v>
-      </c>
-      <c r="K47" s="44" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="47" t="inlineStr">
-        <is>
-          <t>Exercise maximum score</t>
-        </is>
-      </c>
-      <c r="B50" s="48" t="n">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="47" t="inlineStr">
-        <is>
-          <t>Exercise weight</t>
-        </is>
-      </c>
-      <c r="B51" s="49" t="n">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="47" t="inlineStr">
-        <is>
-          <t>Attendance sessions</t>
-        </is>
-      </c>
-      <c r="B52" s="48" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="47" t="inlineStr">
-        <is>
-          <t>Attendance weight</t>
-        </is>
-      </c>
-      <c r="B53" s="49" t="n">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="47" t="n"/>
-      <c r="B54" s="48" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="47" t="inlineStr">
-        <is>
-          <t>Total students</t>
-        </is>
-      </c>
-      <c r="B55" s="48" t="n">
-        <v>46</v>
-      </c>
     </row>
     <row r="56">
-      <c r="A56" s="47" t="inlineStr">
+      <c r="A56" s="49" t="inlineStr">
         <is>
           <t>Mean Grand Total</t>
         </is>
       </c>
-      <c r="B56" s="50" t="n">
-        <v>69.87577639751552</v>
+      <c r="B56" s="52" t="n">
+        <v>71.53147699757869</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="47" t="inlineStr">
+      <c r="A57" s="49" t="inlineStr">
         <is>
           <t>SD Grand Total (population)</t>
         </is>
       </c>
-      <c r="B57" s="50" t="n">
-        <v>21.45721912582595</v>
+      <c r="B57" s="52" t="n">
+        <v>19.49221390346051</v>
       </c>
     </row>
   </sheetData>

--- a/Score_Class_2026_Summary.xlsx
+++ b/Score_Class_2026_Summary.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="39620" yWindow="-7000" windowWidth="18090" windowHeight="20970" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="25490" yWindow="-8600" windowWidth="38620" windowHeight="21100" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exercise" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ClassAttend" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Exercise" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ClassAttend" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Summary" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Summary'!$A$1:$K$47</definedName>
@@ -22,7 +22,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="B1d\-mmm\-yy"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <color rgb="FF000000"/>
@@ -90,6 +90,12 @@
       <sz val="12"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="9"/>
@@ -105,7 +111,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -133,12 +139,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.5999938962981048"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.7999816888943144"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -202,7 +202,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -262,7 +262,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -297,13 +296,24 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -311,34 +321,25 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="12" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="13" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="ปกติ" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -413,7 +414,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor editAs="oneCell">
     <from>
       <col>2</col>
@@ -425,30 +426,30 @@
       <col>3</col>
       <colOff>1313180</colOff>
       <row>5</row>
-      <rowOff>1420790</rowOff>
+      <rowOff>1429860</rowOff>
     </to>
     <pic>
       <nvPicPr>
         <cNvPr id="2" name="/xl/media/image1.png"/>
         <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
+          <a:picLocks noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:xfrm>
           <a:off x="976630" y="1028071"/>
           <a:ext cx="1631950" cy="1586519"/>
         </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+        <a:prstGeom prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:ln>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -459,7 +460,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>12</col>
@@ -474,13 +475,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -642,35 +643,35 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B2:Z56"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="10.796875" defaultRowHeight="15.6"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="10.78515625" defaultRowHeight="15.9"/>
   <cols>
     <col width="1" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="20.6484375" customWidth="1" min="4" max="4"/>
+    <col width="20.640625" customWidth="1" min="4" max="4"/>
     <col hidden="1" width="18" customWidth="1" min="5" max="6"/>
     <col hidden="1" width="10" customWidth="1" min="7" max="8"/>
-    <col hidden="1" width="10.796875" customWidth="1" min="9" max="11"/>
-    <col width="4.6484375" customWidth="1" style="41" min="12" max="20"/>
-    <col width="4.796875" customWidth="1" style="41" min="21" max="21"/>
-    <col width="4.796875" customWidth="1" min="22" max="26"/>
+    <col hidden="1" width="10.78515625" customWidth="1" min="9" max="11"/>
+    <col width="4.640625" customWidth="1" style="43" min="12" max="20"/>
+    <col width="4.78515625" customWidth="1" style="43" min="21" max="22"/>
+    <col width="4.78515625" customWidth="1" min="23" max="26"/>
   </cols>
   <sheetData>
     <row r="2" ht="16" customHeight="1">
-      <c r="B2" s="40" t="inlineStr">
+      <c r="B2" s="42" t="inlineStr">
         <is>
           <t>รายงานแสดงจำนวนนิสิต จำแนกตามหมู่เรียน ภาคต้น ปีการศึกษา 2569</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="18.3" customHeight="1">
-      <c r="B3" s="40" t="inlineStr">
+    <row r="3" ht="18.35" customHeight="1">
+      <c r="B3" s="42" t="inlineStr">
         <is>
           <t>มหาวิทยาลัยเกษตรศาสตร์ บางเขน ระดับการศึกษา ปริญญาตรี</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="26.1" customHeight="1">
+    <row r="4" ht="26.15" customHeight="1">
       <c r="B4" s="1" t="inlineStr">
         <is>
           <t>ชื่อวิชา</t>
@@ -681,13 +682,13 @@
           <t>01218332-65 การฉายแผนที่ Map Projection</t>
         </is>
       </c>
-      <c r="M4" s="41" t="inlineStr">
+      <c r="M4" s="43" t="inlineStr">
         <is>
           <t xml:space="preserve">รศ.ดร.ไพศาล สันติธรรมนนท์ </t>
         </is>
       </c>
     </row>
-    <row r="5" ht="18" customHeight="1">
+    <row r="5" ht="21" customHeight="1">
       <c r="E5" s="1" t="inlineStr">
         <is>
           <t>หมู่เรียน</t>
@@ -725,7 +726,7 @@
           <t>EX.3 Draw Sphere/Spheroid</t>
         </is>
       </c>
-      <c r="N6" s="25" t="inlineStr">
+      <c r="N6" s="24" t="inlineStr">
         <is>
           <t>Ex.4 EFG for Sphere</t>
         </is>
@@ -740,9 +741,9 @@
           <t>Ex.6 Tissot Indicator</t>
         </is>
       </c>
-      <c r="Q6" s="26" t="inlineStr">
-        <is>
-          <t>MidTerm</t>
+      <c r="Q6" s="25" t="inlineStr">
+        <is>
+          <t>MidTerm Exam</t>
         </is>
       </c>
       <c r="R6" s="11" t="inlineStr">
@@ -762,16 +763,28 @@
       </c>
       <c r="U6" s="11" t="inlineStr">
         <is>
-          <t>Ex. UTM zone 47/48</t>
-        </is>
-      </c>
-      <c r="V6" s="9" t="n"/>
-      <c r="W6" s="9" t="n"/>
-      <c r="X6" s="9" t="n"/>
+          <t>Ex.10 UTM zone 47/48</t>
+        </is>
+      </c>
+      <c r="V6" s="11" t="inlineStr">
+        <is>
+          <t>Ex.11 LDP</t>
+        </is>
+      </c>
+      <c r="W6" s="11" t="inlineStr">
+        <is>
+          <t>Ex.12 WebMap</t>
+        </is>
+      </c>
+      <c r="X6" s="25" t="inlineStr">
+        <is>
+          <t>Final Exam</t>
+        </is>
+      </c>
       <c r="Y6" s="9" t="n"/>
       <c r="Z6" s="9" t="n"/>
     </row>
-    <row r="7" ht="20.4" customHeight="1">
+    <row r="7" ht="22.75" customHeight="1">
       <c r="B7" s="3" t="inlineStr">
         <is>
           <t>ลำดับที่</t>
@@ -837,7 +850,7 @@
       <c r="P7" s="20" t="n">
         <v>10</v>
       </c>
-      <c r="Q7" s="27" t="n">
+      <c r="Q7" s="26" t="n">
         <v>26</v>
       </c>
       <c r="R7" s="20" t="n">
@@ -852,13 +865,15 @@
       <c r="U7" s="20" t="n">
         <v>10</v>
       </c>
-      <c r="V7" s="9" t="n"/>
-      <c r="W7" s="9" t="n"/>
-      <c r="X7" s="9" t="n"/>
+      <c r="V7" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="W7" s="20" t="n"/>
+      <c r="X7" s="26" t="n"/>
       <c r="Y7" s="9" t="n"/>
       <c r="Z7" s="9" t="n"/>
     </row>
-    <row r="8" ht="18" customHeight="1">
+    <row r="8" ht="21" customHeight="1">
       <c r="B8" s="5" t="inlineStr">
         <is>
           <t>1</t>
@@ -918,7 +933,7 @@
       <c r="P8" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="Q8" s="28" t="n">
+      <c r="Q8" s="27" t="n">
         <v>10</v>
       </c>
       <c r="R8" s="10" t="n">
@@ -931,13 +946,15 @@
       <c r="U8" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="V8" s="9" t="n"/>
+      <c r="V8" s="10" t="n">
+        <v>3</v>
+      </c>
       <c r="W8" s="9" t="n"/>
       <c r="X8" s="9" t="n"/>
       <c r="Y8" s="9" t="n"/>
       <c r="Z8" s="9" t="n"/>
     </row>
-    <row r="9" ht="18" customHeight="1">
+    <row r="9" ht="21" customHeight="1">
       <c r="B9" s="5" t="inlineStr">
         <is>
           <t>2</t>
@@ -997,7 +1014,7 @@
         <v>10</v>
       </c>
       <c r="P9" s="10" t="n"/>
-      <c r="Q9" s="28" t="n">
+      <c r="Q9" s="27" t="n">
         <v>4</v>
       </c>
       <c r="R9" s="10" t="n">
@@ -1012,13 +1029,15 @@
       <c r="U9" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="V9" s="9" t="n"/>
+      <c r="V9" s="10" t="n">
+        <v>9</v>
+      </c>
       <c r="W9" s="9" t="n"/>
       <c r="X9" s="9" t="n"/>
       <c r="Y9" s="9" t="n"/>
       <c r="Z9" s="9" t="n"/>
     </row>
-    <row r="10" ht="18" customHeight="1">
+    <row r="10" ht="21" customHeight="1">
       <c r="B10" s="5" t="inlineStr">
         <is>
           <t>3</t>
@@ -1080,7 +1099,7 @@
       <c r="P10" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="Q10" s="28" t="n">
+      <c r="Q10" s="27" t="n">
         <v>4</v>
       </c>
       <c r="R10" s="10" t="n"/>
@@ -1093,13 +1112,15 @@
       <c r="U10" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="V10" s="9" t="n"/>
+      <c r="V10" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="W10" s="9" t="n"/>
       <c r="X10" s="9" t="n"/>
       <c r="Y10" s="9" t="n"/>
       <c r="Z10" s="9" t="n"/>
     </row>
-    <row r="11" ht="18" customHeight="1">
+    <row r="11" ht="21" customHeight="1">
       <c r="B11" s="5" t="inlineStr">
         <is>
           <t>4</t>
@@ -1165,7 +1186,7 @@
       <c r="P11" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="Q11" s="28" t="n">
+      <c r="Q11" s="27" t="n">
         <v>9</v>
       </c>
       <c r="R11" s="10" t="n">
@@ -1180,13 +1201,15 @@
       <c r="U11" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="V11" s="9" t="n"/>
+      <c r="V11" s="10" t="n">
+        <v>6</v>
+      </c>
       <c r="W11" s="9" t="n"/>
       <c r="X11" s="9" t="n"/>
       <c r="Y11" s="9" t="n"/>
       <c r="Z11" s="9" t="n"/>
     </row>
-    <row r="12" ht="18" customHeight="1">
+    <row r="12" ht="21" customHeight="1">
       <c r="B12" s="5" t="inlineStr">
         <is>
           <t>5</t>
@@ -1246,7 +1269,7 @@
       <c r="P12" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q12" s="28" t="n">
+      <c r="Q12" s="27" t="n">
         <v>9</v>
       </c>
       <c r="R12" s="10" t="n">
@@ -1261,13 +1284,13 @@
       <c r="U12" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="V12" s="9" t="n"/>
+      <c r="V12" s="10" t="n"/>
       <c r="W12" s="9" t="n"/>
       <c r="X12" s="9" t="n"/>
       <c r="Y12" s="9" t="n"/>
       <c r="Z12" s="9" t="n"/>
     </row>
-    <row r="13" ht="18" customHeight="1">
+    <row r="13" ht="21" customHeight="1">
       <c r="B13" s="5" t="inlineStr">
         <is>
           <t>6</t>
@@ -1323,7 +1346,7 @@
       <c r="N13" s="10" t="n"/>
       <c r="O13" s="10" t="n"/>
       <c r="P13" s="10" t="n"/>
-      <c r="Q13" s="28" t="n">
+      <c r="Q13" s="27" t="n">
         <v>0</v>
       </c>
       <c r="R13" s="10" t="n">
@@ -1338,13 +1361,13 @@
       <c r="U13" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="V13" s="9" t="n"/>
+      <c r="V13" s="10" t="n"/>
       <c r="W13" s="9" t="n"/>
       <c r="X13" s="9" t="n"/>
       <c r="Y13" s="9" t="n"/>
       <c r="Z13" s="9" t="n"/>
     </row>
-    <row r="14" ht="18" customHeight="1">
+    <row r="14" ht="21" customHeight="1">
       <c r="B14" s="5" t="inlineStr">
         <is>
           <t>7</t>
@@ -1406,7 +1429,7 @@
       <c r="P14" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="Q14" s="28" t="n">
+      <c r="Q14" s="27" t="n">
         <v>2</v>
       </c>
       <c r="R14" s="10" t="n">
@@ -1421,13 +1444,15 @@
       <c r="U14" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="V14" s="9" t="n"/>
+      <c r="V14" s="10" t="n">
+        <v>10</v>
+      </c>
       <c r="W14" s="9" t="n"/>
       <c r="X14" s="9" t="n"/>
       <c r="Y14" s="9" t="n"/>
       <c r="Z14" s="9" t="n"/>
     </row>
-    <row r="15" ht="18" customHeight="1">
+    <row r="15" ht="21" customHeight="1">
       <c r="B15" s="5" t="inlineStr">
         <is>
           <t>8</t>
@@ -1493,7 +1518,7 @@
       <c r="P15" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="Q15" s="28" t="n">
+      <c r="Q15" s="27" t="n">
         <v>11</v>
       </c>
       <c r="R15" s="10" t="n">
@@ -1508,13 +1533,15 @@
       <c r="U15" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="V15" s="9" t="n"/>
+      <c r="V15" s="10" t="n">
+        <v>9</v>
+      </c>
       <c r="W15" s="9" t="n"/>
       <c r="X15" s="9" t="n"/>
       <c r="Y15" s="9" t="n"/>
       <c r="Z15" s="9" t="n"/>
     </row>
-    <row r="16" ht="18" customHeight="1">
+    <row r="16" ht="21" customHeight="1">
       <c r="B16" s="5" t="inlineStr">
         <is>
           <t>9</t>
@@ -1576,7 +1603,7 @@
         <v>5</v>
       </c>
       <c r="P16" s="10" t="n"/>
-      <c r="Q16" s="28" t="n">
+      <c r="Q16" s="27" t="n">
         <v>14</v>
       </c>
       <c r="R16" s="10" t="n">
@@ -1591,13 +1618,15 @@
       <c r="U16" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="V16" s="9" t="n"/>
+      <c r="V16" s="10" t="n">
+        <v>6</v>
+      </c>
       <c r="W16" s="9" t="n"/>
       <c r="X16" s="9" t="n"/>
       <c r="Y16" s="9" t="n"/>
       <c r="Z16" s="9" t="n"/>
     </row>
-    <row r="17" ht="18" customHeight="1">
+    <row r="17" ht="21" customHeight="1">
       <c r="B17" s="5" t="inlineStr">
         <is>
           <t>10</t>
@@ -1663,7 +1692,7 @@
       <c r="P17" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q17" s="28" t="n">
+      <c r="Q17" s="27" t="n">
         <v>9</v>
       </c>
       <c r="R17" s="10" t="n">
@@ -1678,13 +1707,15 @@
       <c r="U17" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="V17" s="9" t="n"/>
+      <c r="V17" s="10" t="n">
+        <v>10</v>
+      </c>
       <c r="W17" s="9" t="n"/>
       <c r="X17" s="9" t="n"/>
       <c r="Y17" s="9" t="n"/>
       <c r="Z17" s="9" t="n"/>
     </row>
-    <row r="18" ht="18" customHeight="1">
+    <row r="18" ht="21" customHeight="1">
       <c r="B18" s="5" t="inlineStr">
         <is>
           <t>11</t>
@@ -1746,7 +1777,7 @@
       <c r="P18" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="Q18" s="28" t="n">
+      <c r="Q18" s="27" t="n">
         <v>2</v>
       </c>
       <c r="R18" s="10" t="n">
@@ -1761,13 +1792,13 @@
       <c r="U18" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="V18" s="9" t="n"/>
+      <c r="V18" s="10" t="n"/>
       <c r="W18" s="9" t="n"/>
       <c r="X18" s="9" t="n"/>
       <c r="Y18" s="9" t="n"/>
       <c r="Z18" s="9" t="n"/>
     </row>
-    <row r="19" ht="18" customHeight="1">
+    <row r="19" ht="21" customHeight="1">
       <c r="B19" s="5" t="inlineStr">
         <is>
           <t>12</t>
@@ -1823,7 +1854,7 @@
       <c r="N19" s="10" t="n"/>
       <c r="O19" s="10" t="n"/>
       <c r="P19" s="10" t="n"/>
-      <c r="Q19" s="28" t="n">
+      <c r="Q19" s="27" t="n">
         <v>0</v>
       </c>
       <c r="R19" s="10" t="n">
@@ -1838,13 +1869,13 @@
       <c r="U19" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="V19" s="9" t="n"/>
+      <c r="V19" s="10" t="n"/>
       <c r="W19" s="9" t="n"/>
       <c r="X19" s="9" t="n"/>
       <c r="Y19" s="9" t="n"/>
       <c r="Z19" s="9" t="n"/>
     </row>
-    <row r="20" ht="18" customHeight="1">
+    <row r="20" ht="21" customHeight="1">
       <c r="B20" s="5" t="inlineStr">
         <is>
           <t>13</t>
@@ -1910,7 +1941,7 @@
       <c r="P20" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q20" s="28" t="n">
+      <c r="Q20" s="27" t="n">
         <v>5</v>
       </c>
       <c r="R20" s="10" t="n">
@@ -1923,13 +1954,15 @@
       <c r="U20" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="V20" s="9" t="n"/>
+      <c r="V20" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="W20" s="9" t="n"/>
       <c r="X20" s="9" t="n"/>
       <c r="Y20" s="9" t="n"/>
       <c r="Z20" s="9" t="n"/>
     </row>
-    <row r="21" ht="18" customHeight="1">
+    <row r="21" ht="21" customHeight="1">
       <c r="B21" s="5" t="inlineStr">
         <is>
           <t>14</t>
@@ -1991,7 +2024,7 @@
         <v>5</v>
       </c>
       <c r="P21" s="10" t="n"/>
-      <c r="Q21" s="28" t="n">
+      <c r="Q21" s="27" t="n">
         <v>6</v>
       </c>
       <c r="R21" s="10" t="n"/>
@@ -2004,13 +2037,13 @@
       <c r="U21" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="V21" s="9" t="n"/>
+      <c r="V21" s="10" t="n"/>
       <c r="W21" s="9" t="n"/>
       <c r="X21" s="9" t="n"/>
       <c r="Y21" s="9" t="n"/>
       <c r="Z21" s="9" t="n"/>
     </row>
-    <row r="22" ht="18" customHeight="1">
+    <row r="22" ht="21" customHeight="1">
       <c r="B22" s="5" t="inlineStr">
         <is>
           <t>15</t>
@@ -2076,7 +2109,7 @@
       <c r="P22" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q22" s="28" t="n">
+      <c r="Q22" s="27" t="n">
         <v>2</v>
       </c>
       <c r="R22" s="10" t="n">
@@ -2085,15 +2118,21 @@
       <c r="S22" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="T22" s="10" t="n"/>
-      <c r="U22" s="10" t="n"/>
-      <c r="V22" s="9" t="n"/>
+      <c r="T22" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="U22" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="V22" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="W22" s="9" t="n"/>
       <c r="X22" s="9" t="n"/>
       <c r="Y22" s="9" t="n"/>
       <c r="Z22" s="9" t="n"/>
     </row>
-    <row r="23" ht="18" customHeight="1">
+    <row r="23" ht="21" customHeight="1">
       <c r="B23" s="5" t="inlineStr">
         <is>
           <t>16</t>
@@ -2159,7 +2198,7 @@
       <c r="P23" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q23" s="28" t="n">
+      <c r="Q23" s="27" t="n">
         <v>16</v>
       </c>
       <c r="R23" s="10" t="n">
@@ -2174,13 +2213,15 @@
       <c r="U23" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="V23" s="9" t="n"/>
+      <c r="V23" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="W23" s="9" t="n"/>
       <c r="X23" s="9" t="n"/>
       <c r="Y23" s="9" t="n"/>
       <c r="Z23" s="9" t="n"/>
     </row>
-    <row r="24" ht="18" customHeight="1">
+    <row r="24" ht="21" customHeight="1">
       <c r="B24" s="5" t="inlineStr">
         <is>
           <t>17</t>
@@ -2246,7 +2287,7 @@
       <c r="P24" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q24" s="28" t="n">
+      <c r="Q24" s="27" t="n">
         <v>12</v>
       </c>
       <c r="R24" s="10" t="n">
@@ -2261,13 +2302,15 @@
       <c r="U24" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="V24" s="9" t="n"/>
+      <c r="V24" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="W24" s="9" t="n"/>
       <c r="X24" s="9" t="n"/>
       <c r="Y24" s="9" t="n"/>
       <c r="Z24" s="9" t="n"/>
     </row>
-    <row r="25" ht="18" customHeight="1">
+    <row r="25" ht="21" customHeight="1">
       <c r="B25" s="5" t="inlineStr">
         <is>
           <t>18</t>
@@ -2333,7 +2376,7 @@
       <c r="P25" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q25" s="28" t="n">
+      <c r="Q25" s="27" t="n">
         <v>9</v>
       </c>
       <c r="R25" s="10" t="n">
@@ -2348,13 +2391,15 @@
       <c r="U25" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="V25" s="9" t="n"/>
+      <c r="V25" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="W25" s="9" t="n"/>
       <c r="X25" s="9" t="n"/>
       <c r="Y25" s="9" t="n"/>
       <c r="Z25" s="9" t="n"/>
     </row>
-    <row r="26" ht="18" customHeight="1">
+    <row r="26" ht="21" customHeight="1">
       <c r="B26" s="5" t="inlineStr">
         <is>
           <t>19</t>
@@ -2420,7 +2465,7 @@
       <c r="P26" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q26" s="28" t="n">
+      <c r="Q26" s="27" t="n">
         <v>1</v>
       </c>
       <c r="R26" s="10" t="n">
@@ -2435,13 +2480,15 @@
       <c r="U26" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="V26" s="9" t="n"/>
+      <c r="V26" s="10" t="n">
+        <v>10</v>
+      </c>
       <c r="W26" s="9" t="n"/>
       <c r="X26" s="9" t="n"/>
       <c r="Y26" s="9" t="n"/>
       <c r="Z26" s="9" t="n"/>
     </row>
-    <row r="27" ht="18" customHeight="1">
+    <row r="27" ht="21" customHeight="1">
       <c r="B27" s="5" t="inlineStr">
         <is>
           <t>20</t>
@@ -2505,7 +2552,7 @@
       <c r="P27" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q27" s="28" t="n">
+      <c r="Q27" s="27" t="n">
         <v>1</v>
       </c>
       <c r="R27" s="10" t="n">
@@ -2520,13 +2567,15 @@
       <c r="U27" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="V27" s="9" t="n"/>
+      <c r="V27" s="10" t="n">
+        <v>10</v>
+      </c>
       <c r="W27" s="9" t="n"/>
       <c r="X27" s="9" t="n"/>
       <c r="Y27" s="9" t="n"/>
       <c r="Z27" s="9" t="n"/>
     </row>
-    <row r="28" ht="18" customHeight="1">
+    <row r="28" ht="21" customHeight="1">
       <c r="B28" s="5" t="inlineStr">
         <is>
           <t>21</t>
@@ -2588,7 +2637,7 @@
         <v>4</v>
       </c>
       <c r="P28" s="10" t="n"/>
-      <c r="Q28" s="28" t="n">
+      <c r="Q28" s="27" t="n">
         <v>8</v>
       </c>
       <c r="R28" s="10" t="n">
@@ -2599,13 +2648,15 @@
       </c>
       <c r="T28" s="10" t="n"/>
       <c r="U28" s="10" t="n"/>
-      <c r="V28" s="9" t="n"/>
+      <c r="V28" s="10" t="n">
+        <v>7</v>
+      </c>
       <c r="W28" s="9" t="n"/>
       <c r="X28" s="9" t="n"/>
       <c r="Y28" s="9" t="n"/>
       <c r="Z28" s="9" t="n"/>
     </row>
-    <row r="29" ht="18" customHeight="1">
+    <row r="29" ht="21" customHeight="1">
       <c r="B29" s="5" t="inlineStr">
         <is>
           <t>22</t>
@@ -2671,7 +2722,7 @@
       <c r="P29" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q29" s="28" t="n">
+      <c r="Q29" s="27" t="n">
         <v>9</v>
       </c>
       <c r="R29" s="10" t="n">
@@ -2686,13 +2737,15 @@
       <c r="U29" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="V29" s="9" t="n"/>
+      <c r="V29" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="W29" s="9" t="n"/>
       <c r="X29" s="9" t="n"/>
       <c r="Y29" s="9" t="n"/>
       <c r="Z29" s="9" t="n"/>
     </row>
-    <row r="30" ht="18" customHeight="1">
+    <row r="30" ht="21" customHeight="1">
       <c r="B30" s="5" t="inlineStr">
         <is>
           <t>23</t>
@@ -2758,7 +2811,7 @@
       <c r="P30" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q30" s="28" t="n">
+      <c r="Q30" s="27" t="n">
         <v>11</v>
       </c>
       <c r="R30" s="10" t="n">
@@ -2773,80 +2826,82 @@
       <c r="U30" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="V30" s="9" t="n"/>
+      <c r="V30" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="W30" s="9" t="n"/>
       <c r="X30" s="9" t="n"/>
       <c r="Y30" s="9" t="n"/>
       <c r="Z30" s="9" t="n"/>
     </row>
-    <row r="31" ht="18" customHeight="1">
-      <c r="B31" s="29" t="inlineStr">
+    <row r="31" ht="21" customHeight="1">
+      <c r="B31" s="28" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="C31" s="30" t="inlineStr">
+      <c r="C31" s="29" t="inlineStr">
         <is>
           <t>6710553051</t>
         </is>
       </c>
-      <c r="D31" s="30" t="inlineStr">
+      <c r="D31" s="29" t="inlineStr">
         <is>
           <t>นายธนทัต มุทธากาญจน์</t>
         </is>
       </c>
-      <c r="E31" s="30" t="inlineStr">
+      <c r="E31" s="29" t="inlineStr">
         <is>
           <t>Mr. Tanatud MUTTAKARN</t>
         </is>
       </c>
-      <c r="F31" s="30" t="inlineStr">
+      <c r="F31" s="29" t="inlineStr">
         <is>
           <t>วิศวกรรมศาสตร์</t>
         </is>
       </c>
-      <c r="G31" s="30" t="inlineStr">
+      <c r="G31" s="29" t="inlineStr">
         <is>
           <t>วิศวกรรมสำรวจและสารสนเทศภูมิศาสตร์</t>
         </is>
       </c>
-      <c r="H31" s="30" t="inlineStr">
+      <c r="H31" s="29" t="inlineStr">
         <is>
           <t>E18</t>
         </is>
       </c>
-      <c r="I31" s="30" t="inlineStr">
+      <c r="I31" s="29" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="J31" s="30" t="inlineStr">
+      <c r="J31" s="29" t="inlineStr">
         <is>
           <t>tanatud.m@ku.th</t>
         </is>
       </c>
-      <c r="K31" s="31" t="inlineStr">
+      <c r="K31" s="30" t="inlineStr">
         <is>
           <t>tanatud.m@live.ku.th</t>
         </is>
       </c>
-      <c r="L31" s="32" t="n"/>
-      <c r="M31" s="32" t="n"/>
-      <c r="N31" s="32" t="n"/>
-      <c r="O31" s="32" t="n"/>
-      <c r="P31" s="32" t="n"/>
-      <c r="Q31" s="32" t="n"/>
-      <c r="R31" s="32" t="n"/>
-      <c r="S31" s="32" t="n"/>
-      <c r="T31" s="32" t="n"/>
-      <c r="U31" s="32" t="n"/>
-      <c r="V31" s="33" t="n"/>
-      <c r="W31" s="33" t="n"/>
-      <c r="X31" s="33" t="n"/>
-      <c r="Y31" s="33" t="n"/>
-      <c r="Z31" s="33" t="n"/>
-    </row>
-    <row r="32" ht="18" customHeight="1">
+      <c r="L31" s="31" t="n"/>
+      <c r="M31" s="31" t="n"/>
+      <c r="N31" s="31" t="n"/>
+      <c r="O31" s="31" t="n"/>
+      <c r="P31" s="31" t="n"/>
+      <c r="Q31" s="31" t="n"/>
+      <c r="R31" s="31" t="n"/>
+      <c r="S31" s="31" t="n"/>
+      <c r="T31" s="31" t="n"/>
+      <c r="U31" s="31" t="n"/>
+      <c r="V31" s="31" t="n"/>
+      <c r="W31" s="32" t="n"/>
+      <c r="X31" s="32" t="n"/>
+      <c r="Y31" s="32" t="n"/>
+      <c r="Z31" s="32" t="n"/>
+    </row>
+    <row r="32" ht="21" customHeight="1">
       <c r="B32" s="5" t="inlineStr">
         <is>
           <t>25</t>
@@ -2912,7 +2967,7 @@
       <c r="P32" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q32" s="28" t="n">
+      <c r="Q32" s="27" t="n">
         <v>14</v>
       </c>
       <c r="R32" s="10" t="n">
@@ -2927,13 +2982,15 @@
       <c r="U32" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="V32" s="9" t="n"/>
+      <c r="V32" s="10" t="n">
+        <v>6</v>
+      </c>
       <c r="W32" s="9" t="n"/>
       <c r="X32" s="9" t="n"/>
       <c r="Y32" s="9" t="n"/>
       <c r="Z32" s="9" t="n"/>
     </row>
-    <row r="33" ht="18" customHeight="1">
+    <row r="33" ht="21" customHeight="1">
       <c r="B33" s="5" t="inlineStr">
         <is>
           <t>26</t>
@@ -2997,7 +3054,7 @@
       <c r="P33" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q33" s="28" t="n">
+      <c r="Q33" s="27" t="n">
         <v>3</v>
       </c>
       <c r="R33" s="10" t="n">
@@ -3010,13 +3067,15 @@
       <c r="U33" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="V33" s="9" t="n"/>
+      <c r="V33" s="10" t="n">
+        <v>10</v>
+      </c>
       <c r="W33" s="9" t="n"/>
       <c r="X33" s="9" t="n"/>
       <c r="Y33" s="9" t="n"/>
       <c r="Z33" s="9" t="n"/>
     </row>
-    <row r="34" ht="18" customHeight="1">
+    <row r="34" ht="21" customHeight="1">
       <c r="B34" s="5" t="inlineStr">
         <is>
           <t>27</t>
@@ -3097,13 +3156,15 @@
       <c r="U34" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="V34" s="9" t="n"/>
+      <c r="V34" s="10" t="n">
+        <v>7</v>
+      </c>
       <c r="W34" s="9" t="n"/>
       <c r="X34" s="9" t="n"/>
       <c r="Y34" s="9" t="n"/>
       <c r="Z34" s="9" t="n"/>
     </row>
-    <row r="35" ht="18" customHeight="1">
+    <row r="35" ht="21" customHeight="1">
       <c r="B35" s="5" t="inlineStr">
         <is>
           <t>28</t>
@@ -3169,7 +3230,7 @@
       <c r="P35" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q35" s="28" t="n">
+      <c r="Q35" s="27" t="n">
         <v>17</v>
       </c>
       <c r="R35" s="10" t="n">
@@ -3184,13 +3245,15 @@
       <c r="U35" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="V35" s="9" t="n"/>
+      <c r="V35" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="W35" s="9" t="n"/>
       <c r="X35" s="9" t="n"/>
       <c r="Y35" s="9" t="n"/>
       <c r="Z35" s="9" t="n"/>
     </row>
-    <row r="36" ht="18" customHeight="1">
+    <row r="36" ht="21" customHeight="1">
       <c r="B36" s="5" t="inlineStr">
         <is>
           <t>29</t>
@@ -3256,7 +3319,7 @@
       <c r="P36" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q36" s="28" t="n">
+      <c r="Q36" s="27" t="n">
         <v>7</v>
       </c>
       <c r="R36" s="10" t="n">
@@ -3271,13 +3334,15 @@
       <c r="U36" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="V36" s="9" t="n"/>
+      <c r="V36" s="10" t="n">
+        <v>10</v>
+      </c>
       <c r="W36" s="9" t="n"/>
       <c r="X36" s="9" t="n"/>
       <c r="Y36" s="9" t="n"/>
       <c r="Z36" s="9" t="n"/>
     </row>
-    <row r="37" ht="18" customHeight="1">
+    <row r="37" ht="21" customHeight="1">
       <c r="B37" s="5" t="inlineStr">
         <is>
           <t>30</t>
@@ -3343,7 +3408,7 @@
       <c r="P37" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="Q37" s="28" t="n">
+      <c r="Q37" s="27" t="n">
         <v>17</v>
       </c>
       <c r="R37" s="10" t="n">
@@ -3358,13 +3423,15 @@
       <c r="U37" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="V37" s="9" t="n"/>
+      <c r="V37" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="W37" s="9" t="n"/>
       <c r="X37" s="9" t="n"/>
       <c r="Y37" s="9" t="n"/>
       <c r="Z37" s="9" t="n"/>
     </row>
-    <row r="38" ht="18" customHeight="1">
+    <row r="38" ht="21" customHeight="1">
       <c r="B38" s="5" t="inlineStr">
         <is>
           <t>31</t>
@@ -3428,7 +3495,7 @@
       <c r="P38" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q38" s="28" t="n">
+      <c r="Q38" s="27" t="n">
         <v>16</v>
       </c>
       <c r="R38" s="10" t="n">
@@ -3443,13 +3510,15 @@
       <c r="U38" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="V38" s="9" t="n"/>
+      <c r="V38" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="W38" s="9" t="n"/>
       <c r="X38" s="9" t="n"/>
       <c r="Y38" s="9" t="n"/>
       <c r="Z38" s="9" t="n"/>
     </row>
-    <row r="39" ht="18" customHeight="1">
+    <row r="39" ht="21" customHeight="1">
       <c r="B39" s="5" t="inlineStr">
         <is>
           <t>32</t>
@@ -3515,7 +3584,7 @@
       <c r="P39" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q39" s="28" t="n">
+      <c r="Q39" s="27" t="n">
         <v>22</v>
       </c>
       <c r="R39" s="10" t="n">
@@ -3530,13 +3599,15 @@
       <c r="U39" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="V39" s="9" t="n"/>
+      <c r="V39" s="10" t="n">
+        <v>10</v>
+      </c>
       <c r="W39" s="9" t="n"/>
       <c r="X39" s="9" t="n"/>
       <c r="Y39" s="9" t="n"/>
       <c r="Z39" s="9" t="n"/>
     </row>
-    <row r="40" ht="18" customHeight="1">
+    <row r="40" ht="21" customHeight="1">
       <c r="B40" s="5" t="inlineStr">
         <is>
           <t>33</t>
@@ -3602,7 +3673,7 @@
       <c r="P40" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q40" s="28" t="n">
+      <c r="Q40" s="27" t="n">
         <v>15</v>
       </c>
       <c r="R40" s="10" t="n">
@@ -3617,13 +3688,15 @@
       <c r="U40" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="V40" s="9" t="n"/>
+      <c r="V40" s="10" t="n">
+        <v>8</v>
+      </c>
       <c r="W40" s="9" t="n"/>
       <c r="X40" s="9" t="n"/>
       <c r="Y40" s="9" t="n"/>
       <c r="Z40" s="9" t="n"/>
     </row>
-    <row r="41" ht="18" customHeight="1">
+    <row r="41" ht="21" customHeight="1">
       <c r="B41" s="5" t="inlineStr">
         <is>
           <t>34</t>
@@ -3689,7 +3762,7 @@
       <c r="P41" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q41" s="28" t="n">
+      <c r="Q41" s="27" t="n">
         <v>6</v>
       </c>
       <c r="R41" s="10" t="n">
@@ -3704,13 +3777,15 @@
       <c r="U41" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="V41" s="9" t="n"/>
+      <c r="V41" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="W41" s="9" t="n"/>
       <c r="X41" s="9" t="n"/>
       <c r="Y41" s="9" t="n"/>
       <c r="Z41" s="9" t="n"/>
     </row>
-    <row r="42" ht="18" customHeight="1">
+    <row r="42" ht="21" customHeight="1">
       <c r="B42" s="5" t="inlineStr">
         <is>
           <t>35</t>
@@ -3774,7 +3849,7 @@
         <v>10</v>
       </c>
       <c r="P42" s="10" t="n"/>
-      <c r="Q42" s="28" t="n">
+      <c r="Q42" s="27" t="n">
         <v>4</v>
       </c>
       <c r="R42" s="10" t="n">
@@ -3787,13 +3862,15 @@
       <c r="U42" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="V42" s="9" t="n"/>
+      <c r="V42" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="W42" s="9" t="n"/>
       <c r="X42" s="9" t="n"/>
       <c r="Y42" s="9" t="n"/>
       <c r="Z42" s="9" t="n"/>
     </row>
-    <row r="43" ht="18" customHeight="1">
+    <row r="43" ht="21" customHeight="1">
       <c r="B43" s="5" t="inlineStr">
         <is>
           <t>36</t>
@@ -3859,7 +3936,7 @@
       <c r="P43" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="Q43" s="28" t="n">
+      <c r="Q43" s="27" t="n">
         <v>4</v>
       </c>
       <c r="R43" s="10" t="n">
@@ -3874,13 +3951,15 @@
       <c r="U43" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="V43" s="9" t="n"/>
+      <c r="V43" s="10" t="n">
+        <v>10</v>
+      </c>
       <c r="W43" s="9" t="n"/>
       <c r="X43" s="9" t="n"/>
       <c r="Y43" s="9" t="n"/>
       <c r="Z43" s="9" t="n"/>
     </row>
-    <row r="44" ht="18" customHeight="1">
+    <row r="44" ht="21" customHeight="1">
       <c r="B44" s="5" t="inlineStr">
         <is>
           <t>37</t>
@@ -3946,7 +4025,7 @@
       <c r="P44" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="Q44" s="28" t="n">
+      <c r="Q44" s="27" t="n">
         <v>4</v>
       </c>
       <c r="R44" s="10" t="n">
@@ -3961,13 +4040,15 @@
       <c r="U44" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="V44" s="9" t="n"/>
+      <c r="V44" s="10" t="n">
+        <v>10</v>
+      </c>
       <c r="W44" s="9" t="n"/>
       <c r="X44" s="9" t="n"/>
       <c r="Y44" s="9" t="n"/>
       <c r="Z44" s="9" t="n"/>
     </row>
-    <row r="45" ht="18" customHeight="1">
+    <row r="45" ht="21" customHeight="1">
       <c r="B45" s="5" t="inlineStr">
         <is>
           <t>38</t>
@@ -4033,7 +4114,7 @@
       <c r="P45" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="Q45" s="28" t="n">
+      <c r="Q45" s="27" t="n">
         <v>18</v>
       </c>
       <c r="R45" s="10" t="n">
@@ -4048,13 +4129,15 @@
       <c r="U45" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="V45" s="9" t="n"/>
+      <c r="V45" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="W45" s="9" t="n"/>
       <c r="X45" s="9" t="n"/>
       <c r="Y45" s="9" t="n"/>
       <c r="Z45" s="9" t="n"/>
     </row>
-    <row r="46" ht="18" customHeight="1">
+    <row r="46" ht="21" customHeight="1">
       <c r="B46" s="5" t="inlineStr">
         <is>
           <t>39</t>
@@ -4120,7 +4203,7 @@
       <c r="P46" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q46" s="28" t="n">
+      <c r="Q46" s="27" t="n">
         <v>3</v>
       </c>
       <c r="R46" s="10" t="n">
@@ -4135,13 +4218,15 @@
       <c r="U46" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="V46" s="9" t="n"/>
+      <c r="V46" s="10" t="n">
+        <v>9</v>
+      </c>
       <c r="W46" s="9" t="n"/>
       <c r="X46" s="9" t="n"/>
       <c r="Y46" s="9" t="n"/>
       <c r="Z46" s="9" t="n"/>
     </row>
-    <row r="47" ht="18" customHeight="1">
+    <row r="47" ht="21" customHeight="1">
       <c r="B47" s="5" t="inlineStr">
         <is>
           <t>40</t>
@@ -4207,7 +4292,7 @@
       <c r="P47" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q47" s="28" t="n">
+      <c r="Q47" s="27" t="n">
         <v>13</v>
       </c>
       <c r="R47" s="10" t="n">
@@ -4222,13 +4307,15 @@
       <c r="U47" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="V47" s="9" t="n"/>
+      <c r="V47" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="W47" s="9" t="n"/>
       <c r="X47" s="9" t="n"/>
       <c r="Y47" s="9" t="n"/>
       <c r="Z47" s="9" t="n"/>
     </row>
-    <row r="48" ht="18" customHeight="1">
+    <row r="48" ht="21" customHeight="1">
       <c r="B48" s="5" t="inlineStr">
         <is>
           <t>41</t>
@@ -4294,7 +4381,7 @@
       <c r="P48" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q48" s="28" t="n">
+      <c r="Q48" s="27" t="n">
         <v>6</v>
       </c>
       <c r="R48" s="10" t="n">
@@ -4309,13 +4396,15 @@
       <c r="U48" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="V48" s="9" t="n"/>
+      <c r="V48" s="10" t="n">
+        <v>10</v>
+      </c>
       <c r="W48" s="9" t="n"/>
       <c r="X48" s="9" t="n"/>
       <c r="Y48" s="9" t="n"/>
       <c r="Z48" s="9" t="n"/>
     </row>
-    <row r="49" ht="18" customHeight="1">
+    <row r="49" ht="21" customHeight="1">
       <c r="B49" s="5" t="inlineStr">
         <is>
           <t>42</t>
@@ -4381,7 +4470,7 @@
       <c r="P49" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q49" s="28" t="n">
+      <c r="Q49" s="27" t="n">
         <v>21</v>
       </c>
       <c r="R49" s="10" t="n">
@@ -4396,13 +4485,15 @@
       <c r="U49" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="V49" s="9" t="n"/>
+      <c r="V49" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="W49" s="9" t="n"/>
       <c r="X49" s="9" t="n"/>
       <c r="Y49" s="9" t="n"/>
       <c r="Z49" s="9" t="n"/>
     </row>
-    <row r="50" ht="18" customHeight="1">
+    <row r="50" ht="21" customHeight="1">
       <c r="B50" s="5" t="inlineStr">
         <is>
           <t>43</t>
@@ -4468,7 +4559,7 @@
       <c r="P50" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q50" s="28" t="n">
+      <c r="Q50" s="27" t="n">
         <v>20</v>
       </c>
       <c r="R50" s="10" t="n">
@@ -4483,13 +4574,13 @@
       <c r="U50" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="V50" s="9" t="n"/>
+      <c r="V50" s="10" t="n"/>
       <c r="W50" s="9" t="n"/>
       <c r="X50" s="9" t="n"/>
       <c r="Y50" s="9" t="n"/>
       <c r="Z50" s="9" t="n"/>
     </row>
-    <row r="51" ht="18" customHeight="1">
+    <row r="51" ht="21" customHeight="1">
       <c r="B51" s="5" t="inlineStr">
         <is>
           <t>44</t>
@@ -4553,7 +4644,7 @@
         <v>10</v>
       </c>
       <c r="P51" s="10" t="n"/>
-      <c r="Q51" s="28" t="n">
+      <c r="Q51" s="27" t="n">
         <v>4</v>
       </c>
       <c r="R51" s="10" t="n">
@@ -4566,13 +4657,13 @@
       <c r="U51" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="V51" s="9" t="n"/>
+      <c r="V51" s="10" t="n"/>
       <c r="W51" s="9" t="n"/>
       <c r="X51" s="9" t="n"/>
       <c r="Y51" s="9" t="n"/>
       <c r="Z51" s="9" t="n"/>
     </row>
-    <row r="52" ht="18" customHeight="1">
+    <row r="52" ht="21" customHeight="1">
       <c r="B52" s="5" t="inlineStr">
         <is>
           <t>45</t>
@@ -4638,7 +4729,7 @@
       <c r="P52" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="Q52" s="28" t="n">
+      <c r="Q52" s="27" t="n">
         <v>22</v>
       </c>
       <c r="R52" s="10" t="n">
@@ -4653,13 +4744,15 @@
       <c r="U52" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="V52" s="9" t="n"/>
+      <c r="V52" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="W52" s="9" t="n"/>
       <c r="X52" s="9" t="n"/>
       <c r="Y52" s="9" t="n"/>
       <c r="Z52" s="9" t="n"/>
     </row>
-    <row r="53" ht="18" customHeight="1">
+    <row r="53" ht="21" customHeight="1">
       <c r="B53" s="5" t="inlineStr">
         <is>
           <t>46</t>
@@ -4725,7 +4818,7 @@
       <c r="P53" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Q53" s="28" t="n">
+      <c r="Q53" s="27" t="n">
         <v>19</v>
       </c>
       <c r="R53" s="10" t="n">
@@ -4737,8 +4830,12 @@
       <c r="T53" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="U53" s="10" t="n"/>
-      <c r="V53" s="9" t="n"/>
+      <c r="U53" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="V53" s="10" t="n">
+        <v>8</v>
+      </c>
       <c r="W53" s="9" t="n"/>
       <c r="X53" s="9" t="n"/>
       <c r="Y53" s="9" t="n"/>
@@ -4747,17 +4844,22 @@
     <row r="54">
       <c r="Q54" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="T54" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
+        </is>
+      </c>
+      <c r="T54" s="43" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="V54" s="43" t="inlineStr">
+        <is>
+          <t>  </t>
         </is>
       </c>
     </row>
     <row r="55"/>
-    <row r="56" ht="18" customHeight="1">
+    <row r="56" ht="21" customHeight="1">
       <c r="B56" s="1" t="n"/>
       <c r="G56" s="2" t="inlineStr">
         <is>
@@ -4783,27 +4885,27 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A6:N53"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.6"/>
+  <dimension ref="A6:L53"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.9"/>
   <cols>
-    <col width="6.94921875" customWidth="1" min="1" max="1"/>
-    <col width="16.19921875" customWidth="1" min="2" max="2"/>
-    <col width="31.046875" customWidth="1" min="3" max="3"/>
-    <col width="3.796875" customWidth="1" style="12" min="4" max="4"/>
-    <col width="3.796875" customWidth="1" min="5" max="5"/>
-    <col width="3.796875" customWidth="1" style="18" min="6" max="6"/>
-    <col width="3.796875" customWidth="1" style="41" min="7" max="7"/>
-    <col width="3.796875" customWidth="1" min="8" max="8"/>
-    <col width="3.796875" customWidth="1" style="36" min="9" max="9"/>
-    <col width="3.796875" customWidth="1" style="41" min="10" max="10"/>
-    <col width="3.796875" customWidth="1" min="11" max="14"/>
-    <col width="8.796875" customWidth="1" min="15" max="15"/>
-    <col width="4.6484375" customWidth="1" min="16" max="26"/>
+    <col width="6.92578125" customWidth="1" style="43" min="1" max="1"/>
+    <col width="16.2109375" customWidth="1" min="2" max="2"/>
+    <col width="31.0703125" customWidth="1" min="3" max="3"/>
+    <col width="3.78515625" customWidth="1" style="12" min="4" max="4"/>
+    <col width="3.78515625" customWidth="1" min="5" max="5"/>
+    <col width="3.78515625" customWidth="1" style="18" min="6" max="6"/>
+    <col width="3.78515625" customWidth="1" style="43" min="7" max="7"/>
+    <col width="3.78515625" customWidth="1" min="8" max="8"/>
+    <col width="3.78515625" customWidth="1" style="36" min="9" max="9"/>
+    <col width="3.78515625" customWidth="1" style="43" min="10" max="10"/>
+    <col width="3.78515625" customWidth="1" min="11" max="12"/>
+    <col width="3.85546875" customWidth="1" min="13" max="13"/>
+    <col width="4.640625" customWidth="1" min="14" max="24"/>
   </cols>
   <sheetData>
     <row r="5" ht="19.2" customHeight="1"/>
-    <row r="6" ht="69.59999999999999" customHeight="1">
-      <c r="A6" s="9" t="n"/>
+    <row r="6" ht="69.65000000000001" customHeight="1">
+      <c r="A6" s="10" t="n"/>
       <c r="B6" s="9" t="n"/>
       <c r="C6" s="10" t="inlineStr">
         <is>
@@ -4820,32 +4922,32 @@
           <t>05-20JUL69</t>
         </is>
       </c>
-      <c r="F6" s="42" t="inlineStr">
+      <c r="F6" s="19" t="inlineStr">
         <is>
           <t>06-10/8/1969</t>
         </is>
       </c>
-      <c r="G6" s="43" t="n">
+      <c r="G6" s="33" t="n">
         <v>46258</v>
       </c>
-      <c r="H6" s="43" t="n">
+      <c r="H6" s="33" t="n">
         <v>46265</v>
       </c>
-      <c r="I6" s="44" t="n">
+      <c r="I6" s="37" t="n">
         <v>25460</v>
       </c>
-      <c r="J6" s="39" t="inlineStr">
+      <c r="J6" s="35" t="inlineStr">
         <is>
           <t>21/Sept/2569</t>
         </is>
       </c>
-      <c r="K6" s="17" t="n"/>
-      <c r="L6" s="17" t="n"/>
-      <c r="M6" s="17" t="n"/>
-      <c r="N6" s="17" t="n"/>
+      <c r="K6" s="33" t="n">
+        <v>46307</v>
+      </c>
+      <c r="L6" s="39" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="22">
+      <c r="A7" s="41">
         <f>Exercise!B7</f>
         <v/>
       </c>
@@ -4857,20 +4959,34 @@
         <f>Exercise!D7</f>
         <v/>
       </c>
-      <c r="D7" s="23" t="n"/>
-      <c r="E7" s="23" t="n"/>
-      <c r="F7" s="24" t="n"/>
-      <c r="G7" s="35" t="n"/>
-      <c r="H7" s="23" t="n"/>
-      <c r="I7" s="38" t="n"/>
-      <c r="J7" s="24" t="n"/>
-      <c r="K7" s="23" t="n"/>
-      <c r="L7" s="23" t="n"/>
-      <c r="M7" s="23" t="n"/>
-      <c r="N7" s="23" t="n"/>
+      <c r="D7" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" s="40" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="9">
+      <c r="A8" s="10">
         <f>Exercise!B8</f>
         <v/>
       </c>
@@ -4890,20 +5006,20 @@
         <v>1</v>
       </c>
       <c r="G8" s="10" t="n"/>
-      <c r="H8" s="9" t="n">
+      <c r="H8" s="10" t="n">
         <v>1</v>
       </c>
       <c r="I8" s="38" t="n"/>
       <c r="J8" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="K8" s="9" t="n"/>
-      <c r="L8" s="9" t="n"/>
-      <c r="M8" s="9" t="n"/>
-      <c r="N8" s="9" t="n"/>
+      <c r="K8" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" s="10" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="9">
+      <c r="A9" s="10">
         <f>Exercise!B9</f>
         <v/>
       </c>
@@ -4923,7 +5039,7 @@
       <c r="G9" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="H9" s="9" t="n">
+      <c r="H9" s="10" t="n">
         <v>1</v>
       </c>
       <c r="I9" s="38" t="n">
@@ -4932,13 +5048,13 @@
       <c r="J9" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="K9" s="9" t="n"/>
-      <c r="L9" s="9" t="n"/>
-      <c r="M9" s="9" t="n"/>
-      <c r="N9" s="9" t="n"/>
+      <c r="K9" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" s="10" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="9">
+      <c r="A10" s="10">
         <f>Exercise!B10</f>
         <v/>
       </c>
@@ -4956,20 +5072,20 @@
       </c>
       <c r="F10" s="14" t="n"/>
       <c r="G10" s="10" t="n"/>
-      <c r="H10" s="9" t="n">
+      <c r="H10" s="10" t="n">
         <v>1</v>
       </c>
       <c r="I10" s="38" t="n"/>
       <c r="J10" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="K10" s="9" t="n"/>
-      <c r="L10" s="9" t="n"/>
-      <c r="M10" s="9" t="n"/>
-      <c r="N10" s="9" t="n"/>
+      <c r="K10" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" s="10" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="9">
+      <c r="A11" s="10">
         <f>Exercise!B11</f>
         <v/>
       </c>
@@ -4993,7 +5109,7 @@
       <c r="G11" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="H11" s="9" t="n">
+      <c r="H11" s="10" t="n">
         <v>1</v>
       </c>
       <c r="I11" s="38" t="n">
@@ -5002,13 +5118,13 @@
       <c r="J11" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="K11" s="9" t="n"/>
-      <c r="L11" s="9" t="n"/>
-      <c r="M11" s="9" t="n"/>
-      <c r="N11" s="9" t="n"/>
+      <c r="K11" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" s="10" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="9">
+      <c r="A12" s="10">
         <f>Exercise!B12</f>
         <v/>
       </c>
@@ -5032,7 +5148,7 @@
       <c r="G12" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="H12" s="9" t="n">
+      <c r="H12" s="10" t="n">
         <v>1</v>
       </c>
       <c r="I12" s="38" t="n">
@@ -5041,13 +5157,11 @@
       <c r="J12" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="K12" s="9" t="n"/>
-      <c r="L12" s="9" t="n"/>
-      <c r="M12" s="9" t="n"/>
-      <c r="N12" s="9" t="n"/>
+      <c r="K12" s="10" t="n"/>
+      <c r="L12" s="10" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="9">
+      <c r="A13" s="10">
         <f>Exercise!B13</f>
         <v/>
       </c>
@@ -5067,7 +5181,7 @@
       <c r="G13" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="H13" s="9" t="n">
+      <c r="H13" s="10" t="n">
         <v>1</v>
       </c>
       <c r="I13" s="38" t="n">
@@ -5076,13 +5190,11 @@
       <c r="J13" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="K13" s="9" t="n"/>
-      <c r="L13" s="9" t="n"/>
-      <c r="M13" s="9" t="n"/>
-      <c r="N13" s="9" t="n"/>
+      <c r="K13" s="10" t="n"/>
+      <c r="L13" s="10" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="9">
+      <c r="A14" s="10">
         <f>Exercise!B14</f>
         <v/>
       </c>
@@ -5104,20 +5216,20 @@
       <c r="G14" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="H14" s="9" t="n"/>
+      <c r="H14" s="10" t="n"/>
       <c r="I14" s="38" t="n">
         <v>1</v>
       </c>
       <c r="J14" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="K14" s="9" t="n"/>
-      <c r="L14" s="9" t="n"/>
-      <c r="M14" s="9" t="n"/>
-      <c r="N14" s="9" t="n"/>
+      <c r="K14" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" s="10" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="9">
+      <c r="A15" s="10">
         <f>Exercise!B15</f>
         <v/>
       </c>
@@ -5141,7 +5253,7 @@
       <c r="G15" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="H15" s="9" t="n">
+      <c r="H15" s="10" t="n">
         <v>1</v>
       </c>
       <c r="I15" s="38" t="n">
@@ -5150,13 +5262,13 @@
       <c r="J15" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="K15" s="9" t="n"/>
-      <c r="L15" s="9" t="n"/>
-      <c r="M15" s="9" t="n"/>
-      <c r="N15" s="9" t="n"/>
+      <c r="K15" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" s="10" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="9">
+      <c r="A16" s="10">
         <f>Exercise!B16</f>
         <v/>
       </c>
@@ -5180,7 +5292,7 @@
       <c r="G16" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="H16" s="9" t="n">
+      <c r="H16" s="10" t="n">
         <v>1</v>
       </c>
       <c r="I16" s="38" t="n">
@@ -5189,13 +5301,11 @@
       <c r="J16" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="K16" s="9" t="n"/>
-      <c r="L16" s="9" t="n"/>
-      <c r="M16" s="9" t="n"/>
-      <c r="N16" s="9" t="n"/>
+      <c r="K16" s="10" t="n"/>
+      <c r="L16" s="10" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="9">
+      <c r="A17" s="10">
         <f>Exercise!B17</f>
         <v/>
       </c>
@@ -5219,7 +5329,7 @@
       <c r="G17" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="H17" s="9" t="n">
+      <c r="H17" s="10" t="n">
         <v>1</v>
       </c>
       <c r="I17" s="38" t="n">
@@ -5228,13 +5338,13 @@
       <c r="J17" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="K17" s="9" t="n"/>
-      <c r="L17" s="9" t="n"/>
-      <c r="M17" s="9" t="n"/>
-      <c r="N17" s="9" t="n"/>
+      <c r="K17" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" s="10" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="9">
+      <c r="A18" s="10">
         <f>Exercise!B18</f>
         <v/>
       </c>
@@ -5256,7 +5366,7 @@
       <c r="G18" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="H18" s="9" t="n">
+      <c r="H18" s="10" t="n">
         <v>1</v>
       </c>
       <c r="I18" s="38" t="n">
@@ -5265,13 +5375,13 @@
       <c r="J18" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="K18" s="9" t="n"/>
-      <c r="L18" s="9" t="n"/>
-      <c r="M18" s="9" t="n"/>
-      <c r="N18" s="9" t="n"/>
+      <c r="K18" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L18" s="10" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="9">
+      <c r="A19" s="10">
         <f>Exercise!B19</f>
         <v/>
       </c>
@@ -5291,7 +5401,7 @@
       <c r="G19" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="H19" s="9" t="n">
+      <c r="H19" s="10" t="n">
         <v>1</v>
       </c>
       <c r="I19" s="38" t="n">
@@ -5300,13 +5410,11 @@
       <c r="J19" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="K19" s="9" t="n"/>
-      <c r="L19" s="9" t="n"/>
-      <c r="M19" s="9" t="n"/>
-      <c r="N19" s="9" t="n"/>
+      <c r="K19" s="10" t="n"/>
+      <c r="L19" s="10" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="9">
+      <c r="A20" s="10">
         <f>Exercise!B20</f>
         <v/>
       </c>
@@ -5326,7 +5434,7 @@
       <c r="G20" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="H20" s="9" t="n">
+      <c r="H20" s="10" t="n">
         <v>1</v>
       </c>
       <c r="I20" s="38" t="n">
@@ -5335,13 +5443,13 @@
       <c r="J20" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="K20" s="9" t="n"/>
-      <c r="L20" s="9" t="n"/>
-      <c r="M20" s="9" t="n"/>
-      <c r="N20" s="9" t="n"/>
+      <c r="K20" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" s="10" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="9">
+      <c r="A21" s="10">
         <f>Exercise!B21</f>
         <v/>
       </c>
@@ -5361,18 +5469,16 @@
       </c>
       <c r="F21" s="14" t="n"/>
       <c r="G21" s="10" t="n"/>
-      <c r="H21" s="9" t="n"/>
+      <c r="H21" s="10" t="n"/>
       <c r="I21" s="38" t="n"/>
       <c r="J21" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="K21" s="9" t="n"/>
-      <c r="L21" s="9" t="n"/>
-      <c r="M21" s="9" t="n"/>
-      <c r="N21" s="9" t="n"/>
+      <c r="K21" s="10" t="n"/>
+      <c r="L21" s="10" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="9">
+      <c r="A22" s="10">
         <f>Exercise!B22</f>
         <v/>
       </c>
@@ -5396,20 +5502,20 @@
       <c r="G22" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="H22" s="9" t="n">
+      <c r="H22" s="10" t="n">
         <v>1</v>
       </c>
       <c r="I22" s="38" t="n">
         <v>1</v>
       </c>
       <c r="J22" s="10" t="n"/>
-      <c r="K22" s="9" t="n"/>
-      <c r="L22" s="9" t="n"/>
-      <c r="M22" s="9" t="n"/>
-      <c r="N22" s="9" t="n"/>
+      <c r="K22" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" s="10" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="9">
+      <c r="A23" s="10">
         <f>Exercise!B23</f>
         <v/>
       </c>
@@ -5433,7 +5539,7 @@
       <c r="G23" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="H23" s="9" t="n">
+      <c r="H23" s="10" t="n">
         <v>1</v>
       </c>
       <c r="I23" s="38" t="n">
@@ -5442,13 +5548,13 @@
       <c r="J23" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="K23" s="9" t="n"/>
-      <c r="L23" s="9" t="n"/>
-      <c r="M23" s="9" t="n"/>
-      <c r="N23" s="9" t="n"/>
+      <c r="K23" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L23" s="10" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="9">
+      <c r="A24" s="10">
         <f>Exercise!B24</f>
         <v/>
       </c>
@@ -5472,7 +5578,7 @@
       <c r="G24" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="H24" s="9" t="n">
+      <c r="H24" s="10" t="n">
         <v>1</v>
       </c>
       <c r="I24" s="38" t="n">
@@ -5481,13 +5587,13 @@
       <c r="J24" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="K24" s="9" t="n"/>
-      <c r="L24" s="9" t="n"/>
-      <c r="M24" s="9" t="n"/>
-      <c r="N24" s="9" t="n"/>
+      <c r="K24" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L24" s="10" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="9">
+      <c r="A25" s="10">
         <f>Exercise!B25</f>
         <v/>
       </c>
@@ -5511,7 +5617,7 @@
       <c r="G25" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="H25" s="9" t="n">
+      <c r="H25" s="10" t="n">
         <v>1</v>
       </c>
       <c r="I25" s="38" t="n">
@@ -5520,13 +5626,13 @@
       <c r="J25" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="K25" s="9" t="n"/>
-      <c r="L25" s="9" t="n"/>
-      <c r="M25" s="9" t="n"/>
-      <c r="N25" s="9" t="n"/>
+      <c r="K25" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L25" s="10" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="9">
+      <c r="A26" s="10">
         <f>Exercise!B26</f>
         <v/>
       </c>
@@ -5550,7 +5656,7 @@
       <c r="G26" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="H26" s="9" t="n">
+      <c r="H26" s="10" t="n">
         <v>1</v>
       </c>
       <c r="I26" s="38" t="n">
@@ -5559,13 +5665,13 @@
       <c r="J26" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="K26" s="9" t="n"/>
-      <c r="L26" s="9" t="n"/>
-      <c r="M26" s="9" t="n"/>
-      <c r="N26" s="9" t="n"/>
+      <c r="K26" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L26" s="10" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="9">
+      <c r="A27" s="10">
         <f>Exercise!B27</f>
         <v/>
       </c>
@@ -5587,7 +5693,7 @@
       <c r="G27" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="H27" s="9" t="n">
+      <c r="H27" s="10" t="n">
         <v>1</v>
       </c>
       <c r="I27" s="38" t="n">
@@ -5596,13 +5702,13 @@
       <c r="J27" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="K27" s="9" t="n"/>
-      <c r="L27" s="9" t="n"/>
-      <c r="M27" s="9" t="n"/>
-      <c r="N27" s="9" t="n"/>
+      <c r="K27" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L27" s="10" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="9">
+      <c r="A28" s="10">
         <f>Exercise!B28</f>
         <v/>
       </c>
@@ -5624,18 +5730,18 @@
       <c r="G28" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="H28" s="9" t="n"/>
+      <c r="H28" s="10" t="n"/>
       <c r="I28" s="38" t="n">
         <v>1</v>
       </c>
       <c r="J28" s="10" t="n"/>
-      <c r="K28" s="9" t="n"/>
-      <c r="L28" s="9" t="n"/>
-      <c r="M28" s="9" t="n"/>
-      <c r="N28" s="9" t="n"/>
+      <c r="K28" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L28" s="10" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="9">
+      <c r="A29" s="10">
         <f>Exercise!B29</f>
         <v/>
       </c>
@@ -5659,7 +5765,7 @@
       <c r="G29" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="H29" s="9" t="n">
+      <c r="H29" s="10" t="n">
         <v>1</v>
       </c>
       <c r="I29" s="38" t="n">
@@ -5668,13 +5774,13 @@
       <c r="J29" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="K29" s="9" t="n"/>
-      <c r="L29" s="9" t="n"/>
-      <c r="M29" s="9" t="n"/>
-      <c r="N29" s="9" t="n"/>
+      <c r="K29" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L29" s="10" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="9">
+      <c r="A30" s="10">
         <f>Exercise!B30</f>
         <v/>
       </c>
@@ -5698,7 +5804,7 @@
       <c r="G30" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="H30" s="9" t="n">
+      <c r="H30" s="10" t="n">
         <v>1</v>
       </c>
       <c r="I30" s="38" t="n">
@@ -5707,13 +5813,13 @@
       <c r="J30" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="K30" s="9" t="n"/>
-      <c r="L30" s="9" t="n"/>
-      <c r="M30" s="9" t="n"/>
-      <c r="N30" s="9" t="n"/>
+      <c r="K30" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L30" s="10" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="9">
+      <c r="A31" s="10">
         <f>Exercise!B31</f>
         <v/>
       </c>
@@ -5729,16 +5835,14 @@
       <c r="E31" s="15" t="n"/>
       <c r="F31" s="14" t="n"/>
       <c r="G31" s="10" t="n"/>
-      <c r="H31" s="9" t="n"/>
+      <c r="H31" s="10" t="n"/>
       <c r="I31" s="38" t="n"/>
       <c r="J31" s="10" t="n"/>
-      <c r="K31" s="9" t="n"/>
-      <c r="L31" s="9" t="n"/>
-      <c r="M31" s="9" t="n"/>
-      <c r="N31" s="9" t="n"/>
+      <c r="K31" s="10" t="n"/>
+      <c r="L31" s="10" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="9">
+      <c r="A32" s="10">
         <f>Exercise!B32</f>
         <v/>
       </c>
@@ -5762,7 +5866,7 @@
       <c r="G32" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="H32" s="9" t="n">
+      <c r="H32" s="10" t="n">
         <v>1</v>
       </c>
       <c r="I32" s="38" t="n">
@@ -5771,13 +5875,13 @@
       <c r="J32" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="K32" s="9" t="n"/>
-      <c r="L32" s="9" t="n"/>
-      <c r="M32" s="9" t="n"/>
-      <c r="N32" s="9" t="n"/>
+      <c r="K32" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L32" s="10" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="9">
+      <c r="A33" s="10">
         <f>Exercise!B33</f>
         <v/>
       </c>
@@ -5799,7 +5903,7 @@
       <c r="G33" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="H33" s="9" t="n">
+      <c r="H33" s="10" t="n">
         <v>1</v>
       </c>
       <c r="I33" s="38" t="n">
@@ -5808,13 +5912,13 @@
       <c r="J33" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="K33" s="9" t="n"/>
-      <c r="L33" s="9" t="n"/>
-      <c r="M33" s="9" t="n"/>
-      <c r="N33" s="9" t="n"/>
+      <c r="K33" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L33" s="10" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="9">
+      <c r="A34" s="10">
         <f>Exercise!B34</f>
         <v/>
       </c>
@@ -5838,7 +5942,7 @@
       <c r="G34" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="H34" s="9" t="n">
+      <c r="H34" s="10" t="n">
         <v>1</v>
       </c>
       <c r="I34" s="38" t="n">
@@ -5847,13 +5951,13 @@
       <c r="J34" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="K34" s="9" t="n"/>
-      <c r="L34" s="9" t="n"/>
-      <c r="M34" s="9" t="n"/>
-      <c r="N34" s="9" t="n"/>
+      <c r="K34" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L34" s="10" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="9">
+      <c r="A35" s="10">
         <f>Exercise!B35</f>
         <v/>
       </c>
@@ -5877,7 +5981,7 @@
       <c r="G35" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="H35" s="9" t="n">
+      <c r="H35" s="10" t="n">
         <v>1</v>
       </c>
       <c r="I35" s="38" t="n">
@@ -5886,13 +5990,13 @@
       <c r="J35" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="K35" s="9" t="n"/>
-      <c r="L35" s="9" t="n"/>
-      <c r="M35" s="9" t="n"/>
-      <c r="N35" s="9" t="n"/>
+      <c r="K35" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L35" s="10" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="9">
+      <c r="A36" s="10">
         <f>Exercise!B36</f>
         <v/>
       </c>
@@ -5916,20 +6020,20 @@
       <c r="G36" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="H36" s="9" t="n"/>
+      <c r="H36" s="10" t="n"/>
       <c r="I36" s="38" t="n">
         <v>1</v>
       </c>
       <c r="J36" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="K36" s="9" t="n"/>
-      <c r="L36" s="9" t="n"/>
-      <c r="M36" s="9" t="n"/>
-      <c r="N36" s="9" t="n"/>
+      <c r="K36" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L36" s="10" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="9">
+      <c r="A37" s="10">
         <f>Exercise!B37</f>
         <v/>
       </c>
@@ -5953,7 +6057,7 @@
       <c r="G37" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="H37" s="9" t="n">
+      <c r="H37" s="10" t="n">
         <v>1</v>
       </c>
       <c r="I37" s="38" t="n">
@@ -5962,13 +6066,13 @@
       <c r="J37" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="K37" s="9" t="n"/>
-      <c r="L37" s="9" t="n"/>
-      <c r="M37" s="9" t="n"/>
-      <c r="N37" s="9" t="n"/>
+      <c r="K37" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L37" s="10" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="9">
+      <c r="A38" s="10">
         <f>Exercise!B38</f>
         <v/>
       </c>
@@ -5990,7 +6094,7 @@
       <c r="G38" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="H38" s="9" t="n">
+      <c r="H38" s="10" t="n">
         <v>1</v>
       </c>
       <c r="I38" s="38" t="n">
@@ -5999,13 +6103,13 @@
       <c r="J38" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="K38" s="9" t="n"/>
-      <c r="L38" s="9" t="n"/>
-      <c r="M38" s="9" t="n"/>
-      <c r="N38" s="9" t="n"/>
+      <c r="K38" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L38" s="10" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="9">
+      <c r="A39" s="10">
         <f>Exercise!B39</f>
         <v/>
       </c>
@@ -6029,7 +6133,7 @@
       <c r="G39" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="H39" s="9" t="n">
+      <c r="H39" s="10" t="n">
         <v>1</v>
       </c>
       <c r="I39" s="38" t="n">
@@ -6038,13 +6142,13 @@
       <c r="J39" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="K39" s="9" t="n"/>
-      <c r="L39" s="9" t="n"/>
-      <c r="M39" s="9" t="n"/>
-      <c r="N39" s="9" t="n"/>
+      <c r="K39" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L39" s="10" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="9">
+      <c r="A40" s="10">
         <f>Exercise!B40</f>
         <v/>
       </c>
@@ -6068,20 +6172,20 @@
       <c r="G40" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="H40" s="9" t="n">
+      <c r="H40" s="10" t="n">
         <v>1</v>
       </c>
       <c r="I40" s="38" t="n">
         <v>1</v>
       </c>
       <c r="J40" s="10" t="n"/>
-      <c r="K40" s="9" t="n"/>
-      <c r="L40" s="9" t="n"/>
-      <c r="M40" s="9" t="n"/>
-      <c r="N40" s="9" t="n"/>
+      <c r="K40" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L40" s="10" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="9">
+      <c r="A41" s="10">
         <f>Exercise!B41</f>
         <v/>
       </c>
@@ -6105,7 +6209,7 @@
       <c r="G41" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="H41" s="9" t="n">
+      <c r="H41" s="10" t="n">
         <v>1</v>
       </c>
       <c r="I41" s="38" t="n">
@@ -6114,13 +6218,13 @@
       <c r="J41" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="K41" s="9" t="n"/>
-      <c r="L41" s="9" t="n"/>
-      <c r="M41" s="9" t="n"/>
-      <c r="N41" s="9" t="n"/>
+      <c r="K41" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L41" s="10" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="9">
+      <c r="A42" s="10">
         <f>Exercise!B42</f>
         <v/>
       </c>
@@ -6144,7 +6248,7 @@
       <c r="G42" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="H42" s="9" t="n">
+      <c r="H42" s="10" t="n">
         <v>1</v>
       </c>
       <c r="I42" s="38" t="n">
@@ -6153,13 +6257,13 @@
       <c r="J42" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="K42" s="9" t="n"/>
-      <c r="L42" s="9" t="n"/>
-      <c r="M42" s="9" t="n"/>
-      <c r="N42" s="9" t="n"/>
+      <c r="K42" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L42" s="10" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="9">
+      <c r="A43" s="10">
         <f>Exercise!B43</f>
         <v/>
       </c>
@@ -6183,7 +6287,7 @@
       <c r="G43" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="H43" s="9" t="n">
+      <c r="H43" s="10" t="n">
         <v>1</v>
       </c>
       <c r="I43" s="38" t="n">
@@ -6192,13 +6296,13 @@
       <c r="J43" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="K43" s="9" t="n"/>
-      <c r="L43" s="9" t="n"/>
-      <c r="M43" s="9" t="n"/>
-      <c r="N43" s="9" t="n"/>
+      <c r="K43" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L43" s="10" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="9">
+      <c r="A44" s="10">
         <f>Exercise!B44</f>
         <v/>
       </c>
@@ -6222,7 +6326,7 @@
       <c r="G44" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="H44" s="9" t="n">
+      <c r="H44" s="10" t="n">
         <v>1</v>
       </c>
       <c r="I44" s="38" t="n">
@@ -6231,13 +6335,13 @@
       <c r="J44" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="K44" s="9" t="n"/>
-      <c r="L44" s="9" t="n"/>
-      <c r="M44" s="9" t="n"/>
-      <c r="N44" s="9" t="n"/>
+      <c r="K44" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L44" s="10" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="9">
+      <c r="A45" s="10">
         <f>Exercise!B45</f>
         <v/>
       </c>
@@ -6261,7 +6365,7 @@
       <c r="G45" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="H45" s="9" t="n">
+      <c r="H45" s="10" t="n">
         <v>1</v>
       </c>
       <c r="I45" s="38" t="n">
@@ -6270,13 +6374,13 @@
       <c r="J45" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="K45" s="9" t="n"/>
-      <c r="L45" s="9" t="n"/>
-      <c r="M45" s="9" t="n"/>
-      <c r="N45" s="9" t="n"/>
+      <c r="K45" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L45" s="10" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="9">
+      <c r="A46" s="10">
         <f>Exercise!B46</f>
         <v/>
       </c>
@@ -6300,7 +6404,7 @@
       <c r="G46" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="H46" s="9" t="n">
+      <c r="H46" s="10" t="n">
         <v>1</v>
       </c>
       <c r="I46" s="38" t="n">
@@ -6309,13 +6413,13 @@
       <c r="J46" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="K46" s="9" t="n"/>
-      <c r="L46" s="9" t="n"/>
-      <c r="M46" s="9" t="n"/>
-      <c r="N46" s="9" t="n"/>
+      <c r="K46" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L46" s="10" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="9">
+      <c r="A47" s="10">
         <f>Exercise!B47</f>
         <v/>
       </c>
@@ -6339,7 +6443,7 @@
       <c r="G47" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="H47" s="9" t="n">
+      <c r="H47" s="10" t="n">
         <v>1</v>
       </c>
       <c r="I47" s="38" t="n">
@@ -6348,13 +6452,11 @@
       <c r="J47" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="K47" s="9" t="n"/>
-      <c r="L47" s="9" t="n"/>
-      <c r="M47" s="9" t="n"/>
-      <c r="N47" s="9" t="n"/>
+      <c r="K47" s="10" t="n"/>
+      <c r="L47" s="10" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="9">
+      <c r="A48" s="10">
         <f>Exercise!B48</f>
         <v/>
       </c>
@@ -6378,7 +6480,7 @@
       <c r="G48" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="H48" s="9" t="n">
+      <c r="H48" s="10" t="n">
         <v>1</v>
       </c>
       <c r="I48" s="38" t="n">
@@ -6387,13 +6489,13 @@
       <c r="J48" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="K48" s="9" t="n"/>
-      <c r="L48" s="9" t="n"/>
-      <c r="M48" s="9" t="n"/>
-      <c r="N48" s="9" t="n"/>
+      <c r="K48" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L48" s="10" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="9">
+      <c r="A49" s="10">
         <f>Exercise!B49</f>
         <v/>
       </c>
@@ -6417,7 +6519,7 @@
       <c r="G49" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="H49" s="9" t="n">
+      <c r="H49" s="10" t="n">
         <v>1</v>
       </c>
       <c r="I49" s="38" t="n">
@@ -6426,13 +6528,13 @@
       <c r="J49" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="K49" s="9" t="n"/>
-      <c r="L49" s="9" t="n"/>
-      <c r="M49" s="9" t="n"/>
-      <c r="N49" s="9" t="n"/>
+      <c r="K49" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L49" s="10" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="9">
+      <c r="A50" s="10">
         <f>Exercise!B50</f>
         <v/>
       </c>
@@ -6456,7 +6558,7 @@
       <c r="G50" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="H50" s="9" t="n">
+      <c r="H50" s="10" t="n">
         <v>1</v>
       </c>
       <c r="I50" s="38" t="n">
@@ -6465,13 +6567,13 @@
       <c r="J50" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="K50" s="9" t="n"/>
-      <c r="L50" s="9" t="n"/>
-      <c r="M50" s="9" t="n"/>
-      <c r="N50" s="9" t="n"/>
+      <c r="K50" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L50" s="10" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="9">
+      <c r="A51" s="10">
         <f>Exercise!B51</f>
         <v/>
       </c>
@@ -6495,7 +6597,7 @@
       <c r="G51" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="H51" s="9" t="n">
+      <c r="H51" s="10" t="n">
         <v>1</v>
       </c>
       <c r="I51" s="38" t="n">
@@ -6504,13 +6606,13 @@
       <c r="J51" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="K51" s="9" t="n"/>
-      <c r="L51" s="9" t="n"/>
-      <c r="M51" s="9" t="n"/>
-      <c r="N51" s="9" t="n"/>
+      <c r="K51" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L51" s="10" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="9">
+      <c r="A52" s="10">
         <f>Exercise!B52</f>
         <v/>
       </c>
@@ -6534,7 +6636,7 @@
       <c r="G52" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="H52" s="9" t="n">
+      <c r="H52" s="10" t="n">
         <v>1</v>
       </c>
       <c r="I52" s="38" t="n">
@@ -6543,13 +6645,13 @@
       <c r="J52" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="K52" s="9" t="n"/>
-      <c r="L52" s="9" t="n"/>
-      <c r="M52" s="9" t="n"/>
-      <c r="N52" s="9" t="n"/>
+      <c r="K52" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L52" s="10" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="9">
+      <c r="A53" s="10">
         <f>Exercise!B53</f>
         <v/>
       </c>
@@ -6573,7 +6675,7 @@
       <c r="G53" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="H53" s="9" t="n">
+      <c r="H53" s="10" t="n">
         <v>1</v>
       </c>
       <c r="I53" s="38" t="n">
@@ -6582,10 +6684,10 @@
       <c r="J53" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="K53" s="9" t="n"/>
-      <c r="L53" s="9" t="n"/>
-      <c r="M53" s="9" t="n"/>
-      <c r="N53" s="9" t="n"/>
+      <c r="K53" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L53" s="10" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6616,2204 +6718,2204 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="45" t="inlineStr">
+      <c r="A1" s="44" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B1" s="45" t="inlineStr">
+      <c r="B1" s="44" t="inlineStr">
         <is>
           <t>Student ID</t>
         </is>
       </c>
-      <c r="C1" s="45" t="inlineStr">
+      <c r="C1" s="44" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="D1" s="45" t="inlineStr">
+      <c r="D1" s="44" t="inlineStr">
         <is>
           <t>Exercise Raw</t>
         </is>
       </c>
-      <c r="E1" s="45" t="inlineStr">
+      <c r="E1" s="44" t="inlineStr">
         <is>
           <t>Exercise %</t>
         </is>
       </c>
-      <c r="F1" s="45" t="inlineStr">
+      <c r="F1" s="44" t="inlineStr">
         <is>
           <t>Exercise 70%</t>
         </is>
       </c>
-      <c r="G1" s="45" t="inlineStr">
+      <c r="G1" s="44" t="inlineStr">
         <is>
           <t>Attendance</t>
         </is>
       </c>
-      <c r="H1" s="45" t="inlineStr">
+      <c r="H1" s="44" t="inlineStr">
         <is>
           <t>Attendance %</t>
         </is>
       </c>
-      <c r="I1" s="45" t="inlineStr">
+      <c r="I1" s="44" t="inlineStr">
         <is>
           <t>Attendance 30%</t>
         </is>
       </c>
-      <c r="J1" s="45" t="inlineStr">
+      <c r="J1" s="44" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="K1" s="45" t="inlineStr">
+      <c r="K1" s="44" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="46" t="inlineStr">
+      <c r="A2" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="45" t="inlineStr">
         <is>
           <t>6610553157</t>
         </is>
       </c>
-      <c r="C2" s="47" t="inlineStr">
+      <c r="C2" s="46" t="inlineStr">
         <is>
           <t>----</t>
         </is>
       </c>
-      <c r="D2" s="46" t="inlineStr">
-        <is>
-          <t>47.00/118.00</t>
-        </is>
-      </c>
-      <c r="E2" s="48" t="n">
-        <v>39.83050847457627</v>
-      </c>
-      <c r="F2" s="48" t="n">
-        <v>27.88135593220339</v>
-      </c>
-      <c r="G2" s="46" t="inlineStr">
-        <is>
-          <t>4/7</t>
-        </is>
-      </c>
-      <c r="H2" s="48" t="n">
-        <v>57.14285714285714</v>
-      </c>
-      <c r="I2" s="48" t="n">
-        <v>17.14285714285714</v>
-      </c>
-      <c r="J2" s="48" t="n">
-        <v>45.02421307506053</v>
-      </c>
-      <c r="K2" s="46" t="inlineStr">
+      <c r="D2" s="45" t="inlineStr">
+        <is>
+          <t>50.00/128.00</t>
+        </is>
+      </c>
+      <c r="E2" s="47" t="n">
+        <v>39.0625</v>
+      </c>
+      <c r="F2" s="47" t="n">
+        <v>27.34375</v>
+      </c>
+      <c r="G2" s="45" t="inlineStr">
+        <is>
+          <t>5/8</t>
+        </is>
+      </c>
+      <c r="H2" s="47" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="I2" s="47" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="J2" s="47" t="n">
+        <v>46.09375</v>
+      </c>
+      <c r="K2" s="45" t="inlineStr">
         <is>
           <t>★☆☆☆☆</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="46" t="n">
+      <c r="A3" s="45" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="46" t="inlineStr">
+      <c r="B3" s="45" t="inlineStr">
         <is>
           <t>6610553165</t>
         </is>
       </c>
-      <c r="C3" s="47" t="inlineStr">
+      <c r="C3" s="46" t="inlineStr">
         <is>
           <t>----</t>
         </is>
       </c>
-      <c r="D3" s="46" t="inlineStr">
-        <is>
-          <t>53.00/118.00</t>
-        </is>
-      </c>
-      <c r="E3" s="48" t="n">
-        <v>44.91525423728814</v>
-      </c>
-      <c r="F3" s="48" t="n">
-        <v>31.4406779661017</v>
-      </c>
-      <c r="G3" s="46" t="inlineStr">
-        <is>
-          <t>5/7</t>
-        </is>
-      </c>
-      <c r="H3" s="48" t="n">
-        <v>71.42857142857143</v>
-      </c>
-      <c r="I3" s="48" t="n">
-        <v>21.42857142857143</v>
-      </c>
-      <c r="J3" s="48" t="n">
-        <v>52.86924939467313</v>
-      </c>
-      <c r="K3" s="46" t="inlineStr">
+      <c r="D3" s="45" t="inlineStr">
+        <is>
+          <t>62.00/128.00</t>
+        </is>
+      </c>
+      <c r="E3" s="47" t="n">
+        <v>48.4375</v>
+      </c>
+      <c r="F3" s="47" t="n">
+        <v>33.90625</v>
+      </c>
+      <c r="G3" s="45" t="inlineStr">
+        <is>
+          <t>6/8</t>
+        </is>
+      </c>
+      <c r="H3" s="47" t="n">
+        <v>75</v>
+      </c>
+      <c r="I3" s="47" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="J3" s="47" t="n">
+        <v>56.40625</v>
+      </c>
+      <c r="K3" s="45" t="inlineStr">
         <is>
           <t>★☆☆☆☆</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="46" t="n">
+      <c r="A4" s="45" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="46" t="inlineStr">
+      <c r="B4" s="45" t="inlineStr">
         <is>
           <t>6610553173</t>
         </is>
       </c>
-      <c r="C4" s="47" t="inlineStr">
+      <c r="C4" s="46" t="inlineStr">
         <is>
           <t>----</t>
         </is>
       </c>
-      <c r="D4" s="46" t="inlineStr">
-        <is>
-          <t>50.00/118.00</t>
-        </is>
-      </c>
-      <c r="E4" s="48" t="n">
-        <v>42.3728813559322</v>
-      </c>
-      <c r="F4" s="48" t="n">
-        <v>29.66101694915254</v>
-      </c>
-      <c r="G4" s="46" t="inlineStr">
-        <is>
-          <t>3/7</t>
-        </is>
-      </c>
-      <c r="H4" s="48" t="n">
-        <v>42.85714285714285</v>
-      </c>
-      <c r="I4" s="48" t="n">
-        <v>12.85714285714286</v>
-      </c>
-      <c r="J4" s="48" t="n">
-        <v>42.51815980629539</v>
-      </c>
-      <c r="K4" s="46" t="inlineStr">
+      <c r="D4" s="45" t="inlineStr">
+        <is>
+          <t>50.00/128.00</t>
+        </is>
+      </c>
+      <c r="E4" s="47" t="n">
+        <v>39.0625</v>
+      </c>
+      <c r="F4" s="47" t="n">
+        <v>27.34375</v>
+      </c>
+      <c r="G4" s="45" t="inlineStr">
+        <is>
+          <t>4/8</t>
+        </is>
+      </c>
+      <c r="H4" s="47" t="n">
+        <v>50</v>
+      </c>
+      <c r="I4" s="47" t="n">
+        <v>15</v>
+      </c>
+      <c r="J4" s="47" t="n">
+        <v>42.34375</v>
+      </c>
+      <c r="K4" s="45" t="inlineStr">
         <is>
           <t>★☆☆☆☆</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="46" t="n">
+      <c r="A5" s="45" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="46" t="inlineStr">
+      <c r="B5" s="45" t="inlineStr">
         <is>
           <t>6610553181</t>
         </is>
       </c>
-      <c r="C5" s="47" t="inlineStr">
+      <c r="C5" s="46" t="inlineStr">
         <is>
           <t>----</t>
         </is>
       </c>
-      <c r="D5" s="46" t="inlineStr">
-        <is>
-          <t>78.00/118.00</t>
-        </is>
-      </c>
-      <c r="E5" s="48" t="n">
-        <v>66.10169491525424</v>
-      </c>
-      <c r="F5" s="48" t="n">
-        <v>46.27118644067797</v>
-      </c>
-      <c r="G5" s="46" t="inlineStr">
-        <is>
-          <t>7/7</t>
-        </is>
-      </c>
-      <c r="H5" s="48" t="n">
+      <c r="D5" s="45" t="inlineStr">
+        <is>
+          <t>84.00/128.00</t>
+        </is>
+      </c>
+      <c r="E5" s="47" t="n">
+        <v>65.625</v>
+      </c>
+      <c r="F5" s="47" t="n">
+        <v>45.9375</v>
+      </c>
+      <c r="G5" s="45" t="inlineStr">
+        <is>
+          <t>8/8</t>
+        </is>
+      </c>
+      <c r="H5" s="47" t="n">
         <v>100</v>
       </c>
-      <c r="I5" s="48" t="n">
+      <c r="I5" s="47" t="n">
         <v>30</v>
       </c>
-      <c r="J5" s="48" t="n">
-        <v>76.27118644067797</v>
-      </c>
-      <c r="K5" s="46" t="inlineStr">
+      <c r="J5" s="47" t="n">
+        <v>75.9375</v>
+      </c>
+      <c r="K5" s="45" t="inlineStr">
         <is>
           <t>★★★☆☆</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="46" t="n">
+      <c r="A6" s="45" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="46" t="inlineStr">
+      <c r="B6" s="45" t="inlineStr">
         <is>
           <t>6610553203</t>
         </is>
       </c>
-      <c r="C6" s="47" t="inlineStr">
+      <c r="C6" s="46" t="inlineStr">
         <is>
           <t>----</t>
         </is>
       </c>
-      <c r="D6" s="46" t="inlineStr">
-        <is>
-          <t>61.00/118.00</t>
-        </is>
-      </c>
-      <c r="E6" s="48" t="n">
-        <v>51.69491525423729</v>
-      </c>
-      <c r="F6" s="48" t="n">
-        <v>36.1864406779661</v>
-      </c>
-      <c r="G6" s="46" t="inlineStr">
-        <is>
-          <t>7/7</t>
-        </is>
-      </c>
-      <c r="H6" s="48" t="n">
+      <c r="D6" s="45" t="inlineStr">
+        <is>
+          <t>61.00/128.00</t>
+        </is>
+      </c>
+      <c r="E6" s="47" t="n">
+        <v>47.65625</v>
+      </c>
+      <c r="F6" s="47" t="n">
+        <v>33.359375</v>
+      </c>
+      <c r="G6" s="45" t="inlineStr">
+        <is>
+          <t>7/8</t>
+        </is>
+      </c>
+      <c r="H6" s="47" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="I6" s="47" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="J6" s="47" t="n">
+        <v>59.609375</v>
+      </c>
+      <c r="K6" s="45" t="inlineStr">
+        <is>
+          <t>★☆☆☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="45" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="45" t="inlineStr">
+        <is>
+          <t>6610553220</t>
+        </is>
+      </c>
+      <c r="C7" s="46" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D7" s="45" t="inlineStr">
+        <is>
+          <t>29.00/128.00</t>
+        </is>
+      </c>
+      <c r="E7" s="47" t="n">
+        <v>22.65625</v>
+      </c>
+      <c r="F7" s="47" t="n">
+        <v>15.859375</v>
+      </c>
+      <c r="G7" s="45" t="inlineStr">
+        <is>
+          <t>5/8</t>
+        </is>
+      </c>
+      <c r="H7" s="47" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="I7" s="47" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="J7" s="47" t="n">
+        <v>34.609375</v>
+      </c>
+      <c r="K7" s="45" t="inlineStr">
+        <is>
+          <t>★☆☆☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="45" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="45" t="inlineStr">
+        <is>
+          <t>6610553238</t>
+        </is>
+      </c>
+      <c r="C8" s="46" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D8" s="45" t="inlineStr">
+        <is>
+          <t>56.00/128.00</t>
+        </is>
+      </c>
+      <c r="E8" s="47" t="n">
+        <v>43.75</v>
+      </c>
+      <c r="F8" s="47" t="n">
+        <v>30.625</v>
+      </c>
+      <c r="G8" s="45" t="inlineStr">
+        <is>
+          <t>6/8</t>
+        </is>
+      </c>
+      <c r="H8" s="47" t="n">
+        <v>75</v>
+      </c>
+      <c r="I8" s="47" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="J8" s="47" t="n">
+        <v>53.125</v>
+      </c>
+      <c r="K8" s="45" t="inlineStr">
+        <is>
+          <t>★☆☆☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="45" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="45" t="inlineStr">
+        <is>
+          <t>6610553254</t>
+        </is>
+      </c>
+      <c r="C9" s="46" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D9" s="45" t="inlineStr">
+        <is>
+          <t>84.00/128.00</t>
+        </is>
+      </c>
+      <c r="E9" s="47" t="n">
+        <v>65.625</v>
+      </c>
+      <c r="F9" s="47" t="n">
+        <v>45.9375</v>
+      </c>
+      <c r="G9" s="45" t="inlineStr">
+        <is>
+          <t>8/8</t>
+        </is>
+      </c>
+      <c r="H9" s="47" t="n">
         <v>100</v>
       </c>
-      <c r="I6" s="48" t="n">
+      <c r="I9" s="47" t="n">
         <v>30</v>
       </c>
-      <c r="J6" s="48" t="n">
-        <v>66.18644067796609</v>
-      </c>
-      <c r="K6" s="46" t="inlineStr">
+      <c r="J9" s="47" t="n">
+        <v>75.9375</v>
+      </c>
+      <c r="K9" s="45" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="45" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="45" t="inlineStr">
+        <is>
+          <t>6610553262</t>
+        </is>
+      </c>
+      <c r="C10" s="46" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D10" s="45" t="inlineStr">
+        <is>
+          <t>68.00/128.00</t>
+        </is>
+      </c>
+      <c r="E10" s="47" t="n">
+        <v>53.125</v>
+      </c>
+      <c r="F10" s="47" t="n">
+        <v>37.1875</v>
+      </c>
+      <c r="G10" s="45" t="inlineStr">
+        <is>
+          <t>7/8</t>
+        </is>
+      </c>
+      <c r="H10" s="47" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="I10" s="47" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="J10" s="47" t="n">
+        <v>63.4375</v>
+      </c>
+      <c r="K10" s="45" t="inlineStr">
         <is>
           <t>★★☆☆☆</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="46" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="46" t="inlineStr">
-        <is>
-          <t>6610553220</t>
-        </is>
-      </c>
-      <c r="C7" s="47" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="45" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="45" t="inlineStr">
+        <is>
+          <t>6610553271</t>
+        </is>
+      </c>
+      <c r="C11" s="46" t="inlineStr">
         <is>
           <t>----</t>
         </is>
       </c>
-      <c r="D7" s="46" t="inlineStr">
-        <is>
-          <t>29.00/118.00</t>
-        </is>
-      </c>
-      <c r="E7" s="48" t="n">
-        <v>24.57627118644068</v>
-      </c>
-      <c r="F7" s="48" t="n">
-        <v>17.20338983050847</v>
-      </c>
-      <c r="G7" s="46" t="inlineStr">
-        <is>
-          <t>5/7</t>
-        </is>
-      </c>
-      <c r="H7" s="48" t="n">
-        <v>71.42857142857143</v>
-      </c>
-      <c r="I7" s="48" t="n">
-        <v>21.42857142857143</v>
-      </c>
-      <c r="J7" s="48" t="n">
-        <v>38.6319612590799</v>
-      </c>
-      <c r="K7" s="46" t="inlineStr">
+      <c r="D11" s="45" t="inlineStr">
+        <is>
+          <t>90.00/128.00</t>
+        </is>
+      </c>
+      <c r="E11" s="47" t="n">
+        <v>70.3125</v>
+      </c>
+      <c r="F11" s="47" t="n">
+        <v>49.21875</v>
+      </c>
+      <c r="G11" s="45" t="inlineStr">
+        <is>
+          <t>8/8</t>
+        </is>
+      </c>
+      <c r="H11" s="47" t="n">
+        <v>100</v>
+      </c>
+      <c r="I11" s="47" t="n">
+        <v>30</v>
+      </c>
+      <c r="J11" s="47" t="n">
+        <v>79.21875</v>
+      </c>
+      <c r="K11" s="45" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="45" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="45" t="inlineStr">
+        <is>
+          <t>6610553289</t>
+        </is>
+      </c>
+      <c r="C12" s="46" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D12" s="45" t="inlineStr">
+        <is>
+          <t>57.00/128.00</t>
+        </is>
+      </c>
+      <c r="E12" s="47" t="n">
+        <v>44.53125</v>
+      </c>
+      <c r="F12" s="47" t="n">
+        <v>31.171875</v>
+      </c>
+      <c r="G12" s="45" t="inlineStr">
+        <is>
+          <t>7/8</t>
+        </is>
+      </c>
+      <c r="H12" s="47" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="I12" s="47" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="J12" s="47" t="n">
+        <v>57.421875</v>
+      </c>
+      <c r="K12" s="45" t="inlineStr">
         <is>
           <t>★☆☆☆☆</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="46" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="46" t="inlineStr">
-        <is>
-          <t>6610553238</t>
-        </is>
-      </c>
-      <c r="C8" s="47" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="45" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="45" t="inlineStr">
+        <is>
+          <t>6610553327</t>
+        </is>
+      </c>
+      <c r="C13" s="46" t="inlineStr">
         <is>
           <t>----</t>
         </is>
       </c>
-      <c r="D8" s="46" t="inlineStr">
-        <is>
-          <t>46.00/118.00</t>
-        </is>
-      </c>
-      <c r="E8" s="48" t="n">
-        <v>38.98305084745763</v>
-      </c>
-      <c r="F8" s="48" t="n">
-        <v>27.28813559322034</v>
-      </c>
-      <c r="G8" s="46" t="inlineStr">
-        <is>
-          <t>5/7</t>
-        </is>
-      </c>
-      <c r="H8" s="48" t="n">
-        <v>71.42857142857143</v>
-      </c>
-      <c r="I8" s="48" t="n">
-        <v>21.42857142857143</v>
-      </c>
-      <c r="J8" s="48" t="n">
-        <v>48.71670702179177</v>
-      </c>
-      <c r="K8" s="46" t="inlineStr">
+      <c r="D13" s="45" t="inlineStr">
+        <is>
+          <t>34.00/128.00</t>
+        </is>
+      </c>
+      <c r="E13" s="47" t="n">
+        <v>26.5625</v>
+      </c>
+      <c r="F13" s="47" t="n">
+        <v>18.59375</v>
+      </c>
+      <c r="G13" s="45" t="inlineStr">
+        <is>
+          <t>5/8</t>
+        </is>
+      </c>
+      <c r="H13" s="47" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="I13" s="47" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="J13" s="47" t="n">
+        <v>37.34375</v>
+      </c>
+      <c r="K13" s="45" t="inlineStr">
         <is>
           <t>★☆☆☆☆</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="46" t="n">
+    <row r="14">
+      <c r="A14" s="45" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="45" t="inlineStr">
+        <is>
+          <t>6610554153</t>
+        </is>
+      </c>
+      <c r="C14" s="46" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D14" s="45" t="inlineStr">
+        <is>
+          <t>64.00/128.00</t>
+        </is>
+      </c>
+      <c r="E14" s="47" t="n">
+        <v>50</v>
+      </c>
+      <c r="F14" s="47" t="n">
+        <v>35</v>
+      </c>
+      <c r="G14" s="45" t="inlineStr">
+        <is>
+          <t>6/8</t>
+        </is>
+      </c>
+      <c r="H14" s="47" t="n">
+        <v>75</v>
+      </c>
+      <c r="I14" s="47" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="J14" s="47" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="K14" s="45" t="inlineStr">
+        <is>
+          <t>★☆☆☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="45" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="45" t="inlineStr">
+        <is>
+          <t>6610554161</t>
+        </is>
+      </c>
+      <c r="C15" s="46" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D15" s="45" t="inlineStr">
+        <is>
+          <t>54.00/128.00</t>
+        </is>
+      </c>
+      <c r="E15" s="47" t="n">
+        <v>42.1875</v>
+      </c>
+      <c r="F15" s="47" t="n">
+        <v>29.53125</v>
+      </c>
+      <c r="G15" s="45" t="inlineStr">
+        <is>
+          <t>3/8</t>
+        </is>
+      </c>
+      <c r="H15" s="47" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="I15" s="47" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="J15" s="47" t="n">
+        <v>40.78125</v>
+      </c>
+      <c r="K15" s="45" t="inlineStr">
+        <is>
+          <t>★☆☆☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="45" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="45" t="inlineStr">
+        <is>
+          <t>6710552942</t>
+        </is>
+      </c>
+      <c r="C16" s="46" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D16" s="45" t="inlineStr">
+        <is>
+          <t>82.00/128.00</t>
+        </is>
+      </c>
+      <c r="E16" s="47" t="n">
+        <v>64.0625</v>
+      </c>
+      <c r="F16" s="47" t="n">
+        <v>44.84375</v>
+      </c>
+      <c r="G16" s="45" t="inlineStr">
+        <is>
+          <t>7/8</t>
+        </is>
+      </c>
+      <c r="H16" s="47" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="I16" s="47" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="J16" s="47" t="n">
+        <v>71.09375</v>
+      </c>
+      <c r="K16" s="45" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="45" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="45" t="inlineStr">
+        <is>
+          <t>6710552951</t>
+        </is>
+      </c>
+      <c r="C17" s="46" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D17" s="45" t="inlineStr">
+        <is>
+          <t>101.00/128.00</t>
+        </is>
+      </c>
+      <c r="E17" s="47" t="n">
+        <v>78.90625</v>
+      </c>
+      <c r="F17" s="47" t="n">
+        <v>55.234375</v>
+      </c>
+      <c r="G17" s="45" t="inlineStr">
+        <is>
+          <t>8/8</t>
+        </is>
+      </c>
+      <c r="H17" s="47" t="n">
+        <v>100</v>
+      </c>
+      <c r="I17" s="47" t="n">
+        <v>30</v>
+      </c>
+      <c r="J17" s="47" t="n">
+        <v>85.234375</v>
+      </c>
+      <c r="K17" s="45" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="45" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="45" t="inlineStr">
+        <is>
+          <t>6710552969</t>
+        </is>
+      </c>
+      <c r="C18" s="46" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D18" s="45" t="inlineStr">
+        <is>
+          <t>100.00/128.00</t>
+        </is>
+      </c>
+      <c r="E18" s="47" t="n">
+        <v>78.125</v>
+      </c>
+      <c r="F18" s="47" t="n">
+        <v>54.6875</v>
+      </c>
+      <c r="G18" s="45" t="inlineStr">
+        <is>
+          <t>8/8</t>
+        </is>
+      </c>
+      <c r="H18" s="47" t="n">
+        <v>100</v>
+      </c>
+      <c r="I18" s="47" t="n">
+        <v>30</v>
+      </c>
+      <c r="J18" s="47" t="n">
+        <v>84.6875</v>
+      </c>
+      <c r="K18" s="45" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="45" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="45" t="inlineStr">
+        <is>
+          <t>6710552977</t>
+        </is>
+      </c>
+      <c r="C19" s="46" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D19" s="45" t="inlineStr">
+        <is>
+          <t>74.00/128.00</t>
+        </is>
+      </c>
+      <c r="E19" s="47" t="n">
+        <v>57.8125</v>
+      </c>
+      <c r="F19" s="47" t="n">
+        <v>40.46875</v>
+      </c>
+      <c r="G19" s="45" t="inlineStr">
+        <is>
+          <t>8/8</t>
+        </is>
+      </c>
+      <c r="H19" s="47" t="n">
+        <v>100</v>
+      </c>
+      <c r="I19" s="47" t="n">
+        <v>30</v>
+      </c>
+      <c r="J19" s="47" t="n">
+        <v>70.46875</v>
+      </c>
+      <c r="K19" s="45" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="45" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="45" t="inlineStr">
+        <is>
+          <t>6710552985</t>
+        </is>
+      </c>
+      <c r="C20" s="46" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D20" s="45" t="inlineStr">
+        <is>
+          <t>94.00/128.00</t>
+        </is>
+      </c>
+      <c r="E20" s="47" t="n">
+        <v>73.4375</v>
+      </c>
+      <c r="F20" s="47" t="n">
+        <v>51.40625</v>
+      </c>
+      <c r="G20" s="45" t="inlineStr">
+        <is>
+          <t>8/8</t>
+        </is>
+      </c>
+      <c r="H20" s="47" t="n">
+        <v>100</v>
+      </c>
+      <c r="I20" s="47" t="n">
+        <v>30</v>
+      </c>
+      <c r="J20" s="47" t="n">
+        <v>81.40625</v>
+      </c>
+      <c r="K20" s="45" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="45" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="45" t="inlineStr">
+        <is>
+          <t>6710552993</t>
+        </is>
+      </c>
+      <c r="C21" s="46" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D21" s="45" t="inlineStr">
+        <is>
+          <t>81.00/128.00</t>
+        </is>
+      </c>
+      <c r="E21" s="47" t="n">
+        <v>63.28125</v>
+      </c>
+      <c r="F21" s="47" t="n">
+        <v>44.296875</v>
+      </c>
+      <c r="G21" s="45" t="inlineStr">
+        <is>
+          <t>7/8</t>
+        </is>
+      </c>
+      <c r="H21" s="47" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="I21" s="47" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="J21" s="47" t="n">
+        <v>70.546875</v>
+      </c>
+      <c r="K21" s="45" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="45" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="45" t="inlineStr">
+        <is>
+          <t>6710553001</t>
+        </is>
+      </c>
+      <c r="C22" s="46" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D22" s="45" t="inlineStr">
+        <is>
+          <t>53.00/128.00</t>
+        </is>
+      </c>
+      <c r="E22" s="47" t="n">
+        <v>41.40625</v>
+      </c>
+      <c r="F22" s="47" t="n">
+        <v>28.984375</v>
+      </c>
+      <c r="G22" s="45" t="inlineStr">
+        <is>
+          <t>5/8</t>
+        </is>
+      </c>
+      <c r="H22" s="47" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="I22" s="47" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="J22" s="47" t="n">
+        <v>47.734375</v>
+      </c>
+      <c r="K22" s="45" t="inlineStr">
+        <is>
+          <t>★☆☆☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="45" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="45" t="inlineStr">
+        <is>
+          <t>6710553027</t>
+        </is>
+      </c>
+      <c r="C23" s="46" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D23" s="45" t="inlineStr">
+        <is>
+          <t>93.00/128.00</t>
+        </is>
+      </c>
+      <c r="E23" s="47" t="n">
+        <v>72.65625</v>
+      </c>
+      <c r="F23" s="47" t="n">
+        <v>50.859375</v>
+      </c>
+      <c r="G23" s="45" t="inlineStr">
+        <is>
+          <t>8/8</t>
+        </is>
+      </c>
+      <c r="H23" s="47" t="n">
+        <v>100</v>
+      </c>
+      <c r="I23" s="47" t="n">
+        <v>30</v>
+      </c>
+      <c r="J23" s="47" t="n">
+        <v>80.859375</v>
+      </c>
+      <c r="K23" s="45" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="45" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="45" t="inlineStr">
+        <is>
+          <t>6710553035</t>
+        </is>
+      </c>
+      <c r="C24" s="46" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D24" s="45" t="inlineStr">
+        <is>
+          <t>101.00/128.00</t>
+        </is>
+      </c>
+      <c r="E24" s="47" t="n">
+        <v>78.90625</v>
+      </c>
+      <c r="F24" s="47" t="n">
+        <v>55.234375</v>
+      </c>
+      <c r="G24" s="45" t="inlineStr">
+        <is>
+          <t>8/8</t>
+        </is>
+      </c>
+      <c r="H24" s="47" t="n">
+        <v>100</v>
+      </c>
+      <c r="I24" s="47" t="n">
+        <v>30</v>
+      </c>
+      <c r="J24" s="47" t="n">
+        <v>85.234375</v>
+      </c>
+      <c r="K24" s="45" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="45" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="45" t="inlineStr">
+        <is>
+          <t>6710553051</t>
+        </is>
+      </c>
+      <c r="C25" s="46" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D25" s="45" t="inlineStr">
+        <is>
+          <t>0.00/128.00</t>
+        </is>
+      </c>
+      <c r="E25" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="45" t="inlineStr">
+        <is>
+          <t>0/8</t>
+        </is>
+      </c>
+      <c r="H25" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" s="45" t="inlineStr">
+        <is>
+          <t>★☆☆☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="45" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="45" t="inlineStr">
+        <is>
+          <t>6710553078</t>
+        </is>
+      </c>
+      <c r="C26" s="46" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D26" s="45" t="inlineStr">
+        <is>
+          <t>100.00/128.00</t>
+        </is>
+      </c>
+      <c r="E26" s="47" t="n">
+        <v>78.125</v>
+      </c>
+      <c r="F26" s="47" t="n">
+        <v>54.6875</v>
+      </c>
+      <c r="G26" s="45" t="inlineStr">
+        <is>
+          <t>8/8</t>
+        </is>
+      </c>
+      <c r="H26" s="47" t="n">
+        <v>100</v>
+      </c>
+      <c r="I26" s="47" t="n">
+        <v>30</v>
+      </c>
+      <c r="J26" s="47" t="n">
+        <v>84.6875</v>
+      </c>
+      <c r="K26" s="45" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="45" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="45" t="inlineStr">
+        <is>
+          <t>6710553086</t>
+        </is>
+      </c>
+      <c r="C27" s="46" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D27" s="45" t="inlineStr">
+        <is>
+          <t>78.00/128.00</t>
+        </is>
+      </c>
+      <c r="E27" s="47" t="n">
+        <v>60.9375</v>
+      </c>
+      <c r="F27" s="47" t="n">
+        <v>42.65625</v>
+      </c>
+      <c r="G27" s="45" t="inlineStr">
+        <is>
+          <t>7/8</t>
+        </is>
+      </c>
+      <c r="H27" s="47" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="I27" s="47" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="J27" s="47" t="n">
+        <v>68.90625</v>
+      </c>
+      <c r="K27" s="45" t="inlineStr">
+        <is>
+          <t>★★☆☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="45" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="45" t="inlineStr">
+        <is>
+          <t>6710553094</t>
+        </is>
+      </c>
+      <c r="C28" s="46" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D28" s="45" t="inlineStr">
+        <is>
+          <t>119.00/128.00</t>
+        </is>
+      </c>
+      <c r="E28" s="47" t="n">
+        <v>92.96875</v>
+      </c>
+      <c r="F28" s="47" t="n">
+        <v>65.078125</v>
+      </c>
+      <c r="G28" s="45" t="inlineStr">
+        <is>
+          <t>8/8</t>
+        </is>
+      </c>
+      <c r="H28" s="47" t="n">
+        <v>100</v>
+      </c>
+      <c r="I28" s="47" t="n">
+        <v>30</v>
+      </c>
+      <c r="J28" s="47" t="n">
+        <v>95.078125</v>
+      </c>
+      <c r="K28" s="45" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="45" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="45" t="inlineStr">
+        <is>
+          <t>6710553108</t>
+        </is>
+      </c>
+      <c r="C29" s="46" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D29" s="45" t="inlineStr">
+        <is>
+          <t>98.00/128.00</t>
+        </is>
+      </c>
+      <c r="E29" s="47" t="n">
+        <v>76.5625</v>
+      </c>
+      <c r="F29" s="47" t="n">
+        <v>53.59375</v>
+      </c>
+      <c r="G29" s="45" t="inlineStr">
+        <is>
+          <t>8/8</t>
+        </is>
+      </c>
+      <c r="H29" s="47" t="n">
+        <v>100</v>
+      </c>
+      <c r="I29" s="47" t="n">
+        <v>30</v>
+      </c>
+      <c r="J29" s="47" t="n">
+        <v>83.59375</v>
+      </c>
+      <c r="K29" s="45" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="45" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="45" t="inlineStr">
+        <is>
+          <t>6710553124</t>
+        </is>
+      </c>
+      <c r="C30" s="46" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D30" s="45" t="inlineStr">
+        <is>
+          <t>98.00/128.00</t>
+        </is>
+      </c>
+      <c r="E30" s="47" t="n">
+        <v>76.5625</v>
+      </c>
+      <c r="F30" s="47" t="n">
+        <v>53.59375</v>
+      </c>
+      <c r="G30" s="45" t="inlineStr">
+        <is>
+          <t>7/8</t>
+        </is>
+      </c>
+      <c r="H30" s="47" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="I30" s="47" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="J30" s="47" t="n">
+        <v>79.84375</v>
+      </c>
+      <c r="K30" s="45" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="45" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="45" t="inlineStr">
+        <is>
+          <t>6710553141</t>
+        </is>
+      </c>
+      <c r="C31" s="46" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D31" s="45" t="inlineStr">
+        <is>
+          <t>98.00/128.00</t>
+        </is>
+      </c>
+      <c r="E31" s="47" t="n">
+        <v>76.5625</v>
+      </c>
+      <c r="F31" s="47" t="n">
+        <v>53.59375</v>
+      </c>
+      <c r="G31" s="45" t="inlineStr">
+        <is>
+          <t>8/8</t>
+        </is>
+      </c>
+      <c r="H31" s="47" t="n">
+        <v>100</v>
+      </c>
+      <c r="I31" s="47" t="n">
+        <v>30</v>
+      </c>
+      <c r="J31" s="47" t="n">
+        <v>83.59375</v>
+      </c>
+      <c r="K31" s="45" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="45" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="45" t="inlineStr">
+        <is>
+          <t>6710553167</t>
+        </is>
+      </c>
+      <c r="C32" s="46" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D32" s="45" t="inlineStr">
+        <is>
+          <t>76.00/128.00</t>
+        </is>
+      </c>
+      <c r="E32" s="47" t="n">
+        <v>59.375</v>
+      </c>
+      <c r="F32" s="47" t="n">
+        <v>41.5625</v>
+      </c>
+      <c r="G32" s="45" t="inlineStr">
+        <is>
+          <t>7/8</t>
+        </is>
+      </c>
+      <c r="H32" s="47" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="I32" s="47" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="J32" s="47" t="n">
+        <v>67.8125</v>
+      </c>
+      <c r="K32" s="45" t="inlineStr">
+        <is>
+          <t>★★☆☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="45" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="45" t="inlineStr">
+        <is>
+          <t>6710553191</t>
+        </is>
+      </c>
+      <c r="C33" s="46" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D33" s="45" t="inlineStr">
+        <is>
+          <t>124.00/128.00</t>
+        </is>
+      </c>
+      <c r="E33" s="47" t="n">
+        <v>96.875</v>
+      </c>
+      <c r="F33" s="47" t="n">
+        <v>67.8125</v>
+      </c>
+      <c r="G33" s="45" t="inlineStr">
+        <is>
+          <t>8/8</t>
+        </is>
+      </c>
+      <c r="H33" s="47" t="n">
+        <v>100</v>
+      </c>
+      <c r="I33" s="47" t="n">
+        <v>30</v>
+      </c>
+      <c r="J33" s="47" t="n">
+        <v>97.8125</v>
+      </c>
+      <c r="K33" s="45" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="45" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="45" t="inlineStr">
+        <is>
+          <t>6710553205</t>
+        </is>
+      </c>
+      <c r="C34" s="46" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D34" s="45" t="inlineStr">
+        <is>
+          <t>104.00/128.00</t>
+        </is>
+      </c>
+      <c r="E34" s="47" t="n">
+        <v>81.25</v>
+      </c>
+      <c r="F34" s="47" t="n">
+        <v>56.875</v>
+      </c>
+      <c r="G34" s="45" t="inlineStr">
+        <is>
+          <t>7/8</t>
+        </is>
+      </c>
+      <c r="H34" s="47" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="I34" s="47" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="J34" s="47" t="n">
+        <v>83.125</v>
+      </c>
+      <c r="K34" s="45" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="45" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="45" t="inlineStr">
+        <is>
+          <t>6710553213</t>
+        </is>
+      </c>
+      <c r="C35" s="46" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D35" s="45" t="inlineStr">
+        <is>
+          <t>87.00/128.00</t>
+        </is>
+      </c>
+      <c r="E35" s="47" t="n">
+        <v>67.96875</v>
+      </c>
+      <c r="F35" s="47" t="n">
+        <v>47.578125</v>
+      </c>
+      <c r="G35" s="45" t="inlineStr">
+        <is>
+          <t>8/8</t>
+        </is>
+      </c>
+      <c r="H35" s="47" t="n">
+        <v>100</v>
+      </c>
+      <c r="I35" s="47" t="n">
+        <v>30</v>
+      </c>
+      <c r="J35" s="47" t="n">
+        <v>77.578125</v>
+      </c>
+      <c r="K35" s="45" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="45" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="45" t="inlineStr">
+        <is>
+          <t>6710553264</t>
+        </is>
+      </c>
+      <c r="C36" s="46" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D36" s="45" t="inlineStr">
+        <is>
+          <t>62.00/128.00</t>
+        </is>
+      </c>
+      <c r="E36" s="47" t="n">
+        <v>48.4375</v>
+      </c>
+      <c r="F36" s="47" t="n">
+        <v>33.90625</v>
+      </c>
+      <c r="G36" s="45" t="inlineStr">
+        <is>
+          <t>8/8</t>
+        </is>
+      </c>
+      <c r="H36" s="47" t="n">
+        <v>100</v>
+      </c>
+      <c r="I36" s="47" t="n">
+        <v>30</v>
+      </c>
+      <c r="J36" s="47" t="n">
+        <v>63.90625</v>
+      </c>
+      <c r="K36" s="45" t="inlineStr">
+        <is>
+          <t>★★☆☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="45" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="45" t="inlineStr">
+        <is>
+          <t>6710553272</t>
+        </is>
+      </c>
+      <c r="C37" s="46" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D37" s="45" t="inlineStr">
+        <is>
+          <t>76.00/128.00</t>
+        </is>
+      </c>
+      <c r="E37" s="47" t="n">
+        <v>59.375</v>
+      </c>
+      <c r="F37" s="47" t="n">
+        <v>41.5625</v>
+      </c>
+      <c r="G37" s="45" t="inlineStr">
+        <is>
+          <t>8/8</t>
+        </is>
+      </c>
+      <c r="H37" s="47" t="n">
+        <v>100</v>
+      </c>
+      <c r="I37" s="47" t="n">
+        <v>30</v>
+      </c>
+      <c r="J37" s="47" t="n">
+        <v>71.5625</v>
+      </c>
+      <c r="K37" s="45" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="45" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="45" t="inlineStr">
+        <is>
+          <t>6710553281</t>
+        </is>
+      </c>
+      <c r="C38" s="46" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D38" s="45" t="inlineStr">
+        <is>
+          <t>88.00/128.00</t>
+        </is>
+      </c>
+      <c r="E38" s="47" t="n">
+        <v>68.75</v>
+      </c>
+      <c r="F38" s="47" t="n">
+        <v>48.125</v>
+      </c>
+      <c r="G38" s="45" t="inlineStr">
+        <is>
+          <t>8/8</t>
+        </is>
+      </c>
+      <c r="H38" s="47" t="n">
+        <v>100</v>
+      </c>
+      <c r="I38" s="47" t="n">
+        <v>30</v>
+      </c>
+      <c r="J38" s="47" t="n">
+        <v>78.125</v>
+      </c>
+      <c r="K38" s="45" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="45" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="45" t="inlineStr">
+        <is>
+          <t>6710553299</t>
+        </is>
+      </c>
+      <c r="C39" s="46" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D39" s="45" t="inlineStr">
+        <is>
+          <t>104.00/128.00</t>
+        </is>
+      </c>
+      <c r="E39" s="47" t="n">
+        <v>81.25</v>
+      </c>
+      <c r="F39" s="47" t="n">
+        <v>56.875</v>
+      </c>
+      <c r="G39" s="45" t="inlineStr">
+        <is>
+          <t>8/8</t>
+        </is>
+      </c>
+      <c r="H39" s="47" t="n">
+        <v>100</v>
+      </c>
+      <c r="I39" s="47" t="n">
+        <v>30</v>
+      </c>
+      <c r="J39" s="47" t="n">
+        <v>86.875</v>
+      </c>
+      <c r="K39" s="45" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="45" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="45" t="inlineStr">
+        <is>
+          <t>6710553329</t>
+        </is>
+      </c>
+      <c r="C40" s="46" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D40" s="45" t="inlineStr">
+        <is>
+          <t>95.00/128.00</t>
+        </is>
+      </c>
+      <c r="E40" s="47" t="n">
+        <v>74.21875</v>
+      </c>
+      <c r="F40" s="47" t="n">
+        <v>51.953125</v>
+      </c>
+      <c r="G40" s="45" t="inlineStr">
+        <is>
+          <t>8/8</t>
+        </is>
+      </c>
+      <c r="H40" s="47" t="n">
+        <v>100</v>
+      </c>
+      <c r="I40" s="47" t="n">
+        <v>30</v>
+      </c>
+      <c r="J40" s="47" t="n">
+        <v>81.953125</v>
+      </c>
+      <c r="K40" s="45" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="45" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="45" t="inlineStr">
+        <is>
+          <t>6710553337</t>
+        </is>
+      </c>
+      <c r="C41" s="46" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D41" s="45" t="inlineStr">
+        <is>
+          <t>94.00/128.00</t>
+        </is>
+      </c>
+      <c r="E41" s="47" t="n">
+        <v>73.4375</v>
+      </c>
+      <c r="F41" s="47" t="n">
+        <v>51.40625</v>
+      </c>
+      <c r="G41" s="45" t="inlineStr">
+        <is>
+          <t>7/8</t>
+        </is>
+      </c>
+      <c r="H41" s="47" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="I41" s="47" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="J41" s="47" t="n">
+        <v>77.65625</v>
+      </c>
+      <c r="K41" s="45" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="45" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="45" t="inlineStr">
+        <is>
+          <t>6710553345</t>
+        </is>
+      </c>
+      <c r="C42" s="46" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D42" s="45" t="inlineStr">
+        <is>
+          <t>100.00/128.00</t>
+        </is>
+      </c>
+      <c r="E42" s="47" t="n">
+        <v>78.125</v>
+      </c>
+      <c r="F42" s="47" t="n">
+        <v>54.6875</v>
+      </c>
+      <c r="G42" s="45" t="inlineStr">
+        <is>
+          <t>8/8</t>
+        </is>
+      </c>
+      <c r="H42" s="47" t="n">
+        <v>100</v>
+      </c>
+      <c r="I42" s="47" t="n">
+        <v>30</v>
+      </c>
+      <c r="J42" s="47" t="n">
+        <v>84.6875</v>
+      </c>
+      <c r="K42" s="45" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="45" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="45" t="inlineStr">
+        <is>
+          <t>6710553353</t>
+        </is>
+      </c>
+      <c r="C43" s="46" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D43" s="45" t="inlineStr">
+        <is>
+          <t>101.00/128.00</t>
+        </is>
+      </c>
+      <c r="E43" s="47" t="n">
+        <v>78.90625</v>
+      </c>
+      <c r="F43" s="47" t="n">
+        <v>55.234375</v>
+      </c>
+      <c r="G43" s="45" t="inlineStr">
+        <is>
+          <t>8/8</t>
+        </is>
+      </c>
+      <c r="H43" s="47" t="n">
+        <v>100</v>
+      </c>
+      <c r="I43" s="47" t="n">
+        <v>30</v>
+      </c>
+      <c r="J43" s="47" t="n">
+        <v>85.234375</v>
+      </c>
+      <c r="K43" s="45" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="45" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="45" t="inlineStr">
+        <is>
+          <t>6710553361</t>
+        </is>
+      </c>
+      <c r="C44" s="46" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D44" s="45" t="inlineStr">
+        <is>
+          <t>103.00/128.00</t>
+        </is>
+      </c>
+      <c r="E44" s="47" t="n">
+        <v>80.46875</v>
+      </c>
+      <c r="F44" s="47" t="n">
+        <v>56.328125</v>
+      </c>
+      <c r="G44" s="45" t="inlineStr">
+        <is>
+          <t>8/8</t>
+        </is>
+      </c>
+      <c r="H44" s="47" t="n">
+        <v>100</v>
+      </c>
+      <c r="I44" s="47" t="n">
+        <v>30</v>
+      </c>
+      <c r="J44" s="47" t="n">
+        <v>86.328125</v>
+      </c>
+      <c r="K44" s="45" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="45" t="inlineStr">
+        <is>
+          <t>6710553370</t>
+        </is>
+      </c>
+      <c r="C45" s="46" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D45" s="45" t="inlineStr">
+        <is>
+          <t>52.00/128.00</t>
+        </is>
+      </c>
+      <c r="E45" s="47" t="n">
+        <v>40.625</v>
+      </c>
+      <c r="F45" s="47" t="n">
+        <v>28.4375</v>
+      </c>
+      <c r="G45" s="45" t="inlineStr">
+        <is>
+          <t>8/8</t>
+        </is>
+      </c>
+      <c r="H45" s="47" t="n">
+        <v>100</v>
+      </c>
+      <c r="I45" s="47" t="n">
+        <v>30</v>
+      </c>
+      <c r="J45" s="47" t="n">
+        <v>58.4375</v>
+      </c>
+      <c r="K45" s="45" t="inlineStr">
+        <is>
+          <t>★☆☆☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="45" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="45" t="inlineStr">
+        <is>
+          <t>6710553388</t>
+        </is>
+      </c>
+      <c r="C46" s="46" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D46" s="45" t="inlineStr">
+        <is>
+          <t>107.00/128.00</t>
+        </is>
+      </c>
+      <c r="E46" s="47" t="n">
+        <v>83.59375</v>
+      </c>
+      <c r="F46" s="47" t="n">
+        <v>58.515625</v>
+      </c>
+      <c r="G46" s="45" t="inlineStr">
+        <is>
+          <t>8/8</t>
+        </is>
+      </c>
+      <c r="H46" s="47" t="n">
+        <v>100</v>
+      </c>
+      <c r="I46" s="47" t="n">
+        <v>30</v>
+      </c>
+      <c r="J46" s="47" t="n">
+        <v>88.515625</v>
+      </c>
+      <c r="K46" s="45" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="45" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="45" t="inlineStr">
+        <is>
+          <t>6710553396</t>
+        </is>
+      </c>
+      <c r="C47" s="46" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="D47" s="45" t="inlineStr">
+        <is>
+          <t>114.00/128.00</t>
+        </is>
+      </c>
+      <c r="E47" s="47" t="n">
+        <v>89.0625</v>
+      </c>
+      <c r="F47" s="47" t="n">
+        <v>62.34375</v>
+      </c>
+      <c r="G47" s="45" t="inlineStr">
+        <is>
+          <t>8/8</t>
+        </is>
+      </c>
+      <c r="H47" s="47" t="n">
+        <v>100</v>
+      </c>
+      <c r="I47" s="47" t="n">
+        <v>30</v>
+      </c>
+      <c r="J47" s="47" t="n">
+        <v>92.34375</v>
+      </c>
+      <c r="K47" s="45" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="48" t="inlineStr">
+        <is>
+          <t>Exercise maximum score</t>
+        </is>
+      </c>
+      <c r="B50" s="49" t="n">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="48" t="inlineStr">
+        <is>
+          <t>Exercise weight</t>
+        </is>
+      </c>
+      <c r="B51" s="50" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="48" t="inlineStr">
+        <is>
+          <t>Attendance sessions</t>
+        </is>
+      </c>
+      <c r="B52" s="49" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="46" t="inlineStr">
-        <is>
-          <t>6610553254</t>
-        </is>
-      </c>
-      <c r="C9" s="47" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D9" s="46" t="inlineStr">
-        <is>
-          <t>75.00/118.00</t>
-        </is>
-      </c>
-      <c r="E9" s="48" t="n">
-        <v>63.5593220338983</v>
-      </c>
-      <c r="F9" s="48" t="n">
-        <v>44.49152542372881</v>
-      </c>
-      <c r="G9" s="46" t="inlineStr">
-        <is>
-          <t>7/7</t>
-        </is>
-      </c>
-      <c r="H9" s="48" t="n">
-        <v>100</v>
-      </c>
-      <c r="I9" s="48" t="n">
-        <v>30</v>
-      </c>
-      <c r="J9" s="48" t="n">
-        <v>74.4915254237288</v>
-      </c>
-      <c r="K9" s="46" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="46" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="46" t="inlineStr">
-        <is>
-          <t>6610553262</t>
-        </is>
-      </c>
-      <c r="C10" s="47" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D10" s="46" t="inlineStr">
-        <is>
-          <t>62.00/118.00</t>
-        </is>
-      </c>
-      <c r="E10" s="48" t="n">
-        <v>52.54237288135594</v>
-      </c>
-      <c r="F10" s="48" t="n">
-        <v>36.77966101694916</v>
-      </c>
-      <c r="G10" s="46" t="inlineStr">
-        <is>
-          <t>7/7</t>
-        </is>
-      </c>
-      <c r="H10" s="48" t="n">
-        <v>100</v>
-      </c>
-      <c r="I10" s="48" t="n">
-        <v>30</v>
-      </c>
-      <c r="J10" s="48" t="n">
-        <v>66.77966101694915</v>
-      </c>
-      <c r="K10" s="46" t="inlineStr">
-        <is>
-          <t>★★☆☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="46" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="46" t="inlineStr">
-        <is>
-          <t>6610553271</t>
-        </is>
-      </c>
-      <c r="C11" s="47" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D11" s="46" t="inlineStr">
-        <is>
-          <t>80.00/118.00</t>
-        </is>
-      </c>
-      <c r="E11" s="48" t="n">
-        <v>67.79661016949152</v>
-      </c>
-      <c r="F11" s="48" t="n">
-        <v>47.45762711864407</v>
-      </c>
-      <c r="G11" s="46" t="inlineStr">
-        <is>
-          <t>7/7</t>
-        </is>
-      </c>
-      <c r="H11" s="48" t="n">
-        <v>100</v>
-      </c>
-      <c r="I11" s="48" t="n">
-        <v>30</v>
-      </c>
-      <c r="J11" s="48" t="n">
-        <v>77.45762711864407</v>
-      </c>
-      <c r="K11" s="46" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="46" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="46" t="inlineStr">
-        <is>
-          <t>6610553289</t>
-        </is>
-      </c>
-      <c r="C12" s="47" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D12" s="46" t="inlineStr">
-        <is>
-          <t>57.00/118.00</t>
-        </is>
-      </c>
-      <c r="E12" s="48" t="n">
-        <v>48.30508474576271</v>
-      </c>
-      <c r="F12" s="48" t="n">
-        <v>33.8135593220339</v>
-      </c>
-      <c r="G12" s="46" t="inlineStr">
-        <is>
-          <t>6/7</t>
-        </is>
-      </c>
-      <c r="H12" s="48" t="n">
-        <v>85.71428571428571</v>
-      </c>
-      <c r="I12" s="48" t="n">
-        <v>25.71428571428571</v>
-      </c>
-      <c r="J12" s="48" t="n">
-        <v>59.5278450363196</v>
-      </c>
-      <c r="K12" s="46" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="46" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="46" t="inlineStr">
-        <is>
-          <t>6610553327</t>
-        </is>
-      </c>
-      <c r="C13" s="47" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D13" s="46" t="inlineStr">
-        <is>
-          <t>34.00/118.00</t>
-        </is>
-      </c>
-      <c r="E13" s="48" t="n">
-        <v>28.8135593220339</v>
-      </c>
-      <c r="F13" s="48" t="n">
-        <v>20.16949152542373</v>
-      </c>
-      <c r="G13" s="46" t="inlineStr">
-        <is>
-          <t>5/7</t>
-        </is>
-      </c>
-      <c r="H13" s="48" t="n">
-        <v>71.42857142857143</v>
-      </c>
-      <c r="I13" s="48" t="n">
-        <v>21.42857142857143</v>
-      </c>
-      <c r="J13" s="48" t="n">
-        <v>41.59806295399516</v>
-      </c>
-      <c r="K13" s="46" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="46" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="46" t="inlineStr">
-        <is>
-          <t>6610554153</t>
-        </is>
-      </c>
-      <c r="C14" s="47" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D14" s="46" t="inlineStr">
-        <is>
-          <t>64.00/118.00</t>
-        </is>
-      </c>
-      <c r="E14" s="48" t="n">
-        <v>54.23728813559322</v>
-      </c>
-      <c r="F14" s="48" t="n">
-        <v>37.96610169491525</v>
-      </c>
-      <c r="G14" s="46" t="inlineStr">
-        <is>
-          <t>5/7</t>
-        </is>
-      </c>
-      <c r="H14" s="48" t="n">
-        <v>71.42857142857143</v>
-      </c>
-      <c r="I14" s="48" t="n">
-        <v>21.42857142857143</v>
-      </c>
-      <c r="J14" s="48" t="n">
-        <v>59.39467312348668</v>
-      </c>
-      <c r="K14" s="46" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="46" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="46" t="inlineStr">
-        <is>
-          <t>6610554161</t>
-        </is>
-      </c>
-      <c r="C15" s="47" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D15" s="46" t="inlineStr">
-        <is>
-          <t>54.00/118.00</t>
-        </is>
-      </c>
-      <c r="E15" s="48" t="n">
-        <v>45.76271186440678</v>
-      </c>
-      <c r="F15" s="48" t="n">
-        <v>32.03389830508475</v>
-      </c>
-      <c r="G15" s="46" t="inlineStr">
-        <is>
-          <t>3/7</t>
-        </is>
-      </c>
-      <c r="H15" s="48" t="n">
-        <v>42.85714285714285</v>
-      </c>
-      <c r="I15" s="48" t="n">
-        <v>12.85714285714286</v>
-      </c>
-      <c r="J15" s="48" t="n">
-        <v>44.8910411622276</v>
-      </c>
-      <c r="K15" s="46" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="46" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="46" t="inlineStr">
-        <is>
-          <t>6710552942</t>
-        </is>
-      </c>
-      <c r="C16" s="47" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D16" s="46" t="inlineStr">
-        <is>
-          <t>65.00/118.00</t>
-        </is>
-      </c>
-      <c r="E16" s="48" t="n">
-        <v>55.08474576271186</v>
-      </c>
-      <c r="F16" s="48" t="n">
-        <v>38.5593220338983</v>
-      </c>
-      <c r="G16" s="46" t="inlineStr">
-        <is>
-          <t>6/7</t>
-        </is>
-      </c>
-      <c r="H16" s="48" t="n">
-        <v>85.71428571428571</v>
-      </c>
-      <c r="I16" s="48" t="n">
-        <v>25.71428571428571</v>
-      </c>
-      <c r="J16" s="48" t="n">
-        <v>64.27360774818402</v>
-      </c>
-      <c r="K16" s="46" t="inlineStr">
-        <is>
-          <t>★★☆☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="46" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="46" t="inlineStr">
-        <is>
-          <t>6710552951</t>
-        </is>
-      </c>
-      <c r="C17" s="47" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D17" s="46" t="inlineStr">
-        <is>
-          <t>101.00/118.00</t>
-        </is>
-      </c>
-      <c r="E17" s="48" t="n">
-        <v>85.59322033898306</v>
-      </c>
-      <c r="F17" s="48" t="n">
-        <v>59.91525423728814</v>
-      </c>
-      <c r="G17" s="46" t="inlineStr">
-        <is>
-          <t>7/7</t>
-        </is>
-      </c>
-      <c r="H17" s="48" t="n">
-        <v>100</v>
-      </c>
-      <c r="I17" s="48" t="n">
-        <v>30</v>
-      </c>
-      <c r="J17" s="48" t="n">
-        <v>89.91525423728814</v>
-      </c>
-      <c r="K17" s="46" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="46" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" s="46" t="inlineStr">
-        <is>
-          <t>6710552969</t>
-        </is>
-      </c>
-      <c r="C18" s="47" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D18" s="46" t="inlineStr">
-        <is>
-          <t>100.00/118.00</t>
-        </is>
-      </c>
-      <c r="E18" s="48" t="n">
-        <v>84.7457627118644</v>
-      </c>
-      <c r="F18" s="48" t="n">
-        <v>59.32203389830508</v>
-      </c>
-      <c r="G18" s="46" t="inlineStr">
-        <is>
-          <t>7/7</t>
-        </is>
-      </c>
-      <c r="H18" s="48" t="n">
-        <v>100</v>
-      </c>
-      <c r="I18" s="48" t="n">
-        <v>30</v>
-      </c>
-      <c r="J18" s="48" t="n">
-        <v>89.32203389830508</v>
-      </c>
-      <c r="K18" s="46" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="46" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" s="46" t="inlineStr">
-        <is>
-          <t>6710552977</t>
-        </is>
-      </c>
-      <c r="C19" s="47" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D19" s="46" t="inlineStr">
-        <is>
-          <t>74.00/118.00</t>
-        </is>
-      </c>
-      <c r="E19" s="48" t="n">
-        <v>62.71186440677966</v>
-      </c>
-      <c r="F19" s="48" t="n">
-        <v>43.89830508474576</v>
-      </c>
-      <c r="G19" s="46" t="inlineStr">
-        <is>
-          <t>7/7</t>
-        </is>
-      </c>
-      <c r="H19" s="48" t="n">
-        <v>100</v>
-      </c>
-      <c r="I19" s="48" t="n">
-        <v>30</v>
-      </c>
-      <c r="J19" s="48" t="n">
-        <v>73.89830508474577</v>
-      </c>
-      <c r="K19" s="46" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="46" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" s="46" t="inlineStr">
-        <is>
-          <t>6710552985</t>
-        </is>
-      </c>
-      <c r="C20" s="47" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D20" s="46" t="inlineStr">
-        <is>
-          <t>84.00/118.00</t>
-        </is>
-      </c>
-      <c r="E20" s="48" t="n">
-        <v>71.1864406779661</v>
-      </c>
-      <c r="F20" s="48" t="n">
-        <v>49.83050847457627</v>
-      </c>
-      <c r="G20" s="46" t="inlineStr">
-        <is>
-          <t>7/7</t>
-        </is>
-      </c>
-      <c r="H20" s="48" t="n">
-        <v>100</v>
-      </c>
-      <c r="I20" s="48" t="n">
-        <v>30</v>
-      </c>
-      <c r="J20" s="48" t="n">
-        <v>79.83050847457628</v>
-      </c>
-      <c r="K20" s="46" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="46" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" s="46" t="inlineStr">
-        <is>
-          <t>6710552993</t>
-        </is>
-      </c>
-      <c r="C21" s="47" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D21" s="46" t="inlineStr">
-        <is>
-          <t>71.00/118.00</t>
-        </is>
-      </c>
-      <c r="E21" s="48" t="n">
-        <v>60.16949152542372</v>
-      </c>
-      <c r="F21" s="48" t="n">
-        <v>42.11864406779661</v>
-      </c>
-      <c r="G21" s="46" t="inlineStr">
-        <is>
-          <t>6/7</t>
-        </is>
-      </c>
-      <c r="H21" s="48" t="n">
-        <v>85.71428571428571</v>
-      </c>
-      <c r="I21" s="48" t="n">
-        <v>25.71428571428571</v>
-      </c>
-      <c r="J21" s="48" t="n">
-        <v>67.83292978208232</v>
-      </c>
-      <c r="K21" s="46" t="inlineStr">
-        <is>
-          <t>★★☆☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="46" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" s="46" t="inlineStr">
-        <is>
-          <t>6710553001</t>
-        </is>
-      </c>
-      <c r="C22" s="47" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D22" s="46" t="inlineStr">
-        <is>
-          <t>46.00/118.00</t>
-        </is>
-      </c>
-      <c r="E22" s="48" t="n">
-        <v>38.98305084745763</v>
-      </c>
-      <c r="F22" s="48" t="n">
-        <v>27.28813559322034</v>
-      </c>
-      <c r="G22" s="46" t="inlineStr">
-        <is>
-          <t>4/7</t>
-        </is>
-      </c>
-      <c r="H22" s="48" t="n">
-        <v>57.14285714285714</v>
-      </c>
-      <c r="I22" s="48" t="n">
-        <v>17.14285714285714</v>
-      </c>
-      <c r="J22" s="48" t="n">
-        <v>44.43099273607749</v>
-      </c>
-      <c r="K22" s="46" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="46" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" s="46" t="inlineStr">
-        <is>
-          <t>6710553027</t>
-        </is>
-      </c>
-      <c r="C23" s="47" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D23" s="46" t="inlineStr">
-        <is>
-          <t>93.00/118.00</t>
-        </is>
-      </c>
-      <c r="E23" s="48" t="n">
-        <v>78.8135593220339</v>
-      </c>
-      <c r="F23" s="48" t="n">
-        <v>55.16949152542373</v>
-      </c>
-      <c r="G23" s="46" t="inlineStr">
-        <is>
-          <t>7/7</t>
-        </is>
-      </c>
-      <c r="H23" s="48" t="n">
-        <v>100</v>
-      </c>
-      <c r="I23" s="48" t="n">
-        <v>30</v>
-      </c>
-      <c r="J23" s="48" t="n">
-        <v>85.16949152542372</v>
-      </c>
-      <c r="K23" s="46" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="46" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" s="46" t="inlineStr">
-        <is>
-          <t>6710553035</t>
-        </is>
-      </c>
-      <c r="C24" s="47" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D24" s="46" t="inlineStr">
-        <is>
-          <t>101.00/118.00</t>
-        </is>
-      </c>
-      <c r="E24" s="48" t="n">
-        <v>85.59322033898306</v>
-      </c>
-      <c r="F24" s="48" t="n">
-        <v>59.91525423728814</v>
-      </c>
-      <c r="G24" s="46" t="inlineStr">
-        <is>
-          <t>7/7</t>
-        </is>
-      </c>
-      <c r="H24" s="48" t="n">
-        <v>100</v>
-      </c>
-      <c r="I24" s="48" t="n">
-        <v>30</v>
-      </c>
-      <c r="J24" s="48" t="n">
-        <v>89.91525423728814</v>
-      </c>
-      <c r="K24" s="46" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="46" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" s="46" t="inlineStr">
-        <is>
-          <t>6710553051</t>
-        </is>
-      </c>
-      <c r="C25" s="47" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D25" s="46" t="inlineStr">
-        <is>
-          <t>0.00/118.00</t>
-        </is>
-      </c>
-      <c r="E25" s="48" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" s="48" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" s="46" t="inlineStr">
-        <is>
-          <t>0/7</t>
-        </is>
-      </c>
-      <c r="H25" s="48" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" s="48" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" s="48" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" s="46" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="46" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" s="46" t="inlineStr">
-        <is>
-          <t>6710553078</t>
-        </is>
-      </c>
-      <c r="C26" s="47" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D26" s="46" t="inlineStr">
-        <is>
-          <t>94.00/118.00</t>
-        </is>
-      </c>
-      <c r="E26" s="48" t="n">
-        <v>79.66101694915254</v>
-      </c>
-      <c r="F26" s="48" t="n">
-        <v>55.76271186440678</v>
-      </c>
-      <c r="G26" s="46" t="inlineStr">
-        <is>
-          <t>7/7</t>
-        </is>
-      </c>
-      <c r="H26" s="48" t="n">
-        <v>100</v>
-      </c>
-      <c r="I26" s="48" t="n">
-        <v>30</v>
-      </c>
-      <c r="J26" s="48" t="n">
-        <v>85.76271186440678</v>
-      </c>
-      <c r="K26" s="46" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="46" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" s="46" t="inlineStr">
-        <is>
-          <t>6710553086</t>
-        </is>
-      </c>
-      <c r="C27" s="47" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D27" s="46" t="inlineStr">
-        <is>
-          <t>68.00/118.00</t>
-        </is>
-      </c>
-      <c r="E27" s="48" t="n">
-        <v>57.6271186440678</v>
-      </c>
-      <c r="F27" s="48" t="n">
-        <v>40.33898305084746</v>
-      </c>
-      <c r="G27" s="46" t="inlineStr">
-        <is>
-          <t>6/7</t>
-        </is>
-      </c>
-      <c r="H27" s="48" t="n">
-        <v>85.71428571428571</v>
-      </c>
-      <c r="I27" s="48" t="n">
-        <v>25.71428571428571</v>
-      </c>
-      <c r="J27" s="48" t="n">
-        <v>66.05326876513317</v>
-      </c>
-      <c r="K27" s="46" t="inlineStr">
-        <is>
-          <t>★★☆☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="46" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" s="46" t="inlineStr">
-        <is>
-          <t>6710553094</t>
-        </is>
-      </c>
-      <c r="C28" s="47" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D28" s="46" t="inlineStr">
-        <is>
-          <t>112.00/118.00</t>
-        </is>
-      </c>
-      <c r="E28" s="48" t="n">
-        <v>94.91525423728814</v>
-      </c>
-      <c r="F28" s="48" t="n">
-        <v>66.4406779661017</v>
-      </c>
-      <c r="G28" s="46" t="inlineStr">
-        <is>
-          <t>7/7</t>
-        </is>
-      </c>
-      <c r="H28" s="48" t="n">
-        <v>100</v>
-      </c>
-      <c r="I28" s="48" t="n">
-        <v>30</v>
-      </c>
-      <c r="J28" s="48" t="n">
-        <v>96.4406779661017</v>
-      </c>
-      <c r="K28" s="46" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="46" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" s="46" t="inlineStr">
-        <is>
-          <t>6710553108</t>
-        </is>
-      </c>
-      <c r="C29" s="47" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D29" s="46" t="inlineStr">
-        <is>
-          <t>98.00/118.00</t>
-        </is>
-      </c>
-      <c r="E29" s="48" t="n">
-        <v>83.05084745762711</v>
-      </c>
-      <c r="F29" s="48" t="n">
-        <v>58.13559322033898</v>
-      </c>
-      <c r="G29" s="46" t="inlineStr">
-        <is>
-          <t>7/7</t>
-        </is>
-      </c>
-      <c r="H29" s="48" t="n">
-        <v>100</v>
-      </c>
-      <c r="I29" s="48" t="n">
-        <v>30</v>
-      </c>
-      <c r="J29" s="48" t="n">
-        <v>88.13559322033899</v>
-      </c>
-      <c r="K29" s="46" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="46" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" s="46" t="inlineStr">
-        <is>
-          <t>6710553124</t>
-        </is>
-      </c>
-      <c r="C30" s="47" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D30" s="46" t="inlineStr">
-        <is>
-          <t>88.00/118.00</t>
-        </is>
-      </c>
-      <c r="E30" s="48" t="n">
-        <v>74.57627118644068</v>
-      </c>
-      <c r="F30" s="48" t="n">
-        <v>52.20338983050848</v>
-      </c>
-      <c r="G30" s="46" t="inlineStr">
-        <is>
-          <t>6/7</t>
-        </is>
-      </c>
-      <c r="H30" s="48" t="n">
-        <v>85.71428571428571</v>
-      </c>
-      <c r="I30" s="48" t="n">
-        <v>25.71428571428571</v>
-      </c>
-      <c r="J30" s="48" t="n">
-        <v>77.91767554479419</v>
-      </c>
-      <c r="K30" s="46" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="46" t="n">
-        <v>30</v>
-      </c>
-      <c r="B31" s="46" t="inlineStr">
-        <is>
-          <t>6710553141</t>
-        </is>
-      </c>
-      <c r="C31" s="47" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D31" s="46" t="inlineStr">
-        <is>
-          <t>98.00/118.00</t>
-        </is>
-      </c>
-      <c r="E31" s="48" t="n">
-        <v>83.05084745762711</v>
-      </c>
-      <c r="F31" s="48" t="n">
-        <v>58.13559322033898</v>
-      </c>
-      <c r="G31" s="46" t="inlineStr">
-        <is>
-          <t>7/7</t>
-        </is>
-      </c>
-      <c r="H31" s="48" t="n">
-        <v>100</v>
-      </c>
-      <c r="I31" s="48" t="n">
-        <v>30</v>
-      </c>
-      <c r="J31" s="48" t="n">
-        <v>88.13559322033899</v>
-      </c>
-      <c r="K31" s="46" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="46" t="n">
-        <v>31</v>
-      </c>
-      <c r="B32" s="46" t="inlineStr">
-        <is>
-          <t>6710553167</t>
-        </is>
-      </c>
-      <c r="C32" s="47" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D32" s="46" t="inlineStr">
-        <is>
-          <t>76.00/118.00</t>
-        </is>
-      </c>
-      <c r="E32" s="48" t="n">
-        <v>64.40677966101694</v>
-      </c>
-      <c r="F32" s="48" t="n">
-        <v>45.08474576271186</v>
-      </c>
-      <c r="G32" s="46" t="inlineStr">
-        <is>
-          <t>6/7</t>
-        </is>
-      </c>
-      <c r="H32" s="48" t="n">
-        <v>85.71428571428571</v>
-      </c>
-      <c r="I32" s="48" t="n">
-        <v>25.71428571428571</v>
-      </c>
-      <c r="J32" s="48" t="n">
-        <v>70.79903147699757</v>
-      </c>
-      <c r="K32" s="46" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="46" t="n">
-        <v>32</v>
-      </c>
-      <c r="B33" s="46" t="inlineStr">
-        <is>
-          <t>6710553191</t>
-        </is>
-      </c>
-      <c r="C33" s="47" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D33" s="46" t="inlineStr">
-        <is>
-          <t>114.00/118.00</t>
-        </is>
-      </c>
-      <c r="E33" s="48" t="n">
-        <v>96.61016949152543</v>
-      </c>
-      <c r="F33" s="48" t="n">
-        <v>67.62711864406779</v>
-      </c>
-      <c r="G33" s="46" t="inlineStr">
-        <is>
-          <t>7/7</t>
-        </is>
-      </c>
-      <c r="H33" s="48" t="n">
-        <v>100</v>
-      </c>
-      <c r="I33" s="48" t="n">
-        <v>30</v>
-      </c>
-      <c r="J33" s="48" t="n">
-        <v>97.62711864406779</v>
-      </c>
-      <c r="K33" s="46" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="46" t="n">
-        <v>33</v>
-      </c>
-      <c r="B34" s="46" t="inlineStr">
-        <is>
-          <t>6710553205</t>
-        </is>
-      </c>
-      <c r="C34" s="47" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D34" s="46" t="inlineStr">
-        <is>
-          <t>96.00/118.00</t>
-        </is>
-      </c>
-      <c r="E34" s="48" t="n">
-        <v>81.35593220338984</v>
-      </c>
-      <c r="F34" s="48" t="n">
-        <v>56.94915254237289</v>
-      </c>
-      <c r="G34" s="46" t="inlineStr">
-        <is>
-          <t>6/7</t>
-        </is>
-      </c>
-      <c r="H34" s="48" t="n">
-        <v>85.71428571428571</v>
-      </c>
-      <c r="I34" s="48" t="n">
-        <v>25.71428571428571</v>
-      </c>
-      <c r="J34" s="48" t="n">
-        <v>82.66343825665859</v>
-      </c>
-      <c r="K34" s="46" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="46" t="n">
-        <v>34</v>
-      </c>
-      <c r="B35" s="46" t="inlineStr">
-        <is>
-          <t>6710553213</t>
-        </is>
-      </c>
-      <c r="C35" s="47" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D35" s="46" t="inlineStr">
-        <is>
-          <t>87.00/118.00</t>
-        </is>
-      </c>
-      <c r="E35" s="48" t="n">
-        <v>73.72881355932203</v>
-      </c>
-      <c r="F35" s="48" t="n">
-        <v>51.61016949152543</v>
-      </c>
-      <c r="G35" s="46" t="inlineStr">
-        <is>
-          <t>7/7</t>
-        </is>
-      </c>
-      <c r="H35" s="48" t="n">
-        <v>100</v>
-      </c>
-      <c r="I35" s="48" t="n">
-        <v>30</v>
-      </c>
-      <c r="J35" s="48" t="n">
-        <v>81.61016949152543</v>
-      </c>
-      <c r="K35" s="46" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="46" t="n">
-        <v>35</v>
-      </c>
-      <c r="B36" s="46" t="inlineStr">
-        <is>
-          <t>6710553264</t>
-        </is>
-      </c>
-      <c r="C36" s="47" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D36" s="46" t="inlineStr">
-        <is>
-          <t>62.00/118.00</t>
-        </is>
-      </c>
-      <c r="E36" s="48" t="n">
-        <v>52.54237288135594</v>
-      </c>
-      <c r="F36" s="48" t="n">
-        <v>36.77966101694916</v>
-      </c>
-      <c r="G36" s="46" t="inlineStr">
-        <is>
-          <t>7/7</t>
-        </is>
-      </c>
-      <c r="H36" s="48" t="n">
-        <v>100</v>
-      </c>
-      <c r="I36" s="48" t="n">
-        <v>30</v>
-      </c>
-      <c r="J36" s="48" t="n">
-        <v>66.77966101694915</v>
-      </c>
-      <c r="K36" s="46" t="inlineStr">
-        <is>
-          <t>★★☆☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="46" t="n">
-        <v>36</v>
-      </c>
-      <c r="B37" s="46" t="inlineStr">
-        <is>
-          <t>6710553272</t>
-        </is>
-      </c>
-      <c r="C37" s="47" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D37" s="46" t="inlineStr">
-        <is>
-          <t>66.00/118.00</t>
-        </is>
-      </c>
-      <c r="E37" s="48" t="n">
-        <v>55.93220338983051</v>
-      </c>
-      <c r="F37" s="48" t="n">
-        <v>39.15254237288135</v>
-      </c>
-      <c r="G37" s="46" t="inlineStr">
-        <is>
-          <t>7/7</t>
-        </is>
-      </c>
-      <c r="H37" s="48" t="n">
-        <v>100</v>
-      </c>
-      <c r="I37" s="48" t="n">
-        <v>30</v>
-      </c>
-      <c r="J37" s="48" t="n">
-        <v>69.15254237288136</v>
-      </c>
-      <c r="K37" s="46" t="inlineStr">
-        <is>
-          <t>★★☆☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="46" t="n">
-        <v>37</v>
-      </c>
-      <c r="B38" s="46" t="inlineStr">
-        <is>
-          <t>6710553281</t>
-        </is>
-      </c>
-      <c r="C38" s="47" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D38" s="46" t="inlineStr">
-        <is>
-          <t>78.00/118.00</t>
-        </is>
-      </c>
-      <c r="E38" s="48" t="n">
-        <v>66.10169491525424</v>
-      </c>
-      <c r="F38" s="48" t="n">
-        <v>46.27118644067797</v>
-      </c>
-      <c r="G38" s="46" t="inlineStr">
-        <is>
-          <t>7/7</t>
-        </is>
-      </c>
-      <c r="H38" s="48" t="n">
-        <v>100</v>
-      </c>
-      <c r="I38" s="48" t="n">
-        <v>30</v>
-      </c>
-      <c r="J38" s="48" t="n">
-        <v>76.27118644067797</v>
-      </c>
-      <c r="K38" s="46" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="46" t="n">
-        <v>38</v>
-      </c>
-      <c r="B39" s="46" t="inlineStr">
-        <is>
-          <t>6710553299</t>
-        </is>
-      </c>
-      <c r="C39" s="47" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D39" s="46" t="inlineStr">
-        <is>
-          <t>104.00/118.00</t>
-        </is>
-      </c>
-      <c r="E39" s="48" t="n">
-        <v>88.13559322033898</v>
-      </c>
-      <c r="F39" s="48" t="n">
-        <v>61.69491525423729</v>
-      </c>
-      <c r="G39" s="46" t="inlineStr">
-        <is>
-          <t>7/7</t>
-        </is>
-      </c>
-      <c r="H39" s="48" t="n">
-        <v>100</v>
-      </c>
-      <c r="I39" s="48" t="n">
-        <v>30</v>
-      </c>
-      <c r="J39" s="48" t="n">
-        <v>91.69491525423729</v>
-      </c>
-      <c r="K39" s="46" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="46" t="n">
-        <v>39</v>
-      </c>
-      <c r="B40" s="46" t="inlineStr">
-        <is>
-          <t>6710553329</t>
-        </is>
-      </c>
-      <c r="C40" s="47" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D40" s="46" t="inlineStr">
-        <is>
-          <t>86.00/118.00</t>
-        </is>
-      </c>
-      <c r="E40" s="48" t="n">
-        <v>72.88135593220339</v>
-      </c>
-      <c r="F40" s="48" t="n">
-        <v>51.01694915254237</v>
-      </c>
-      <c r="G40" s="46" t="inlineStr">
-        <is>
-          <t>7/7</t>
-        </is>
-      </c>
-      <c r="H40" s="48" t="n">
-        <v>100</v>
-      </c>
-      <c r="I40" s="48" t="n">
-        <v>30</v>
-      </c>
-      <c r="J40" s="48" t="n">
-        <v>81.01694915254237</v>
-      </c>
-      <c r="K40" s="46" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="46" t="n">
-        <v>40</v>
-      </c>
-      <c r="B41" s="46" t="inlineStr">
-        <is>
-          <t>6710553337</t>
-        </is>
-      </c>
-      <c r="C41" s="47" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D41" s="46" t="inlineStr">
-        <is>
-          <t>94.00/118.00</t>
-        </is>
-      </c>
-      <c r="E41" s="48" t="n">
-        <v>79.66101694915254</v>
-      </c>
-      <c r="F41" s="48" t="n">
-        <v>55.76271186440678</v>
-      </c>
-      <c r="G41" s="46" t="inlineStr">
-        <is>
-          <t>7/7</t>
-        </is>
-      </c>
-      <c r="H41" s="48" t="n">
-        <v>100</v>
-      </c>
-      <c r="I41" s="48" t="n">
-        <v>30</v>
-      </c>
-      <c r="J41" s="48" t="n">
-        <v>85.76271186440678</v>
-      </c>
-      <c r="K41" s="46" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="46" t="n">
-        <v>41</v>
-      </c>
-      <c r="B42" s="46" t="inlineStr">
-        <is>
-          <t>6710553345</t>
-        </is>
-      </c>
-      <c r="C42" s="47" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D42" s="46" t="inlineStr">
-        <is>
-          <t>90.00/118.00</t>
-        </is>
-      </c>
-      <c r="E42" s="48" t="n">
-        <v>76.27118644067797</v>
-      </c>
-      <c r="F42" s="48" t="n">
-        <v>53.38983050847457</v>
-      </c>
-      <c r="G42" s="46" t="inlineStr">
-        <is>
-          <t>7/7</t>
-        </is>
-      </c>
-      <c r="H42" s="48" t="n">
-        <v>100</v>
-      </c>
-      <c r="I42" s="48" t="n">
-        <v>30</v>
-      </c>
-      <c r="J42" s="48" t="n">
-        <v>83.38983050847457</v>
-      </c>
-      <c r="K42" s="46" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="46" t="n">
-        <v>42</v>
-      </c>
-      <c r="B43" s="46" t="inlineStr">
-        <is>
-          <t>6710553353</t>
-        </is>
-      </c>
-      <c r="C43" s="47" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D43" s="46" t="inlineStr">
-        <is>
-          <t>101.00/118.00</t>
-        </is>
-      </c>
-      <c r="E43" s="48" t="n">
-        <v>85.59322033898306</v>
-      </c>
-      <c r="F43" s="48" t="n">
-        <v>59.91525423728814</v>
-      </c>
-      <c r="G43" s="46" t="inlineStr">
-        <is>
-          <t>7/7</t>
-        </is>
-      </c>
-      <c r="H43" s="48" t="n">
-        <v>100</v>
-      </c>
-      <c r="I43" s="48" t="n">
-        <v>30</v>
-      </c>
-      <c r="J43" s="48" t="n">
-        <v>89.91525423728814</v>
-      </c>
-      <c r="K43" s="46" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="46" t="n">
-        <v>43</v>
-      </c>
-      <c r="B44" s="46" t="inlineStr">
-        <is>
-          <t>6710553361</t>
-        </is>
-      </c>
-      <c r="C44" s="47" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D44" s="46" t="inlineStr">
-        <is>
-          <t>103.00/118.00</t>
-        </is>
-      </c>
-      <c r="E44" s="48" t="n">
-        <v>87.28813559322035</v>
-      </c>
-      <c r="F44" s="48" t="n">
-        <v>61.10169491525424</v>
-      </c>
-      <c r="G44" s="46" t="inlineStr">
-        <is>
-          <t>7/7</t>
-        </is>
-      </c>
-      <c r="H44" s="48" t="n">
-        <v>100</v>
-      </c>
-      <c r="I44" s="48" t="n">
-        <v>30</v>
-      </c>
-      <c r="J44" s="48" t="n">
-        <v>91.10169491525423</v>
-      </c>
-      <c r="K44" s="46" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="46" t="n">
-        <v>44</v>
-      </c>
-      <c r="B45" s="46" t="inlineStr">
-        <is>
-          <t>6710553370</t>
-        </is>
-      </c>
-      <c r="C45" s="47" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D45" s="46" t="inlineStr">
-        <is>
-          <t>52.00/118.00</t>
-        </is>
-      </c>
-      <c r="E45" s="48" t="n">
-        <v>44.06779661016949</v>
-      </c>
-      <c r="F45" s="48" t="n">
-        <v>30.84745762711864</v>
-      </c>
-      <c r="G45" s="46" t="inlineStr">
-        <is>
-          <t>7/7</t>
-        </is>
-      </c>
-      <c r="H45" s="48" t="n">
-        <v>100</v>
-      </c>
-      <c r="I45" s="48" t="n">
-        <v>30</v>
-      </c>
-      <c r="J45" s="48" t="n">
-        <v>60.84745762711864</v>
-      </c>
-      <c r="K45" s="46" t="inlineStr">
-        <is>
-          <t>★★☆☆☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="46" t="n">
-        <v>45</v>
-      </c>
-      <c r="B46" s="46" t="inlineStr">
-        <is>
-          <t>6710553388</t>
-        </is>
-      </c>
-      <c r="C46" s="47" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D46" s="46" t="inlineStr">
-        <is>
-          <t>107.00/118.00</t>
-        </is>
-      </c>
-      <c r="E46" s="48" t="n">
-        <v>90.67796610169492</v>
-      </c>
-      <c r="F46" s="48" t="n">
-        <v>63.47457627118644</v>
-      </c>
-      <c r="G46" s="46" t="inlineStr">
-        <is>
-          <t>7/7</t>
-        </is>
-      </c>
-      <c r="H46" s="48" t="n">
-        <v>100</v>
-      </c>
-      <c r="I46" s="48" t="n">
-        <v>30</v>
-      </c>
-      <c r="J46" s="48" t="n">
-        <v>93.47457627118644</v>
-      </c>
-      <c r="K46" s="46" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="46" t="n">
+    </row>
+    <row r="53">
+      <c r="A53" s="48" t="inlineStr">
+        <is>
+          <t>Attendance weight</t>
+        </is>
+      </c>
+      <c r="B53" s="50" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="48" t="n"/>
+      <c r="B54" s="49" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="48" t="inlineStr">
+        <is>
+          <t>Total students</t>
+        </is>
+      </c>
+      <c r="B55" s="49" t="n">
         <v>46</v>
       </c>
-      <c r="B47" s="46" t="inlineStr">
-        <is>
-          <t>6710553396</t>
-        </is>
-      </c>
-      <c r="C47" s="47" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="D47" s="46" t="inlineStr">
-        <is>
-          <t>96.00/118.00</t>
-        </is>
-      </c>
-      <c r="E47" s="48" t="n">
-        <v>81.35593220338984</v>
-      </c>
-      <c r="F47" s="48" t="n">
-        <v>56.94915254237289</v>
-      </c>
-      <c r="G47" s="46" t="inlineStr">
-        <is>
-          <t>7/7</t>
-        </is>
-      </c>
-      <c r="H47" s="48" t="n">
-        <v>100</v>
-      </c>
-      <c r="I47" s="48" t="n">
-        <v>30</v>
-      </c>
-      <c r="J47" s="48" t="n">
-        <v>86.94915254237289</v>
-      </c>
-      <c r="K47" s="46" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="49" t="inlineStr">
-        <is>
-          <t>Exercise maximum score</t>
-        </is>
-      </c>
-      <c r="B50" s="50" t="n">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="49" t="inlineStr">
-        <is>
-          <t>Exercise weight</t>
-        </is>
-      </c>
-      <c r="B51" s="51" t="n">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="49" t="inlineStr">
-        <is>
-          <t>Attendance sessions</t>
-        </is>
-      </c>
-      <c r="B52" s="50" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="49" t="inlineStr">
-        <is>
-          <t>Attendance weight</t>
-        </is>
-      </c>
-      <c r="B53" s="51" t="n">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="49" t="n"/>
-      <c r="B54" s="50" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="49" t="inlineStr">
-        <is>
-          <t>Total students</t>
-        </is>
-      </c>
-      <c r="B55" s="50" t="n">
-        <v>46</v>
-      </c>
     </row>
     <row r="56">
-      <c r="A56" s="49" t="inlineStr">
+      <c r="A56" s="48" t="inlineStr">
         <is>
           <t>Mean Grand Total</t>
         </is>
       </c>
-      <c r="B56" s="52" t="n">
-        <v>71.53147699757869</v>
+      <c r="B56" s="51" t="n">
+        <v>70.31929347826087</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="49" t="inlineStr">
+      <c r="A57" s="48" t="inlineStr">
         <is>
           <t>SD Grand Total (population)</t>
         </is>
       </c>
-      <c r="B57" s="52" t="n">
-        <v>19.49221390346051</v>
+      <c r="B57" s="51" t="n">
+        <v>18.95225231539077</v>
       </c>
     </row>
   </sheetData>
